--- a/2026/SALTA 1167/Julio/SALTA1167-Julio.xlsx
+++ b/2026/SALTA 1167/Julio/SALTA1167-Julio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44AE9C5-1525-423D-860F-9208DA998AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3F5D8D-B0A2-481E-9293-2A49DC7A2A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,11 +24,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="148">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -427,24 +432,9 @@
     <t xml:space="preserve">Ingreso 05/05 </t>
   </si>
   <si>
-    <t>Transf 02/06</t>
-  </si>
-  <si>
-    <t>Cambio de caja de piso</t>
-  </si>
-  <si>
     <t>Transf 05/06</t>
   </si>
   <si>
-    <t>Transf 08/06</t>
-  </si>
-  <si>
-    <t>Horas extra Sra. Carina</t>
-  </si>
-  <si>
-    <t>Easy Barracas - Compra de termotanque - Cuota 4  - Restan 2 cuotas de $157.988,29</t>
-  </si>
-  <si>
     <t>Transf 30/06</t>
   </si>
   <si>
@@ -473,6 +463,24 @@
   </si>
   <si>
     <t>Transf 06/07</t>
+  </si>
+  <si>
+    <t>Transf 13/07</t>
+  </si>
+  <si>
+    <t>Transf 23/07</t>
+  </si>
+  <si>
+    <t>Grupo protect - Compra de matafuegos - Cuota 1/3</t>
+  </si>
+  <si>
+    <t>Easy Barracas - Compra de termotanque - Cuota 5  - Resta 1 cuotas de $157.988,29</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>Compra de pilas - Puerta SUM</t>
   </si>
 </sst>
 </file>
@@ -491,7 +499,7 @@
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -687,6 +695,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1117,7 +1132,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1347,7 +1362,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1395,120 +1409,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1519,22 +1419,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1549,12 +1442,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1567,9 +1454,139 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="26" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="26" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1648,9 +1665,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1688,9 +1705,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1723,9 +1740,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1758,9 +1792,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1935,21 +1986,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="44" t="s">
         <v>74</v>
@@ -1958,7 +2009,7 @@
       <c r="D1" s="44"/>
       <c r="E1" s="45"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="46" t="s">
         <v>14</v>
@@ -1967,16 +2018,16 @@
       <c r="D2" s="46"/>
       <c r="E2" s="47"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="206" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="174"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="207"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
@@ -1987,12 +2038,12 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>75</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="46" t="s">
@@ -2000,7 +2051,7 @@
       </c>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>126</v>
       </c>
@@ -2011,57 +2062,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="176" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="176"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="176"/>
-      <c r="C9" s="176"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="175" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="209" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="209"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="209"/>
+      <c r="C10" s="209"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="208" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="175"/>
-      <c r="C13" s="175"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="175"/>
-      <c r="B14" s="175"/>
-      <c r="C14" s="175"/>
-      <c r="D14" s="175"/>
-      <c r="E14" s="175"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="175"/>
-      <c r="B15" s="175"/>
-      <c r="C15" s="175"/>
-      <c r="D15" s="175"/>
-      <c r="E15" s="175"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="175"/>
-      <c r="B16" s="175"/>
-      <c r="C16" s="175"/>
-      <c r="D16" s="175"/>
-      <c r="E16" s="175"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="208"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="208"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>104</v>
       </c>
@@ -2070,7 +2121,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>77</v>
       </c>
@@ -2079,283 +2130,287 @@
       <c r="D21" s="100"/>
       <c r="E21" s="94"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="209" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="200" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="210"/>
-      <c r="C22" s="211"/>
-      <c r="D22" s="171">
+      <c r="B22" s="201"/>
+      <c r="C22" s="172"/>
+      <c r="D22" s="170">
         <v>510846.85</v>
       </c>
-      <c r="E22" s="163" t="s">
-        <v>145</v>
+      <c r="E22" s="162" t="s">
+        <v>140</v>
       </c>
       <c r="H22" s="83"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="209" t="s">
-        <v>135</v>
-      </c>
-      <c r="B23" s="210"/>
-      <c r="C23" s="211"/>
-      <c r="D23" s="212">
-        <v>15000</v>
-      </c>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="200"/>
+      <c r="B23" s="201"/>
+      <c r="C23" s="172"/>
+      <c r="D23" s="173"/>
       <c r="E23" s="95"/>
       <c r="H23" s="83"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="213" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="213"/>
-      <c r="C24" s="213"/>
+      <c r="B24" s="174"/>
+      <c r="C24" s="174"/>
       <c r="D24" s="101"/>
-      <c r="E24" s="154">
+      <c r="E24" s="153">
         <f>SUM(D22:D23)</f>
-        <v>525846.85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="214" t="s">
+        <v>510846.85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="213"/>
-      <c r="C25" s="213"/>
-      <c r="D25" s="215"/>
-      <c r="E25" s="155"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="209" t="s">
+      <c r="B25" s="174"/>
+      <c r="C25" s="174"/>
+      <c r="D25" s="176"/>
+      <c r="E25" s="154"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="200" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="210"/>
-      <c r="C26" s="216"/>
-      <c r="D26" s="217">
+      <c r="B26" s="201"/>
+      <c r="C26" s="177"/>
+      <c r="D26" s="240">
         <v>79864</v>
       </c>
       <c r="E26" s="97" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="213" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="213"/>
-      <c r="C27" s="213"/>
+      <c r="B27" s="174"/>
+      <c r="C27" s="174"/>
       <c r="D27" s="101"/>
       <c r="E27" s="107">
         <f>SUM(D26:D26)</f>
         <v>79864</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="214" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="218"/>
-      <c r="C28" s="218"/>
-      <c r="D28" s="219"/>
-      <c r="E28" s="156"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="178"/>
+      <c r="C28" s="178"/>
+      <c r="D28" s="179"/>
+      <c r="E28" s="155"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="65" t="s">
         <v>67</v>
       </c>
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
-      <c r="D29" s="170">
-        <v>162387.16</v>
-      </c>
-      <c r="E29" s="163"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D29" s="169">
+        <v>162387.66</v>
+      </c>
+      <c r="E29" s="97" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
         <v>66</v>
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
-      <c r="D30" s="170">
+      <c r="D30" s="169">
         <v>7090.36</v>
       </c>
-      <c r="E30" s="163" t="str">
+      <c r="E30" s="162" t="str">
         <f>E31</f>
         <v>Transf 06/07</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="220"/>
+      <c r="B31" s="180"/>
       <c r="C31" s="65"/>
-      <c r="D31" s="170">
+      <c r="D31" s="169">
         <v>482288.43</v>
       </c>
       <c r="E31" s="97" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="204" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="205"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="169">
+        <v>632390</v>
+      </c>
+      <c r="E32" s="97" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="181" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="182"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="169">
+        <v>27338.01</v>
+      </c>
+      <c r="E33" s="97" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="174" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="174"/>
+      <c r="C34" s="174"/>
+      <c r="D34" s="183"/>
+      <c r="E34" s="156">
+        <f>SUM(D29:D33)</f>
+        <v>1311494.46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="175"/>
+      <c r="B35" s="174"/>
+      <c r="C35" s="174"/>
+      <c r="D35" s="101"/>
+      <c r="E35" s="157"/>
+    </row>
+    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="200" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="201"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="169">
+        <v>82000</v>
+      </c>
+      <c r="E36" s="97" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="184" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" s="185"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="169">
+        <v>199530</v>
+      </c>
+      <c r="E37" s="97" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="200" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" s="201"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="171">
+        <v>339060</v>
+      </c>
+      <c r="E38" s="97" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="200" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="201"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="171">
+        <v>157988.29</v>
+      </c>
+      <c r="E39" s="97"/>
+    </row>
+    <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="200" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="201"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="171">
+        <v>8000</v>
+      </c>
+      <c r="E40" s="97" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="221" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="222"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="170">
-        <v>632390</v>
-      </c>
-      <c r="E32" s="97" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="223" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="224"/>
-      <c r="C33" s="65"/>
-      <c r="D33" s="96">
-        <v>26036.19</v>
-      </c>
-      <c r="E33" s="97" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="213" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" s="213"/>
-      <c r="C34" s="213"/>
-      <c r="D34" s="225"/>
-      <c r="E34" s="157">
-        <f>SUM(D29:D33)</f>
-        <v>1310192.1399999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="214"/>
-      <c r="B35" s="213"/>
-      <c r="C35" s="213"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="158"/>
-    </row>
-    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="209" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="210"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="170">
-        <v>82000</v>
-      </c>
-      <c r="E36" s="97" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="226" t="s">
-        <v>132</v>
-      </c>
-      <c r="B37" s="227"/>
-      <c r="C37" s="65"/>
-      <c r="D37" s="68">
-        <v>150000</v>
-      </c>
-      <c r="E37" s="97" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="209" t="s">
-        <v>143</v>
-      </c>
-      <c r="B38" s="210"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="172">
-        <v>339060</v>
-      </c>
-      <c r="E38" s="97" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="209" t="s">
-        <v>136</v>
-      </c>
-      <c r="B39" s="210"/>
-      <c r="C39" s="65"/>
-      <c r="D39" s="68">
-        <v>157988.29</v>
-      </c>
-      <c r="E39" s="97"/>
-    </row>
-    <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="209"/>
-      <c r="B40" s="210"/>
-      <c r="C40" s="65"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="97"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="213" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="174" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="214"/>
-      <c r="C41" s="214"/>
-      <c r="D41" s="214"/>
+      <c r="B41" s="175"/>
+      <c r="C41" s="175"/>
+      <c r="D41" s="175"/>
       <c r="E41" s="107">
         <f>SUM(D36:D40)</f>
-        <v>729048.29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="214" t="s">
+        <v>786578.29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="214"/>
-      <c r="C42" s="214"/>
+      <c r="B42" s="175"/>
+      <c r="C42" s="175"/>
       <c r="D42" s="100"/>
-      <c r="E42" s="159"/>
-    </row>
-    <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="209" t="s">
-        <v>142</v>
-      </c>
-      <c r="B43" s="210"/>
-      <c r="C43" s="211"/>
-      <c r="D43" s="228">
+      <c r="E42" s="158"/>
+    </row>
+    <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="200" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="201"/>
+      <c r="C43" s="172"/>
+      <c r="D43" s="186">
         <v>170000</v>
       </c>
-      <c r="E43" s="160" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="213" t="s">
+      <c r="E43" s="159" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="213"/>
-      <c r="C44" s="213"/>
+      <c r="B44" s="174"/>
+      <c r="C44" s="174"/>
       <c r="D44" s="101"/>
-      <c r="E44" s="154">
+      <c r="E44" s="153">
         <f>SUM(D43:D43)</f>
         <v>170000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="214" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="175" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="229"/>
-      <c r="C45" s="213"/>
+      <c r="B45" s="187"/>
+      <c r="C45" s="174"/>
       <c r="D45" s="99"/>
       <c r="E45" s="107"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="65" t="s">
         <v>26</v>
       </c>
@@ -2364,20 +2419,20 @@
       <c r="D46" s="96">
         <v>69000</v>
       </c>
-      <c r="E46" s="161"/>
-    </row>
-    <row r="47" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="230" t="s">
-        <v>138</v>
-      </c>
-      <c r="B47" s="231"/>
+      <c r="E46" s="160"/>
+    </row>
+    <row r="47" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="202" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="203"/>
       <c r="C47" s="65"/>
       <c r="D47" s="96">
         <v>14770</v>
       </c>
-      <c r="E47" s="161"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E47" s="160"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="65" t="s">
         <v>116</v>
       </c>
@@ -2386,66 +2441,66 @@
       <c r="D48" s="96">
         <v>56522.84</v>
       </c>
-      <c r="E48" s="162"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="232" t="s">
+      <c r="E48" s="161"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="188" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="232"/>
-      <c r="C49" s="232"/>
+      <c r="B49" s="188"/>
+      <c r="C49" s="188"/>
       <c r="D49" s="70"/>
       <c r="E49" s="107">
         <f>SUM(D46:D48)</f>
         <v>140292.84</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="65"/>
       <c r="B50" s="65"/>
       <c r="C50" s="65"/>
       <c r="D50" s="65"/>
       <c r="E50" s="71"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="233" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="189" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="233"/>
-      <c r="C51" s="233"/>
+      <c r="B51" s="189"/>
+      <c r="C51" s="189"/>
       <c r="D51" s="72"/>
       <c r="E51" s="108"/>
     </row>
-    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="234"/>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="190"/>
       <c r="B52" s="73"/>
       <c r="C52" s="73"/>
       <c r="D52" s="73"/>
       <c r="E52" s="74"/>
       <c r="F52" s="27"/>
     </row>
-    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="235" t="s">
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="191" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="236"/>
+      <c r="B53" s="192"/>
       <c r="C53" s="75"/>
       <c r="D53" s="75"/>
       <c r="E53" s="76">
         <f>(SUM(E21:E51))</f>
-        <v>2955244.1199999996</v>
+        <v>2999076.44</v>
       </c>
       <c r="F53" s="93"/>
       <c r="G53" s="27"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="73"/>
       <c r="B54" s="73"/>
       <c r="C54" s="73"/>
       <c r="D54" s="73"/>
       <c r="E54" s="73"/>
     </row>
-    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="73"/>
       <c r="B55" s="73"/>
       <c r="C55" s="73"/>
@@ -2453,44 +2508,44 @@
       <c r="E55" s="73"/>
       <c r="H55" s="102"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="237" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="193" t="s">
         <v>97</v>
       </c>
-      <c r="B56" s="238"/>
-      <c r="C56" s="239"/>
+      <c r="B56" s="194"/>
+      <c r="C56" s="195"/>
       <c r="D56" s="77"/>
       <c r="E56" s="78"/>
     </row>
-    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="240"/>
-      <c r="B57" s="224"/>
+    <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="196"/>
+      <c r="B57" s="182"/>
       <c r="C57" s="65"/>
       <c r="D57" s="68"/>
       <c r="E57" s="66"/>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="241"/>
-      <c r="B58" s="241"/>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="199"/>
+      <c r="B58" s="199"/>
       <c r="C58" s="65"/>
       <c r="D58" s="96"/>
       <c r="E58" s="66"/>
     </row>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="67"/>
       <c r="B60" s="69"/>
       <c r="C60" s="4"/>
       <c r="D60" s="68"/>
       <c r="E60" s="66"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="32"/>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
@@ -2500,19 +2555,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
         <v>99</v>
       </c>
       <c r="B64" s="20"/>
       <c r="C64" s="20"/>
       <c r="D64" s="21"/>
-      <c r="E64" s="151"/>
-    </row>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E64" s="150"/>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>98</v>
       </c>
@@ -2524,26 +2579,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="63" t="s">
         <v>105</v>
       </c>
       <c r="B68" s="64">
         <f>E53</f>
-        <v>2955244.1199999996</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2999076.44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="63" t="s">
         <v>106</v>
       </c>
       <c r="B69" s="64">
         <f>E53-E51</f>
-        <v>2955244.1199999996</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2999076.44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="63" t="s">
         <v>107</v>
       </c>
@@ -2552,7 +2607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="63" t="s">
         <v>108</v>
       </c>
@@ -2561,12 +2616,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="B73" s="26"/>
       <c r="C73" s="24"/>
     </row>
-    <row r="74" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="85" t="s">
         <v>109</v>
       </c>
@@ -2576,17 +2631,17 @@
       <c r="C74" s="24"/>
       <c r="D74" s="30"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
         <v>102</v>
       </c>
       <c r="B75" s="90">
         <f>-B69</f>
-        <v>-2955244.1199999996</v>
+        <v>-2999076.44</v>
       </c>
       <c r="E75" s="27"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
         <v>25</v>
       </c>
@@ -2595,38 +2650,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
         <v>111</v>
       </c>
       <c r="B77" s="91">
         <f>PRORRATEO!G36-B84</f>
-        <v>2367966.9600000004</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2788870.3600000008</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="92" t="s">
         <v>24</v>
       </c>
       <c r="B78" s="103"/>
     </row>
-    <row r="79" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="88" t="s">
         <v>113</v>
       </c>
       <c r="B79" s="89">
         <f>SUM(B74:C78)</f>
-        <v>-295388.1699999976</v>
+        <v>81682.910000002477</v>
       </c>
       <c r="D79" s="27"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="86"/>
       <c r="B80" s="86"/>
       <c r="D80" s="27"/>
       <c r="E80" s="26"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="85" t="s">
         <v>110</v>
       </c>
@@ -2636,7 +2691,7 @@
       <c r="D81" s="26"/>
       <c r="E81" s="27"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
         <v>103</v>
       </c>
@@ -2647,7 +2702,7 @@
       <c r="D82" s="27"/>
       <c r="E82" s="27"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
         <v>25</v>
       </c>
@@ -2657,16 +2712,16 @@
       </c>
       <c r="D83" s="27"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="35" t="s">
         <v>112</v>
       </c>
       <c r="B84" s="91">
         <v>0</v>
       </c>
-      <c r="D84" s="152"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D84" s="151"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="92" t="s">
         <v>24</v>
       </c>
@@ -2674,7 +2729,7 @@
       <c r="E85" s="27"/>
       <c r="F85" s="26"/>
     </row>
-    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="88" t="s">
         <v>114</v>
       </c>
@@ -2684,15 +2739,15 @@
       </c>
       <c r="F86" s="27"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="86"/>
       <c r="B87" s="86"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="86"/>
       <c r="B88" s="86"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="85" t="s">
         <v>129</v>
       </c>
@@ -2700,7 +2755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="35" t="s">
         <v>130</v>
       </c>
@@ -2708,32 +2763,32 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="92"/>
       <c r="B91" s="103"/>
     </row>
-    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="88" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B92" s="89">
         <v>1025063.51</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="178" t="s">
+    <row r="93" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="198" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="178"/>
-      <c r="C94" s="178"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="178"/>
-      <c r="B95" s="178"/>
-      <c r="C95" s="178"/>
-    </row>
-    <row r="96" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B94" s="198"/>
+      <c r="C94" s="198"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="198"/>
+      <c r="B95" s="198"/>
+      <c r="C95" s="198"/>
+    </row>
+    <row r="96" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="80"/>
       <c r="B96" s="23"/>
       <c r="C96" s="23">
@@ -2741,13 +2796,13 @@
       </c>
       <c r="E96" s="93"/>
     </row>
-    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="80"/>
       <c r="B97" s="82"/>
       <c r="C97" s="79"/>
       <c r="D97" s="93"/>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="28" t="s">
         <v>6</v>
       </c>
@@ -2757,39 +2812,46 @@
       </c>
       <c r="C98" s="29"/>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M99" s="5"/>
     </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="177"/>
-      <c r="B100" s="177"/>
-      <c r="C100" s="177"/>
-      <c r="D100" s="177"/>
-      <c r="E100" s="177"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="177"/>
-      <c r="B101" s="177"/>
-      <c r="C101" s="177"/>
-      <c r="D101" s="177"/>
-      <c r="E101" s="177"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="177"/>
-      <c r="B102" s="177"/>
-      <c r="C102" s="177"/>
-      <c r="D102" s="177"/>
-      <c r="E102" s="177"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="177"/>
-      <c r="B103" s="177"/>
-      <c r="C103" s="177"/>
-      <c r="D103" s="177"/>
-      <c r="E103" s="177"/>
+    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="197"/>
+      <c r="B100" s="197"/>
+      <c r="C100" s="197"/>
+      <c r="D100" s="197"/>
+      <c r="E100" s="197"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="197"/>
+      <c r="B101" s="197"/>
+      <c r="C101" s="197"/>
+      <c r="D101" s="197"/>
+      <c r="E101" s="197"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="197"/>
+      <c r="B102" s="197"/>
+      <c r="C102" s="197"/>
+      <c r="D102" s="197"/>
+      <c r="E102" s="197"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="197"/>
+      <c r="B103" s="197"/>
+      <c r="C103" s="197"/>
+      <c r="D103" s="197"/>
+      <c r="E103" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A100:E103"/>
     <mergeCell ref="A94:C95"/>
     <mergeCell ref="A58:B58"/>
@@ -2799,13 +2861,6 @@
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2816,47 +2871,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="119"/>
       <c r="B1" s="120"/>
       <c r="C1" s="121"/>
       <c r="D1" s="121"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
-      <c r="N1" s="179"/>
+      <c r="E1" s="215"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
+      <c r="L1" s="215"/>
+      <c r="M1" s="215"/>
+      <c r="N1" s="215"/>
       <c r="O1" s="120"/>
       <c r="P1" s="122"/>
     </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="123"/>
       <c r="B2" s="124"/>
       <c r="C2" s="125"/>
@@ -2883,7 +2938,7 @@
       <c r="P2" s="131"/>
       <c r="Q2" s="19"/>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="123"/>
       <c r="B3" s="124"/>
       <c r="C3" s="125"/>
@@ -2902,212 +2957,212 @@
       <c r="P3" s="131"/>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="190" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="222" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="191"/>
-      <c r="L4" s="191"/>
-      <c r="M4" s="191"/>
-      <c r="N4" s="191"/>
-      <c r="O4" s="191"/>
-      <c r="P4" s="192"/>
+      <c r="B4" s="223"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="223"/>
+      <c r="G4" s="223"/>
+      <c r="H4" s="223"/>
+      <c r="I4" s="223"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="223"/>
+      <c r="L4" s="223"/>
+      <c r="M4" s="223"/>
+      <c r="N4" s="223"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="224"/>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="193"/>
-      <c r="B5" s="194"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
-      <c r="F5" s="194"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="194"/>
-      <c r="I5" s="194"/>
-      <c r="J5" s="194"/>
-      <c r="K5" s="194"/>
-      <c r="L5" s="194"/>
-      <c r="M5" s="194"/>
-      <c r="N5" s="194"/>
-      <c r="O5" s="194"/>
-      <c r="P5" s="195"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="225"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="226"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="226"/>
+      <c r="N5" s="226"/>
+      <c r="O5" s="226"/>
+      <c r="P5" s="227"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="193"/>
-      <c r="B6" s="194"/>
-      <c r="C6" s="194"/>
-      <c r="D6" s="194"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="194"/>
-      <c r="I6" s="194"/>
-      <c r="J6" s="194"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="194"/>
-      <c r="N6" s="194"/>
-      <c r="O6" s="194"/>
-      <c r="P6" s="195"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="225"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
+      <c r="L6" s="226"/>
+      <c r="M6" s="226"/>
+      <c r="N6" s="226"/>
+      <c r="O6" s="226"/>
+      <c r="P6" s="227"/>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="193"/>
-      <c r="B7" s="194"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="194"/>
-      <c r="I7" s="194"/>
-      <c r="J7" s="194"/>
-      <c r="K7" s="194"/>
-      <c r="L7" s="194"/>
-      <c r="M7" s="194"/>
-      <c r="N7" s="194"/>
-      <c r="O7" s="194"/>
-      <c r="P7" s="195"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="225"/>
+      <c r="B7" s="226"/>
+      <c r="C7" s="226"/>
+      <c r="D7" s="226"/>
+      <c r="E7" s="226"/>
+      <c r="F7" s="226"/>
+      <c r="G7" s="226"/>
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="226"/>
+      <c r="N7" s="226"/>
+      <c r="O7" s="226"/>
+      <c r="P7" s="227"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="196"/>
-      <c r="B8" s="197"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="197"/>
-      <c r="E8" s="197"/>
-      <c r="F8" s="197"/>
-      <c r="G8" s="197"/>
-      <c r="H8" s="197"/>
-      <c r="I8" s="197"/>
-      <c r="J8" s="197"/>
-      <c r="K8" s="197"/>
-      <c r="L8" s="197"/>
-      <c r="M8" s="197"/>
-      <c r="N8" s="197"/>
-      <c r="O8" s="197"/>
-      <c r="P8" s="198"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="201" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="228"/>
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="230"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="233" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="202"/>
-      <c r="C9" s="202"/>
-      <c r="D9" s="202"/>
-      <c r="E9" s="202"/>
-      <c r="F9" s="202"/>
-      <c r="G9" s="202"/>
-      <c r="H9" s="202"/>
-      <c r="I9" s="202"/>
-      <c r="J9" s="202"/>
-      <c r="K9" s="202"/>
-      <c r="L9" s="202"/>
-      <c r="M9" s="202"/>
-      <c r="N9" s="202"/>
-      <c r="O9" s="202"/>
-      <c r="P9" s="202"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="203" t="s">
+      <c r="B9" s="234"/>
+      <c r="C9" s="234"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="234"/>
+      <c r="F9" s="234"/>
+      <c r="G9" s="234"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="234"/>
+      <c r="J9" s="234"/>
+      <c r="K9" s="234"/>
+      <c r="L9" s="234"/>
+      <c r="M9" s="234"/>
+      <c r="N9" s="234"/>
+      <c r="O9" s="234"/>
+      <c r="P9" s="234"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="235" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="203"/>
-      <c r="C10" s="203"/>
-      <c r="D10" s="203"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="203"/>
-      <c r="G10" s="203"/>
-      <c r="H10" s="203"/>
-      <c r="I10" s="203"/>
-      <c r="J10" s="203"/>
-      <c r="K10" s="203"/>
-      <c r="L10" s="203"/>
-      <c r="M10" s="203"/>
-      <c r="N10" s="203"/>
-      <c r="O10" s="203"/>
-      <c r="P10" s="203"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="184" t="s">
+      <c r="B10" s="235"/>
+      <c r="C10" s="235"/>
+      <c r="D10" s="235"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="235"/>
+      <c r="G10" s="235"/>
+      <c r="H10" s="235"/>
+      <c r="I10" s="235"/>
+      <c r="J10" s="235"/>
+      <c r="K10" s="235"/>
+      <c r="L10" s="235"/>
+      <c r="M10" s="235"/>
+      <c r="N10" s="235"/>
+      <c r="O10" s="235"/>
+      <c r="P10" s="235"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="210" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="104"/>
-      <c r="C11" s="184" t="s">
+      <c r="C11" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="184" t="s">
+      <c r="D11" s="210" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="184" t="s">
+      <c r="E11" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="180" t="s">
+      <c r="F11" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="184" t="s">
+      <c r="G11" s="210" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="186" t="s">
+      <c r="H11" s="218" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="180" t="s">
+      <c r="I11" s="213" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="180" t="s">
+      <c r="J11" s="213" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="188" t="s">
+      <c r="K11" s="220" t="s">
         <v>95</v>
       </c>
-      <c r="L11" s="180" t="s">
+      <c r="L11" s="213" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="180" t="s">
+      <c r="M11" s="213" t="s">
         <v>128</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="182" t="s">
+      <c r="O11" s="216" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="199" t="s">
+      <c r="P11" s="231" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="185"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="212"/>
       <c r="B12" s="105"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="204"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="181"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="187"/>
-      <c r="I12" s="181"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="189"/>
-      <c r="L12" s="181"/>
-      <c r="M12" s="181"/>
+      <c r="C12" s="212"/>
+      <c r="D12" s="211"/>
+      <c r="E12" s="212"/>
+      <c r="F12" s="214"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="219"/>
+      <c r="I12" s="214"/>
+      <c r="J12" s="214"/>
+      <c r="K12" s="221"/>
+      <c r="L12" s="214"/>
+      <c r="M12" s="214"/>
       <c r="N12" s="37" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="O12" s="183"/>
-      <c r="P12" s="200"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O12" s="217"/>
+      <c r="P12" s="232"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>1</v>
       </c>
@@ -3122,19 +3177,19 @@
         <v>12</v>
       </c>
       <c r="F13" s="49">
-        <v>288000.01</v>
-      </c>
-      <c r="G13" s="50">
-        <f>316800.01+396-G29-G30</f>
-        <v>287999.66000000003</v>
+        <v>324000.01</v>
+      </c>
+      <c r="G13" s="241">
+        <f>356868.01-G29-G30</f>
+        <v>324009.66000000003</v>
       </c>
       <c r="H13" s="51">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
-        <v>0.34999999997671694</v>
+        <v>-9.6500000000232831</v>
       </c>
       <c r="I13" s="51">
         <f>IF(H13&gt;0,H13*3%,0)</f>
-        <v>1.0499999999301507E-2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="98">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
@@ -3144,86 +3199,86 @@
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="149">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="M13" s="165"/>
-      <c r="N13" s="149">
+      <c r="M13" s="164"/>
+      <c r="N13" s="148">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
-        <v>324000.01</v>
+        <v>323990.01</v>
       </c>
       <c r="O13" s="52">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
-        <v>343440.01</v>
+        <v>343429.01</v>
       </c>
       <c r="P13" s="53">
         <f>ROUND(N13*3%,0) + N13</f>
-        <v>333720.01</v>
+        <v>333710.01</v>
       </c>
       <c r="Q13" s="27">
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="142">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="141">
         <v>2</v>
       </c>
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="141" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="143"/>
-      <c r="E14" s="144">
+      <c r="D14" s="142"/>
+      <c r="E14" s="143">
         <v>6.6</v>
       </c>
       <c r="F14" s="50">
-        <v>189415.02</v>
-      </c>
-      <c r="G14" s="50">
-        <v>190000</v>
-      </c>
-      <c r="H14" s="145">
+        <v>280517.02</v>
+      </c>
+      <c r="G14" s="241">
+        <v>281000</v>
+      </c>
+      <c r="H14" s="144">
         <f t="shared" si="0"/>
-        <v>-584.98000000001048</v>
-      </c>
-      <c r="I14" s="145">
+        <v>-482.97999999998137</v>
+      </c>
+      <c r="I14" s="144">
         <f t="shared" ref="I14:I35" si="3">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="146">
+      <c r="J14" s="145">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K14" s="146">
+      <c r="K14" s="145">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="153">
+      <c r="L14" s="152">
         <f>EDESUR!I6</f>
         <v>102901.79</v>
       </c>
-      <c r="M14" s="166"/>
-      <c r="N14" s="149">
+      <c r="M14" s="165"/>
+      <c r="N14" s="148">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>280517.02</v>
-      </c>
-      <c r="O14" s="147">
+        <v>280619.02</v>
+      </c>
+      <c r="O14" s="146">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>297348.02</v>
-      </c>
-      <c r="P14" s="148">
+        <v>297456.02</v>
+      </c>
+      <c r="P14" s="147">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>288933.02</v>
+        <v>289038.02</v>
       </c>
       <c r="Q14" s="27">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>3</v>
       </c>
@@ -3240,11 +3295,11 @@
         <v>5.4</v>
       </c>
       <c r="F15" s="49">
-        <v>135021.03</v>
-      </c>
-      <c r="G15" s="50">
+        <v>149456.03</v>
+      </c>
+      <c r="G15" s="241">
         <f>F15</f>
-        <v>135021.03</v>
+        <v>149456.03</v>
       </c>
       <c r="H15" s="51">
         <f t="shared" si="0"/>
@@ -3262,12 +3317,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="150">
+      <c r="L15" s="149">
         <f>EDESUR!I7</f>
         <v>3655.79</v>
       </c>
-      <c r="M15" s="164"/>
-      <c r="N15" s="149">
+      <c r="M15" s="163"/>
+      <c r="N15" s="148">
         <f t="shared" si="4"/>
         <v>149456.03</v>
       </c>
@@ -3284,7 +3339,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>4</v>
       </c>
@@ -3301,15 +3356,15 @@
         <v>6.6</v>
       </c>
       <c r="F16" s="49">
-        <v>158400.04</v>
-      </c>
-      <c r="G16" s="50">
-        <f>178400.24-G32</f>
-        <v>164000.03999999998</v>
+        <v>172600.04</v>
+      </c>
+      <c r="G16" s="241">
+        <f>189033-G32</f>
+        <v>172603.8</v>
       </c>
       <c r="H16" s="51">
         <f t="shared" si="0"/>
-        <v>-5599.9999999999709</v>
+        <v>-3.7599999999802094</v>
       </c>
       <c r="I16" s="51">
         <f t="shared" si="3"/>
@@ -3323,83 +3378,83 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="150">
+      <c r="L16" s="149">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="M16" s="165"/>
-      <c r="N16" s="149">
+      <c r="M16" s="164"/>
+      <c r="N16" s="148">
         <f t="shared" si="4"/>
-        <v>172600.04</v>
+        <v>178196.04</v>
       </c>
       <c r="O16" s="52">
         <f t="shared" si="5"/>
-        <v>182956.04</v>
+        <v>188888.04</v>
       </c>
       <c r="P16" s="53">
         <f t="shared" si="6"/>
-        <v>177778.04</v>
+        <v>183542.04</v>
       </c>
       <c r="Q16" s="27">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="142">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="141">
         <v>5</v>
       </c>
-      <c r="B17" s="142" t="s">
+      <c r="B17" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="142" t="s">
+      <c r="D17" s="141" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="144">
+      <c r="E17" s="143">
         <v>6.6</v>
       </c>
       <c r="F17" s="50">
-        <v>158400.04999999999</v>
-      </c>
-      <c r="G17" s="50">
+        <v>178200.05</v>
+      </c>
+      <c r="G17" s="241">
         <f>F17</f>
-        <v>158400.04999999999</v>
-      </c>
-      <c r="H17" s="145">
+        <v>178200.05</v>
+      </c>
+      <c r="H17" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="145">
+      <c r="I17" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="146">
+      <c r="J17" s="145">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K17" s="146">
+      <c r="K17" s="145">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="153">
+      <c r="L17" s="152">
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="M17" s="166">
-        <v>0</v>
-      </c>
-      <c r="N17" s="149">
+      <c r="M17" s="165">
+        <v>0</v>
+      </c>
+      <c r="N17" s="148">
         <f t="shared" si="4"/>
         <v>178200.05</v>
       </c>
-      <c r="O17" s="147">
+      <c r="O17" s="146">
         <f t="shared" si="5"/>
         <v>188892.05</v>
       </c>
-      <c r="P17" s="148">
+      <c r="P17" s="147">
         <f t="shared" si="6"/>
         <v>183546.05</v>
       </c>
@@ -3411,7 +3466,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>6</v>
       </c>
@@ -3428,18 +3483,18 @@
         <v>5.4</v>
       </c>
       <c r="F18" s="49">
+        <v>156924.06</v>
+      </c>
+      <c r="G18" s="241">
         <v>129600.06</v>
-      </c>
-      <c r="G18" s="50">
-        <v>118800</v>
       </c>
       <c r="H18" s="51">
         <f t="shared" si="0"/>
-        <v>10800.059999999998</v>
+        <v>27324</v>
       </c>
       <c r="I18" s="51">
         <f t="shared" si="3"/>
-        <v>324.00179999999995</v>
+        <v>819.71999999999991</v>
       </c>
       <c r="J18" s="98">
         <f t="shared" si="1"/>
@@ -3449,148 +3504,150 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="150">
+      <c r="L18" s="149">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="M18" s="165"/>
-      <c r="N18" s="149">
+      <c r="M18" s="164"/>
+      <c r="N18" s="148">
         <f t="shared" si="4"/>
-        <v>156924.06</v>
+        <v>173944.06</v>
       </c>
       <c r="O18" s="52">
         <f t="shared" si="5"/>
-        <v>166340.06</v>
+        <v>184381.06</v>
       </c>
       <c r="P18" s="53">
         <f t="shared" si="6"/>
-        <v>161632.06</v>
+        <v>179162.06</v>
       </c>
       <c r="Q18" s="27">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="142">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="141">
         <v>7</v>
       </c>
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="142" t="s">
+      <c r="C19" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="142" t="s">
+      <c r="D19" s="141" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="144">
+      <c r="E19" s="143">
         <v>5.4</v>
       </c>
       <c r="F19" s="50">
-        <v>129600.07</v>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="145">
+        <v>279288.07</v>
+      </c>
+      <c r="G19" s="241">
+        <f>F19</f>
+        <v>279288.07</v>
+      </c>
+      <c r="H19" s="144">
         <f t="shared" si="0"/>
-        <v>129600.07</v>
-      </c>
-      <c r="I19" s="145">
+        <v>0</v>
+      </c>
+      <c r="I19" s="144">
         <f t="shared" si="3"/>
-        <v>3888.0021000000002</v>
-      </c>
-      <c r="J19" s="146">
+        <v>0</v>
+      </c>
+      <c r="J19" s="145">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K19" s="146">
+      <c r="K19" s="145">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="150">
+      <c r="L19" s="149">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M19" s="165"/>
-      <c r="N19" s="149">
+      <c r="M19" s="164"/>
+      <c r="N19" s="148">
         <f t="shared" si="4"/>
-        <v>279288.07</v>
-      </c>
-      <c r="O19" s="147">
+        <v>145800.07</v>
+      </c>
+      <c r="O19" s="146">
         <f t="shared" si="5"/>
-        <v>296045.07</v>
-      </c>
-      <c r="P19" s="148">
+        <v>154548.07</v>
+      </c>
+      <c r="P19" s="147">
         <f t="shared" si="6"/>
-        <v>287667.07</v>
+        <v>150174.07</v>
       </c>
       <c r="Q19" s="27">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="142">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="141">
         <v>8</v>
       </c>
-      <c r="B20" s="142" t="s">
+      <c r="B20" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="141" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="143" t="s">
+      <c r="D20" s="142" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="144">
+      <c r="E20" s="143">
         <v>6.6</v>
       </c>
       <c r="F20" s="50">
-        <v>225080.08</v>
+        <v>241432.08</v>
       </c>
       <c r="G20" s="50">
-        <f>F20</f>
-        <v>225080.08</v>
-      </c>
-      <c r="H20" s="145">
+        <v>0</v>
+      </c>
+      <c r="H20" s="144">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="145">
+        <v>241432.08</v>
+      </c>
+      <c r="I20" s="144">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="146">
+        <v>7242.9623999999994</v>
+      </c>
+      <c r="J20" s="145">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K20" s="146">
+      <c r="K20" s="145">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="150">
+      <c r="L20" s="149">
         <f>EDESUR!I13</f>
         <v>63231.57</v>
       </c>
-      <c r="M20" s="165"/>
-      <c r="N20" s="149">
+      <c r="M20" s="164"/>
+      <c r="N20" s="148">
         <f t="shared" si="4"/>
-        <v>241432.08</v>
-      </c>
-      <c r="O20" s="147">
+        <v>490107.08</v>
+      </c>
+      <c r="O20" s="146">
         <f t="shared" si="5"/>
-        <v>255918.07999999999</v>
-      </c>
-      <c r="P20" s="148">
+        <v>519514.08</v>
+      </c>
+      <c r="P20" s="147">
         <f t="shared" si="6"/>
-        <v>248675.08</v>
+        <v>504810.08</v>
       </c>
       <c r="Q20" s="27">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>9</v>
       </c>
@@ -3607,15 +3664,15 @@
         <v>6.6</v>
       </c>
       <c r="F21" s="49">
-        <v>130013.09</v>
-      </c>
-      <c r="G21" s="50">
-        <f>F21+28387</f>
-        <v>158400.09</v>
+        <v>199813.09</v>
+      </c>
+      <c r="G21" s="241">
+        <f>F21</f>
+        <v>199813.09</v>
       </c>
       <c r="H21" s="51">
         <f t="shared" si="0"/>
-        <v>-28387</v>
+        <v>0</v>
       </c>
       <c r="I21" s="51">
         <f t="shared" si="3"/>
@@ -3629,31 +3686,31 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="150">
+      <c r="L21" s="149">
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="M21" s="165">
+      <c r="M21" s="164">
         <v>50000</v>
       </c>
-      <c r="N21" s="149">
+      <c r="N21" s="148">
         <f t="shared" si="4"/>
-        <v>199813.09</v>
+        <v>228200.09</v>
       </c>
       <c r="O21" s="52">
         <f t="shared" si="5"/>
-        <v>211802.09</v>
+        <v>241892.09</v>
       </c>
       <c r="P21" s="53">
         <f t="shared" si="6"/>
-        <v>205807.09</v>
+        <v>235046.09</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>10</v>
       </c>
@@ -3670,15 +3727,15 @@
         <v>5.4</v>
       </c>
       <c r="F22" s="49">
-        <v>-0.9</v>
-      </c>
-      <c r="G22" s="50">
-        <f>RESUMEN!D39-28387</f>
-        <v>129601.29000000001</v>
+        <v>16198.1</v>
+      </c>
+      <c r="G22" s="243">
+        <f>RESUMEN!D39+16198.1</f>
+        <v>174186.39</v>
       </c>
       <c r="H22" s="51">
         <f>F22-G22</f>
-        <v>-129602.19</v>
+        <v>-157988.29</v>
       </c>
       <c r="I22" s="51">
         <f t="shared" si="3"/>
@@ -3692,29 +3749,29 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="150">
+      <c r="L22" s="149">
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="M22" s="165"/>
-      <c r="N22" s="149">
+      <c r="M22" s="164"/>
+      <c r="N22" s="148">
         <f t="shared" si="4"/>
-        <v>16198.1</v>
+        <v>-12187.9</v>
       </c>
       <c r="O22" s="52">
         <f t="shared" si="5"/>
-        <v>17170.099999999999</v>
+        <v>-12918.9</v>
       </c>
       <c r="P22" s="53">
         <f t="shared" si="6"/>
-        <v>16684.099999999999</v>
+        <v>-12553.9</v>
       </c>
       <c r="Q22" s="27">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>11</v>
       </c>
@@ -3729,19 +3786,19 @@
         <v>5.4</v>
       </c>
       <c r="F23" s="49">
-        <v>129600.11</v>
-      </c>
-      <c r="G23" s="50">
-        <f>136800-G34</f>
-        <v>129599.78</v>
+        <v>145800.10999999999</v>
+      </c>
+      <c r="G23" s="241">
+        <f>154014.33-G34</f>
+        <v>145800.10999999999</v>
       </c>
       <c r="H23" s="51">
         <f t="shared" si="0"/>
-        <v>0.33000000000174623</v>
+        <v>0</v>
       </c>
       <c r="I23" s="51">
         <f t="shared" si="3"/>
-        <v>9.900000000052386E-3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="98">
         <f t="shared" si="1"/>
@@ -3751,12 +3808,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="150">
+      <c r="L23" s="149">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="M23" s="165"/>
-      <c r="N23" s="149">
+      <c r="M23" s="164"/>
+      <c r="N23" s="148">
         <f t="shared" si="4"/>
         <v>145800.10999999999</v>
       </c>
@@ -3776,7 +3833,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>12</v>
       </c>
@@ -3793,11 +3850,11 @@
         <v>6.6</v>
       </c>
       <c r="F24" s="49">
-        <v>158400.12</v>
-      </c>
-      <c r="G24" s="50">
+        <v>178200.12</v>
+      </c>
+      <c r="G24" s="241">
         <f>F24</f>
-        <v>158400.12</v>
+        <v>178200.12</v>
       </c>
       <c r="H24" s="51">
         <f t="shared" si="0"/>
@@ -3815,12 +3872,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="150">
+      <c r="L24" s="149">
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="M24" s="165"/>
-      <c r="N24" s="149">
+      <c r="M24" s="164"/>
+      <c r="N24" s="148">
         <f t="shared" si="4"/>
         <v>178200.12</v>
       </c>
@@ -3837,7 +3894,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>13</v>
       </c>
@@ -3854,14 +3911,15 @@
         <v>6.6</v>
       </c>
       <c r="F25" s="49">
-        <v>154044.13</v>
-      </c>
-      <c r="G25" s="50">
-        <v>158665.13</v>
+        <v>173579.13</v>
+      </c>
+      <c r="G25" s="241">
+        <f>F25</f>
+        <v>173579.13</v>
       </c>
       <c r="H25" s="51">
         <f t="shared" si="0"/>
-        <v>-4621</v>
+        <v>0</v>
       </c>
       <c r="I25" s="51">
         <f t="shared" si="3"/>
@@ -3875,79 +3933,78 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="150">
+      <c r="L25" s="149">
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="M25" s="165"/>
-      <c r="N25" s="149">
+      <c r="M25" s="164"/>
+      <c r="N25" s="148">
         <f t="shared" si="4"/>
-        <v>173579.13</v>
+        <v>178200.13</v>
       </c>
       <c r="O25" s="52">
         <f t="shared" si="5"/>
-        <v>183994.13</v>
+        <v>188892.13</v>
       </c>
       <c r="P25" s="53">
         <f t="shared" si="6"/>
-        <v>178786.13</v>
+        <v>183546.13</v>
       </c>
       <c r="Q25" s="27">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="142">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="141">
         <v>14</v>
       </c>
-      <c r="B26" s="142" t="s">
+      <c r="B26" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="142" t="s">
+      <c r="C26" s="141" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="143"/>
-      <c r="E26" s="144">
+      <c r="D26" s="142"/>
+      <c r="E26" s="143">
         <v>5.4</v>
       </c>
       <c r="F26" s="50">
-        <v>129600.14</v>
-      </c>
-      <c r="G26" s="50">
-        <f>F26</f>
-        <v>129600.14</v>
-      </c>
-      <c r="H26" s="145">
+        <v>150174.14000000001</v>
+      </c>
+      <c r="G26" s="241">
+        <v>150174.14000000001</v>
+      </c>
+      <c r="H26" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="145">
+      <c r="I26" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="146">
+      <c r="J26" s="145">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K26" s="146">
+      <c r="K26" s="145">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="153">
+      <c r="L26" s="152">
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="M26" s="166"/>
-      <c r="N26" s="149">
+      <c r="M26" s="165"/>
+      <c r="N26" s="148">
         <f t="shared" si="4"/>
         <v>145800.14000000001</v>
       </c>
-      <c r="O26" s="147">
+      <c r="O26" s="146">
         <f t="shared" si="5"/>
         <v>154548.14000000001</v>
       </c>
-      <c r="P26" s="148">
+      <c r="P26" s="147">
         <f t="shared" si="6"/>
         <v>150174.14000000001</v>
       </c>
@@ -3956,7 +4013,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>15</v>
       </c>
@@ -3971,11 +4028,11 @@
         <v>5.4</v>
       </c>
       <c r="F27" s="49">
-        <v>129600.15</v>
-      </c>
-      <c r="G27" s="50">
+        <v>145800.15</v>
+      </c>
+      <c r="G27" s="241">
         <f>F27</f>
-        <v>129600.15</v>
+        <v>145800.15</v>
       </c>
       <c r="H27" s="51">
         <f t="shared" si="0"/>
@@ -3993,12 +4050,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="150">
+      <c r="L27" s="149">
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="M27" s="165"/>
-      <c r="N27" s="149">
+      <c r="M27" s="164"/>
+      <c r="N27" s="148">
         <f t="shared" si="4"/>
         <v>145800.15</v>
       </c>
@@ -4015,14 +4072,14 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="142">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="141">
         <v>16</v>
       </c>
-      <c r="B28" s="142" t="s">
+      <c r="B28" s="141" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="142" t="s">
+      <c r="C28" s="141" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="40" t="s">
@@ -4032,18 +4089,18 @@
         <v>0.7</v>
       </c>
       <c r="F28" s="49">
+        <v>20609.16</v>
+      </c>
+      <c r="G28" s="241">
         <v>16800.16</v>
-      </c>
-      <c r="G28" s="50">
-        <v>15400</v>
       </c>
       <c r="H28" s="51">
         <f t="shared" si="0"/>
-        <v>1400.1599999999999</v>
+        <v>3809</v>
       </c>
       <c r="I28" s="51">
         <f t="shared" si="3"/>
-        <v>42.004799999999996</v>
+        <v>114.27</v>
       </c>
       <c r="J28" s="98">
         <f t="shared" si="1"/>
@@ -4053,36 +4110,36 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="150">
+      <c r="L28" s="149">
         <f>EDESUR!I22</f>
         <v>266.88</v>
       </c>
-      <c r="M28" s="165"/>
-      <c r="N28" s="149">
+      <c r="M28" s="164"/>
+      <c r="N28" s="148">
         <f t="shared" si="4"/>
-        <v>20609.16</v>
+        <v>23090.16</v>
       </c>
       <c r="O28" s="52">
         <f t="shared" si="5"/>
-        <v>21846.16</v>
+        <v>24476.16</v>
       </c>
       <c r="P28" s="53">
         <f t="shared" si="6"/>
-        <v>21227.16</v>
+        <v>23783.16</v>
       </c>
       <c r="Q28" s="27">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="142">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="141">
         <v>17</v>
       </c>
-      <c r="B29" s="142" t="s">
+      <c r="B29" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="142" t="s">
+      <c r="C29" s="141" t="s">
         <v>28</v>
       </c>
       <c r="D29" s="41"/>
@@ -4090,11 +4147,11 @@
         <v>0.6</v>
       </c>
       <c r="F29" s="50">
-        <v>1200.17</v>
-      </c>
-      <c r="G29" s="50">
+        <v>16429.169999999998</v>
+      </c>
+      <c r="G29" s="241">
         <f>F29</f>
-        <v>1200.17</v>
+        <v>16429.169999999998</v>
       </c>
       <c r="H29" s="51">
         <f t="shared" si="0"/>
@@ -4112,12 +4169,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="150">
+      <c r="L29" s="149">
         <f>EDESUR!I23</f>
         <v>228.75</v>
       </c>
-      <c r="M29" s="165"/>
-      <c r="N29" s="149">
+      <c r="M29" s="164"/>
+      <c r="N29" s="148">
         <f t="shared" si="4"/>
         <v>16429.169999999998</v>
       </c>
@@ -4134,7 +4191,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>18</v>
       </c>
@@ -4149,11 +4206,11 @@
         <v>0.6</v>
       </c>
       <c r="F30" s="49">
-        <v>27996.18</v>
-      </c>
-      <c r="G30" s="50">
+        <v>16429.18</v>
+      </c>
+      <c r="G30" s="241">
         <f>F30</f>
-        <v>27996.18</v>
+        <v>16429.18</v>
       </c>
       <c r="H30" s="51">
         <f t="shared" si="0"/>
@@ -4171,12 +4228,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="150">
+      <c r="L30" s="149">
         <f>EDESUR!I24</f>
         <v>228.75</v>
       </c>
-      <c r="M30" s="165"/>
-      <c r="N30" s="149">
+      <c r="M30" s="164"/>
+      <c r="N30" s="148">
         <f t="shared" si="4"/>
         <v>16429.18</v>
       </c>
@@ -4193,54 +4250,54 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="142">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="141">
         <v>19</v>
       </c>
-      <c r="B31" s="142" t="s">
+      <c r="B31" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="142" t="s">
+      <c r="C31" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="143"/>
-      <c r="E31" s="144">
+      <c r="D31" s="142"/>
+      <c r="E31" s="143">
         <v>0.6</v>
       </c>
       <c r="F31" s="50">
-        <v>14400.19</v>
-      </c>
-      <c r="G31" s="50">
+        <v>16429.189999999999</v>
+      </c>
+      <c r="G31" s="241">
         <f>F31</f>
-        <v>14400.19</v>
-      </c>
-      <c r="H31" s="145">
+        <v>16429.189999999999</v>
+      </c>
+      <c r="H31" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="145">
+      <c r="I31" s="144">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="146">
+      <c r="J31" s="145">
         <f t="shared" si="1"/>
         <v>16200</v>
       </c>
-      <c r="K31" s="146">
+      <c r="K31" s="145">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="153">
+      <c r="L31" s="152">
         <f>EDESUR!I25</f>
         <v>228.75</v>
       </c>
-      <c r="M31" s="166"/>
-      <c r="N31" s="149">
+      <c r="M31" s="165"/>
+      <c r="N31" s="148">
         <f t="shared" si="4"/>
         <v>16429.189999999999</v>
       </c>
-      <c r="O31" s="147"/>
-      <c r="P31" s="148">
+      <c r="O31" s="146"/>
+      <c r="P31" s="147">
         <f t="shared" si="6"/>
         <v>16922.189999999999</v>
       </c>
@@ -4249,7 +4306,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A32" s="54">
         <v>20</v>
       </c>
@@ -4266,11 +4323,11 @@
         <v>0.6</v>
       </c>
       <c r="F32" s="56">
-        <v>14400.2</v>
-      </c>
-      <c r="G32" s="50">
+        <v>16429.2</v>
+      </c>
+      <c r="G32" s="241">
         <f>F32</f>
-        <v>14400.2</v>
+        <v>16429.2</v>
       </c>
       <c r="H32" s="51">
         <f t="shared" si="0"/>
@@ -4288,12 +4345,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="150">
+      <c r="L32" s="149">
         <f>EDESUR!I26</f>
         <v>228.75</v>
       </c>
-      <c r="M32" s="165"/>
-      <c r="N32" s="149">
+      <c r="M32" s="164"/>
+      <c r="N32" s="148">
         <f t="shared" si="4"/>
         <v>16429.2</v>
       </c>
@@ -4307,7 +4364,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="54">
         <v>21</v>
       </c>
@@ -4324,11 +4381,11 @@
         <v>0.3</v>
       </c>
       <c r="F33" s="56">
-        <v>7002.21</v>
-      </c>
-      <c r="G33" s="50">
+        <v>8214.2099999999991</v>
+      </c>
+      <c r="G33" s="241">
         <f>F33</f>
-        <v>7002.21</v>
+        <v>8214.2099999999991</v>
       </c>
       <c r="H33" s="51">
         <f t="shared" si="0"/>
@@ -4346,12 +4403,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="150">
+      <c r="L33" s="149">
         <f>EDESUR!I27</f>
         <v>114.38</v>
       </c>
-      <c r="M33" s="165"/>
-      <c r="N33" s="149">
+      <c r="M33" s="164"/>
+      <c r="N33" s="148">
         <f t="shared" si="4"/>
         <v>8214.2099999999991</v>
       </c>
@@ -4365,7 +4422,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="55">
         <v>22</v>
       </c>
@@ -4380,11 +4437,11 @@
         <v>0.3</v>
       </c>
       <c r="F34" s="56">
-        <v>7200.22</v>
-      </c>
-      <c r="G34" s="141">
+        <v>8214.2199999999993</v>
+      </c>
+      <c r="G34" s="242">
         <f t="shared" ref="G34" si="9">F34</f>
-        <v>7200.22</v>
+        <v>8214.2199999999993</v>
       </c>
       <c r="H34" s="51">
         <f t="shared" si="0"/>
@@ -4402,12 +4459,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="150">
+      <c r="L34" s="149">
         <f>EDESUR!I28</f>
         <v>114.38</v>
       </c>
-      <c r="M34" s="165"/>
-      <c r="N34" s="149">
+      <c r="M34" s="164"/>
+      <c r="N34" s="148">
         <f t="shared" si="4"/>
         <v>8214.2199999999993</v>
       </c>
@@ -4421,7 +4478,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>23</v>
       </c>
@@ -4438,11 +4495,11 @@
         <v>0.3</v>
       </c>
       <c r="F35" s="56">
-        <v>7200.23</v>
-      </c>
-      <c r="G35" s="50">
+        <v>8214.23</v>
+      </c>
+      <c r="G35" s="241">
         <f>F35</f>
-        <v>7200.23</v>
+        <v>8214.23</v>
       </c>
       <c r="H35" s="51">
         <f t="shared" si="0"/>
@@ -4460,12 +4517,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="150">
+      <c r="L35" s="149">
         <f>EDESUR!I29</f>
         <v>114.38</v>
       </c>
-      <c r="M35" s="165"/>
-      <c r="N35" s="149">
+      <c r="M35" s="164"/>
+      <c r="N35" s="148">
         <f t="shared" si="4"/>
         <v>8214.23</v>
       </c>
@@ -4479,7 +4536,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="59"/>
       <c r="B36" s="59"/>
       <c r="C36" s="60"/>
@@ -4490,19 +4547,19 @@
       </c>
       <c r="F36" s="34">
         <f>SUM(F13:F35)</f>
-        <v>2340972.7600000012</v>
+        <v>2902950.7600000012</v>
       </c>
       <c r="G36" s="38">
         <f>SUM(G13:G35)</f>
-        <v>2367966.9600000004</v>
+        <v>2788870.3600000008</v>
       </c>
       <c r="H36" s="38">
         <f>SUM(H13:H35)</f>
-        <v>-26994.2</v>
+        <v>114080.4</v>
       </c>
       <c r="I36" s="38">
         <f t="shared" ref="I36:O36" si="10">SUM(I13:I35)</f>
-        <v>4254.0290999999988</v>
+        <v>8176.9524000000001</v>
       </c>
       <c r="J36" s="87">
         <f t="shared" si="10"/>
@@ -4519,117 +4576,111 @@
       <c r="M36" s="61"/>
       <c r="N36" s="61">
         <f>SUM(N13:N35)</f>
-        <v>2898576.7600000012</v>
+        <v>3043574.7600000007</v>
       </c>
       <c r="O36" s="61">
         <f t="shared" si="10"/>
-        <v>3011541.7100000004</v>
+        <v>3165239.7100000004</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P13:P35)</f>
-        <v>2985533.7600000012</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3134881.7600000007</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="33"/>
       <c r="D37" s="33"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="177" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="197" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="177"/>
-      <c r="E39" s="177"/>
-      <c r="F39" s="177"/>
-      <c r="G39" s="177"/>
-      <c r="H39" s="177"/>
-      <c r="I39" s="177"/>
-      <c r="J39" s="177"/>
-      <c r="K39" s="177"/>
-      <c r="L39" s="177"/>
-      <c r="M39" s="177"/>
-      <c r="N39" s="177"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="177"/>
-      <c r="D40" s="177"/>
-      <c r="E40" s="177"/>
-      <c r="F40" s="177"/>
-      <c r="G40" s="177"/>
-      <c r="H40" s="177"/>
-      <c r="I40" s="177"/>
-      <c r="J40" s="177"/>
-      <c r="K40" s="177"/>
-      <c r="L40" s="177"/>
-      <c r="M40" s="177"/>
-      <c r="N40" s="177"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="177"/>
-      <c r="D41" s="177"/>
-      <c r="E41" s="177"/>
-      <c r="F41" s="177"/>
-      <c r="G41" s="177"/>
-      <c r="H41" s="177"/>
-      <c r="I41" s="177"/>
-      <c r="J41" s="177"/>
-      <c r="K41" s="177"/>
-      <c r="L41" s="177"/>
-      <c r="M41" s="177"/>
-      <c r="N41" s="177"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="177"/>
-      <c r="D42" s="177"/>
-      <c r="E42" s="177"/>
-      <c r="F42" s="177"/>
-      <c r="G42" s="177"/>
-      <c r="H42" s="177"/>
-      <c r="I42" s="177"/>
-      <c r="J42" s="177"/>
-      <c r="K42" s="177"/>
-      <c r="L42" s="177"/>
-      <c r="M42" s="177"/>
-      <c r="N42" s="177"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="177"/>
-      <c r="D43" s="177"/>
-      <c r="E43" s="177"/>
-      <c r="F43" s="177"/>
-      <c r="G43" s="177"/>
-      <c r="H43" s="177"/>
-      <c r="I43" s="177"/>
-      <c r="J43" s="177"/>
-      <c r="K43" s="177"/>
-      <c r="L43" s="177"/>
-      <c r="M43" s="177"/>
-      <c r="N43" s="177"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="177"/>
-      <c r="D44" s="177"/>
-      <c r="E44" s="177"/>
-      <c r="F44" s="177"/>
-      <c r="G44" s="177"/>
-      <c r="H44" s="177"/>
-      <c r="I44" s="177"/>
-      <c r="J44" s="177"/>
-      <c r="K44" s="177"/>
-      <c r="L44" s="177"/>
-      <c r="M44" s="177"/>
-      <c r="N44" s="177"/>
+      <c r="D39" s="197"/>
+      <c r="E39" s="197"/>
+      <c r="F39" s="197"/>
+      <c r="G39" s="197"/>
+      <c r="H39" s="197"/>
+      <c r="I39" s="197"/>
+      <c r="J39" s="197"/>
+      <c r="K39" s="197"/>
+      <c r="L39" s="197"/>
+      <c r="M39" s="197"/>
+      <c r="N39" s="197"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="197"/>
+      <c r="D40" s="197"/>
+      <c r="E40" s="197"/>
+      <c r="F40" s="197"/>
+      <c r="G40" s="197"/>
+      <c r="H40" s="197"/>
+      <c r="I40" s="197"/>
+      <c r="J40" s="197"/>
+      <c r="K40" s="197"/>
+      <c r="L40" s="197"/>
+      <c r="M40" s="197"/>
+      <c r="N40" s="197"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="197"/>
+      <c r="D41" s="197"/>
+      <c r="E41" s="197"/>
+      <c r="F41" s="197"/>
+      <c r="G41" s="197"/>
+      <c r="H41" s="197"/>
+      <c r="I41" s="197"/>
+      <c r="J41" s="197"/>
+      <c r="K41" s="197"/>
+      <c r="L41" s="197"/>
+      <c r="M41" s="197"/>
+      <c r="N41" s="197"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="197"/>
+      <c r="D42" s="197"/>
+      <c r="E42" s="197"/>
+      <c r="F42" s="197"/>
+      <c r="G42" s="197"/>
+      <c r="H42" s="197"/>
+      <c r="I42" s="197"/>
+      <c r="J42" s="197"/>
+      <c r="K42" s="197"/>
+      <c r="L42" s="197"/>
+      <c r="M42" s="197"/>
+      <c r="N42" s="197"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="197"/>
+      <c r="D43" s="197"/>
+      <c r="E43" s="197"/>
+      <c r="F43" s="197"/>
+      <c r="G43" s="197"/>
+      <c r="H43" s="197"/>
+      <c r="I43" s="197"/>
+      <c r="J43" s="197"/>
+      <c r="K43" s="197"/>
+      <c r="L43" s="197"/>
+      <c r="M43" s="197"/>
+      <c r="N43" s="197"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="197"/>
+      <c r="D44" s="197"/>
+      <c r="E44" s="197"/>
+      <c r="F44" s="197"/>
+      <c r="G44" s="197"/>
+      <c r="H44" s="197"/>
+      <c r="I44" s="197"/>
+      <c r="J44" s="197"/>
+      <c r="K44" s="197"/>
+      <c r="L44" s="197"/>
+      <c r="M44" s="197"/>
+      <c r="N44" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4643,6 +4694,12 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4652,17 +4709,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
-    <col min="6" max="6" width="4.5546875" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="109" t="s">
         <v>80</v>
       </c>
@@ -4675,346 +4732,346 @@
       <c r="G3" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="207" t="s">
+      <c r="I3" s="238" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="208"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="239"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="109"/>
       <c r="C4" s="109"/>
       <c r="E4" s="109"/>
       <c r="G4" s="112"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="208"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I4" s="238"/>
+      <c r="J4" s="239"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="109">
         <v>1</v>
       </c>
       <c r="C5" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="167">
+      <c r="E5" s="166">
         <v>8123.99</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="168">
+      <c r="G5" s="167">
         <f>E5</f>
         <v>8123.99</v>
       </c>
-      <c r="I5" s="205">
+      <c r="I5" s="236">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="206"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="237"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="109">
         <v>1</v>
       </c>
       <c r="C6" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="167">
+      <c r="E6" s="166">
         <v>102901.79</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="168">
-        <v>0</v>
-      </c>
-      <c r="I6" s="205">
+      <c r="G6" s="167">
+        <v>0</v>
+      </c>
+      <c r="I6" s="236">
         <f t="shared" ref="I6:I19" si="0">E6-G6</f>
         <v>102901.79</v>
       </c>
-      <c r="J6" s="206"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="237"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="109">
         <v>1</v>
       </c>
       <c r="C7" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="167">
+      <c r="E7" s="166">
         <v>3655.79</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="168">
-        <v>0</v>
-      </c>
-      <c r="I7" s="205">
+      <c r="G7" s="167">
+        <v>0</v>
+      </c>
+      <c r="I7" s="236">
         <f t="shared" si="0"/>
         <v>3655.79</v>
       </c>
-      <c r="J7" s="206"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J7" s="237"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="109">
         <v>2</v>
       </c>
       <c r="C8" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="167">
+      <c r="E8" s="166">
         <v>3655.79</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="168">
+      <c r="G8" s="167">
         <f>E8</f>
         <v>3655.79</v>
       </c>
-      <c r="I8" s="205">
+      <c r="I8" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="206"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J8" s="237"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="110">
         <v>2</v>
       </c>
       <c r="C9" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="167">
+      <c r="E9" s="166">
         <v>4468.1899999999996</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="168">
+      <c r="G9" s="167">
         <f>E9</f>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I9" s="205">
+      <c r="I9" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="206"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J9" s="237"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="110">
         <v>2</v>
       </c>
       <c r="C10" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="167">
+      <c r="E10" s="166">
         <v>4468.1899999999996</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="168">
+      <c r="G10" s="167">
         <f>E10</f>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I10" s="205">
+      <c r="I10" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="206"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J10" s="237"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="110">
         <v>2</v>
       </c>
       <c r="C11" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="167">
+      <c r="E11" s="166">
         <v>3655.79</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="168">
+      <c r="G11" s="167">
         <f>E11</f>
         <v>3655.79</v>
       </c>
-      <c r="I11" s="205">
+      <c r="I11" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="206"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J11" s="237"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="110">
         <v>3</v>
       </c>
       <c r="C12" s="110" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="167">
+      <c r="E12" s="166">
         <v>3655.79</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="168">
+      <c r="G12" s="167">
         <f>E12</f>
         <v>3655.79</v>
       </c>
-      <c r="I12" s="205">
+      <c r="I12" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="206"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J12" s="237"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="109">
         <v>3</v>
       </c>
       <c r="C13" s="109" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="167">
+      <c r="E13" s="166">
         <v>63231.57</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="168">
-        <v>0</v>
-      </c>
-      <c r="I13" s="205">
+      <c r="G13" s="167">
+        <v>0</v>
+      </c>
+      <c r="I13" s="236">
         <f t="shared" si="0"/>
         <v>63231.57</v>
       </c>
-      <c r="J13" s="206"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J13" s="237"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="110">
         <v>3</v>
       </c>
       <c r="C14" s="110" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="167">
+      <c r="E14" s="166">
         <f>E10</f>
         <v>4468.1899999999996</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="168">
+      <c r="G14" s="167">
         <f t="shared" ref="G14:G19" si="1">E14</f>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I14" s="205">
+      <c r="I14" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="206"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J14" s="237"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="110">
         <v>3</v>
       </c>
       <c r="C15" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="167">
+      <c r="E15" s="166">
         <f>E12</f>
         <v>3655.79</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="168">
+      <c r="G15" s="167">
         <f t="shared" si="1"/>
         <v>3655.79</v>
       </c>
-      <c r="I15" s="205">
+      <c r="I15" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="206"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J15" s="237"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="109">
         <v>4</v>
       </c>
       <c r="C16" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="167">
+      <c r="E16" s="166">
         <f>E15</f>
         <v>3655.79</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="168">
+      <c r="G16" s="167">
         <f t="shared" si="1"/>
         <v>3655.79</v>
       </c>
-      <c r="I16" s="205">
+      <c r="I16" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="206"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J16" s="237"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="110">
         <v>4</v>
       </c>
       <c r="C17" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="167">
+      <c r="E17" s="166">
         <f>E14</f>
         <v>4468.1899999999996</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="168">
+      <c r="G17" s="167">
         <f t="shared" si="1"/>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I17" s="205">
+      <c r="I17" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="206"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J17" s="237"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="109">
         <v>4</v>
       </c>
       <c r="C18" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="167">
+      <c r="E18" s="166">
         <f>E17</f>
         <v>4468.1899999999996</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="168">
+      <c r="G18" s="167">
         <f t="shared" si="1"/>
         <v>4468.1899999999996</v>
       </c>
-      <c r="I18" s="205">
+      <c r="I18" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="206"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J18" s="237"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="110">
         <v>4</v>
       </c>
       <c r="C19" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="167">
+      <c r="E19" s="166">
         <f>E16</f>
         <v>3655.79</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="168">
+      <c r="G19" s="167">
         <f t="shared" si="1"/>
         <v>3655.79</v>
       </c>
-      <c r="I19" s="205">
+      <c r="I19" s="236">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="206"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J19" s="237"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="109"/>
       <c r="C20" s="109"/>
       <c r="E20" s="109"/>
       <c r="G20" s="112"/>
-      <c r="I20" s="205"/>
-      <c r="J20" s="206"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I20" s="236"/>
+      <c r="J20" s="237"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="133" t="s">
         <v>120</v>
       </c>
@@ -5029,170 +5086,170 @@
         <f>SUM(G5:G20)</f>
         <v>52399.68</v>
       </c>
-      <c r="I21" s="205">
+      <c r="I21" s="236">
         <f>E21-G21</f>
         <v>169789.15000000002</v>
       </c>
-      <c r="J21" s="206"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J21" s="237"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="109" t="s">
         <v>86</v>
       </c>
       <c r="C22" s="109">
         <v>1</v>
       </c>
-      <c r="E22" s="169">
+      <c r="E22" s="168">
         <v>473.9</v>
       </c>
       <c r="G22" s="117">
         <v>207.02</v>
       </c>
-      <c r="I22" s="205">
+      <c r="I22" s="236">
         <f t="shared" ref="I22" si="2">E22-G22</f>
         <v>266.88</v>
       </c>
-      <c r="J22" s="206"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J22" s="237"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="109" t="s">
         <v>86</v>
       </c>
       <c r="C23" s="109">
         <v>2</v>
       </c>
-      <c r="E23" s="169">
+      <c r="E23" s="168">
         <v>406.2</v>
       </c>
       <c r="G23" s="117">
         <v>177.45</v>
       </c>
-      <c r="I23" s="205">
+      <c r="I23" s="236">
         <f t="shared" ref="I23:I31" si="3">E23-G23</f>
         <v>228.75</v>
       </c>
-      <c r="J23" s="206"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J23" s="237"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="109" t="s">
         <v>86</v>
       </c>
       <c r="C24" s="109">
         <v>3</v>
       </c>
-      <c r="E24" s="169">
+      <c r="E24" s="168">
         <f>E23</f>
         <v>406.2</v>
       </c>
       <c r="G24" s="117">
         <v>177.45</v>
       </c>
-      <c r="I24" s="205">
+      <c r="I24" s="236">
         <f t="shared" si="3"/>
         <v>228.75</v>
       </c>
-      <c r="J24" s="206"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J24" s="237"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="109" t="s">
         <v>86</v>
       </c>
       <c r="C25" s="109">
         <v>4</v>
       </c>
-      <c r="E25" s="169">
+      <c r="E25" s="168">
         <f>E24</f>
         <v>406.2</v>
       </c>
       <c r="G25" s="117">
         <v>177.45</v>
       </c>
-      <c r="I25" s="205">
+      <c r="I25" s="236">
         <f t="shared" si="3"/>
         <v>228.75</v>
       </c>
-      <c r="J25" s="206"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J25" s="237"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="109" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="109">
         <v>5</v>
       </c>
-      <c r="E26" s="169">
+      <c r="E26" s="168">
         <f>E25</f>
         <v>406.2</v>
       </c>
       <c r="G26" s="117">
         <v>177.45</v>
       </c>
-      <c r="I26" s="205">
+      <c r="I26" s="236">
         <f t="shared" si="3"/>
         <v>228.75</v>
       </c>
-      <c r="J26" s="206"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J26" s="237"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="109" t="s">
         <v>86</v>
       </c>
       <c r="C27" s="109">
         <v>6</v>
       </c>
-      <c r="E27" s="169">
+      <c r="E27" s="168">
         <v>203.1</v>
       </c>
       <c r="G27" s="117">
         <v>88.72</v>
       </c>
-      <c r="I27" s="205">
+      <c r="I27" s="236">
         <f t="shared" si="3"/>
         <v>114.38</v>
       </c>
-      <c r="J27" s="206"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J27" s="237"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="109" t="s">
         <v>86</v>
       </c>
       <c r="C28" s="109">
         <v>7</v>
       </c>
-      <c r="E28" s="169">
+      <c r="E28" s="168">
         <f>E27</f>
         <v>203.1</v>
       </c>
       <c r="G28" s="117">
         <v>88.72</v>
       </c>
-      <c r="I28" s="205">
+      <c r="I28" s="236">
         <f t="shared" si="3"/>
         <v>114.38</v>
       </c>
-      <c r="J28" s="206"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J28" s="237"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="109" t="s">
         <v>86</v>
       </c>
       <c r="C29" s="109">
         <v>8</v>
       </c>
-      <c r="E29" s="169">
+      <c r="E29" s="168">
         <f>E28</f>
         <v>203.1</v>
       </c>
       <c r="G29" s="117">
         <v>88.72</v>
       </c>
-      <c r="I29" s="205">
+      <c r="I29" s="236">
         <f t="shared" si="3"/>
         <v>114.38</v>
       </c>
-      <c r="J29" s="206"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J29" s="237"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="138" t="s">
         <v>120</v>
       </c>
@@ -5207,28 +5264,28 @@
         <f>SUM(G22:G29)</f>
         <v>1182.9800000000002</v>
       </c>
-      <c r="I30" s="205">
+      <c r="I30" s="236">
         <f t="shared" si="3"/>
         <v>1525.0199999999993</v>
       </c>
-      <c r="J30" s="206"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J30" s="237"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E31" s="116"/>
       <c r="G31" s="113"/>
-      <c r="I31" s="205">
+      <c r="I31" s="236">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="206"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="J31" s="237"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E32" s="114"/>
       <c r="G32" s="115"/>
-      <c r="I32" s="205"/>
-      <c r="J32" s="206"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="I32" s="236"/>
+      <c r="J32" s="237"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
       <c r="E33" s="116">
         <f>E30+E21</f>
         <v>224896.83000000002</v>
@@ -5237,29 +5294,14 @@
         <f>G21+G30</f>
         <v>53582.66</v>
       </c>
-      <c r="I33" s="205">
+      <c r="I33" s="236">
         <f>E33-G33</f>
         <v>171314.17</v>
       </c>
-      <c r="J33" s="206"/>
+      <c r="J33" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5276,6 +5318,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
@@ -5285,7 +5342,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/SALTA 1167/Julio/SALTA1167-Julio.xlsx
+++ b/2026/SALTA 1167/Julio/SALTA1167-Julio.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3F5D8D-B0A2-481E-9293-2A49DC7A2A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2247283-1D06-4607-9DAB-4B27BB113B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
-    <sheet name="EDESUR" sheetId="3" r:id="rId3"/>
-    <sheet name="Anotaciones" sheetId="4" r:id="rId4"/>
+    <sheet name="Anotaciones" sheetId="4" r:id="rId3"/>
+    <sheet name="EDESUR" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$99</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$97</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="161">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -111,9 +110,6 @@
   </si>
   <si>
     <t>Pagos sin identificar</t>
-  </si>
-  <si>
-    <t>Mantenimiento de cuenta</t>
   </si>
   <si>
     <t>1  A</t>
@@ -298,12 +294,6 @@
     <t>Cochera</t>
   </si>
   <si>
-    <t>Total Edesur x Depto</t>
-  </si>
-  <si>
-    <t>SALDO a PAGAR</t>
-  </si>
-  <si>
     <t>Daniel Leiva</t>
   </si>
   <si>
@@ -395,9 +385,6 @@
   </si>
   <si>
     <t>QUIENES ESTAN EN VIOLETA NO ESTAN RESPETANDO LOS CENTAVOS AL ABONAR.</t>
-  </si>
-  <si>
-    <t>Totales</t>
   </si>
   <si>
     <t>Federacion patronal  Seguro obligatorio de consorcio - Poliza nro. 1-2249124-0</t>
@@ -420,27 +407,12 @@
     <t>CONSORCIO DE PROPIETARIOS DEL EDIFICIO CALLE SALTA 1167</t>
   </si>
   <si>
-    <t xml:space="preserve">Bonificado x EDESUR </t>
-  </si>
-  <si>
     <t>SUM</t>
   </si>
   <si>
     <t>FCI FIMA</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso 05/05 </t>
-  </si>
-  <si>
-    <t>Transf 05/06</t>
-  </si>
-  <si>
-    <t>Transf 30/06</t>
-  </si>
-  <si>
-    <t>Comision cuenta dolares - Reclamo enviado - El banco evaluara una bonificacion</t>
-  </si>
-  <si>
     <t>SALDO A FIN DE MES</t>
   </si>
   <si>
@@ -453,9 +425,6 @@
     <t xml:space="preserve">Honorario administracion - Mes de JULIO </t>
   </si>
   <si>
-    <t>Matafuegos Fire - Recarga de matefuegos</t>
-  </si>
-  <si>
     <t>Transf 10/07</t>
   </si>
   <si>
@@ -471,9 +440,6 @@
     <t>Transf 23/07</t>
   </si>
   <si>
-    <t>Grupo protect - Compra de matafuegos - Cuota 1/3</t>
-  </si>
-  <si>
     <t>Easy Barracas - Compra de termotanque - Cuota 5  - Resta 1 cuotas de $157.988,29</t>
   </si>
   <si>
@@ -481,13 +447,85 @@
   </si>
   <si>
     <t>Compra de pilas - Puerta SUM</t>
+  </si>
+  <si>
+    <t>Transf 30/07</t>
+  </si>
+  <si>
+    <t>Mantenimiento de cuenta - Bonificacion bancaria</t>
+  </si>
+  <si>
+    <t>Saldo al 01/07</t>
+  </si>
+  <si>
+    <t>Megasec - Compra de matafuegos - Cuota 1/2</t>
+  </si>
+  <si>
+    <t>GrupoProtect - Compra de matafuego</t>
+  </si>
+  <si>
+    <t>Transf 27/07</t>
+  </si>
+  <si>
+    <t>26/052026</t>
+  </si>
+  <si>
+    <t>25/062026</t>
+  </si>
+  <si>
+    <t>Consumo Kw</t>
+  </si>
+  <si>
+    <t>% Consumido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumo x Dep </t>
+  </si>
+  <si>
+    <t>Cons Esp Com</t>
+  </si>
+  <si>
+    <t>Total x Depto</t>
+  </si>
+  <si>
+    <t>Cons Deptos</t>
+  </si>
+  <si>
+    <t>Cons Coch</t>
+  </si>
+  <si>
+    <t>Total Consumo s/Edesur</t>
+  </si>
+  <si>
+    <t>Total x cons Edesur</t>
+  </si>
+  <si>
+    <t>Total Consumo Medidores</t>
+  </si>
+  <si>
+    <t>Consumo Esp Comunes</t>
+  </si>
+  <si>
+    <t>Cons Esp Com $</t>
+  </si>
+  <si>
+    <t>TOTAL FACT EDESUR</t>
+  </si>
+  <si>
+    <t>Lecturas EDESUR s/facturas</t>
+  </si>
+  <si>
+    <t>Cons s/EDESUR</t>
+  </si>
+  <si>
+    <t>Lect Med Edesur 01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -498,8 +536,9 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,13 +703,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
@@ -696,8 +728,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1127,12 +1183,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1229,7 +1286,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1274,9 +1330,7 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1295,28 +1349,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1347,20 +1389,6 @@
     <xf numFmtId="44" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1379,13 +1407,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1398,29 +1425,16 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1428,17 +1442,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1454,6 +1462,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1463,135 +1495,208 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="26" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="26" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1985,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2003,7 +2108,7 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C1" s="44"/>
       <c r="D1" s="44"/>
@@ -2020,12 +2125,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
-      <c r="B3" s="206" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="206"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="207"/>
+      <c r="B3" s="176" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="177"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -2040,10 +2145,10 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="46" t="s">
@@ -2053,59 +2158,59 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E6" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="209" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="209"/>
+      <c r="B8" s="179" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="179"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
+      <c r="B9" s="179"/>
+      <c r="C9" s="179"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="209"/>
-      <c r="C10" s="209"/>
+      <c r="B10" s="179"/>
+      <c r="C10" s="179"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="208" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="208"/>
-      <c r="C13" s="208"/>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
+      <c r="A13" s="178" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="178"/>
+      <c r="C13" s="178"/>
+      <c r="D13" s="178"/>
+      <c r="E13" s="178"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="208"/>
-      <c r="B14" s="208"/>
-      <c r="C14" s="208"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
+      <c r="A14" s="178"/>
+      <c r="B14" s="178"/>
+      <c r="C14" s="178"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="178"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="208"/>
-      <c r="B15" s="208"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="208"/>
-      <c r="E15" s="208"/>
+      <c r="A15" s="178"/>
+      <c r="B15" s="178"/>
+      <c r="C15" s="178"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="208"/>
-      <c r="B16" s="208"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
+      <c r="A16" s="178"/>
+      <c r="B16" s="178"/>
+      <c r="C16" s="178"/>
+      <c r="D16" s="178"/>
+      <c r="E16" s="178"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2114,7 +2219,7 @@
     <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="10"/>
@@ -2123,728 +2228,724 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="100"/>
-      <c r="E21" s="94"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="93"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="200" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="201"/>
-      <c r="C22" s="172"/>
-      <c r="D22" s="170">
+      <c r="A22" s="174" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="175"/>
+      <c r="C22" s="152"/>
+      <c r="D22" s="209">
         <v>510846.85</v>
       </c>
-      <c r="E22" s="162" t="s">
-        <v>140</v>
-      </c>
-      <c r="H22" s="83"/>
+      <c r="E22" s="146" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" s="82"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="200"/>
-      <c r="B23" s="201"/>
-      <c r="C23" s="172"/>
-      <c r="D23" s="173"/>
-      <c r="E23" s="95"/>
-      <c r="H23" s="83"/>
+      <c r="A23" s="174"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="209"/>
+      <c r="E23" s="94"/>
+      <c r="H23" s="82"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="174" t="s">
+      <c r="A24" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="174"/>
-      <c r="C24" s="174"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="153">
+      <c r="B24" s="153"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="210"/>
+      <c r="E24" s="137">
         <f>SUM(D22:D23)</f>
         <v>510846.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="175" t="s">
+      <c r="A25" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="174"/>
-      <c r="C25" s="174"/>
-      <c r="D25" s="176"/>
-      <c r="E25" s="154"/>
+      <c r="B25" s="153"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="211"/>
+      <c r="E25" s="138"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="200" t="s">
-        <v>121</v>
-      </c>
-      <c r="B26" s="201"/>
-      <c r="C26" s="177"/>
-      <c r="D26" s="240">
+      <c r="A26" s="174" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="175"/>
+      <c r="C26" s="155"/>
+      <c r="D26" s="212">
         <v>79864</v>
       </c>
-      <c r="E26" s="97" t="s">
-        <v>141</v>
+      <c r="E26" s="96" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="174" t="s">
+      <c r="A27" s="153" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="174"/>
-      <c r="C27" s="174"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="107">
+      <c r="B27" s="153"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="210"/>
+      <c r="E27" s="104">
         <f>SUM(D26:D26)</f>
         <v>79864</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="175" t="s">
+      <c r="A28" s="154" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="178"/>
-      <c r="C28" s="178"/>
-      <c r="D28" s="179"/>
-      <c r="E28" s="155"/>
+      <c r="B28" s="156"/>
+      <c r="C28" s="156"/>
+      <c r="D28" s="213"/>
+      <c r="E28" s="139"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
-      <c r="D29" s="169">
+      <c r="D29" s="214">
         <v>162387.66</v>
       </c>
-      <c r="E29" s="97" t="s">
-        <v>143</v>
+      <c r="E29" s="96" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
-      <c r="D30" s="169">
+      <c r="D30" s="214">
         <v>7090.36</v>
       </c>
-      <c r="E30" s="162" t="str">
+      <c r="E30" s="146" t="str">
         <f>E31</f>
         <v>Transf 06/07</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="180"/>
+        <v>65</v>
+      </c>
+      <c r="B31" s="157"/>
       <c r="C31" s="65"/>
-      <c r="D31" s="169">
+      <c r="D31" s="214">
         <v>482288.43</v>
       </c>
-      <c r="E31" s="97" t="s">
-        <v>141</v>
+      <c r="E31" s="96" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="204" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="205"/>
+      <c r="A32" s="172" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="173"/>
       <c r="C32" s="65"/>
-      <c r="D32" s="169">
+      <c r="D32" s="214">
         <v>632390</v>
       </c>
-      <c r="E32" s="97" t="s">
-        <v>141</v>
+      <c r="E32" s="96" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="181" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="182"/>
+      <c r="A33" s="158" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="159"/>
       <c r="C33" s="65"/>
-      <c r="D33" s="169">
+      <c r="D33" s="214">
         <v>27338.01</v>
       </c>
-      <c r="E33" s="97" t="s">
-        <v>141</v>
+      <c r="E33" s="96" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="174" t="s">
+      <c r="A34" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="174"/>
-      <c r="C34" s="174"/>
-      <c r="D34" s="183"/>
-      <c r="E34" s="156">
+      <c r="B34" s="153"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="215"/>
+      <c r="E34" s="140">
         <f>SUM(D29:D33)</f>
         <v>1311494.46</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="175"/>
-      <c r="B35" s="174"/>
-      <c r="C35" s="174"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="157"/>
+      <c r="A35" s="154"/>
+      <c r="B35" s="153"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="210"/>
+      <c r="E35" s="141"/>
     </row>
     <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="200" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="201"/>
+      <c r="A36" s="174" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="175"/>
       <c r="C36" s="65"/>
-      <c r="D36" s="169">
+      <c r="D36" s="214">
         <v>82000</v>
       </c>
-      <c r="E36" s="97" t="s">
-        <v>139</v>
+      <c r="E36" s="96" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="184" t="s">
-        <v>144</v>
-      </c>
-      <c r="B37" s="185"/>
+      <c r="A37" s="160" t="s">
+        <v>140</v>
+      </c>
+      <c r="B37" s="161"/>
       <c r="C37" s="65"/>
-      <c r="D37" s="169">
+      <c r="D37" s="214">
+        <f>199530</f>
         <v>199530</v>
       </c>
-      <c r="E37" s="97" t="s">
+      <c r="E37" s="96" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="174" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" s="175"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="216">
+        <v>72635</v>
+      </c>
+      <c r="E38" s="96" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="200" t="s">
-        <v>138</v>
-      </c>
-      <c r="B38" s="201"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="171">
-        <v>339060</v>
-      </c>
-      <c r="E38" s="97" t="s">
-        <v>131</v>
-      </c>
-    </row>
     <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="200" t="s">
-        <v>145</v>
-      </c>
-      <c r="B39" s="201"/>
+      <c r="A39" s="174" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="175"/>
       <c r="C39" s="65"/>
-      <c r="D39" s="171">
+      <c r="D39" s="216">
         <v>157988.29</v>
       </c>
-      <c r="E39" s="97"/>
+      <c r="E39" s="96"/>
     </row>
     <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="200" t="s">
-        <v>147</v>
-      </c>
-      <c r="B40" s="201"/>
+      <c r="A40" s="174" t="s">
+        <v>136</v>
+      </c>
+      <c r="B40" s="175"/>
       <c r="C40" s="65"/>
-      <c r="D40" s="171">
+      <c r="D40" s="216">
         <v>8000</v>
       </c>
-      <c r="E40" s="97" t="s">
-        <v>146</v>
+      <c r="E40" s="96" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="174" t="s">
+      <c r="A41" s="153" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="175"/>
-      <c r="C41" s="175"/>
-      <c r="D41" s="175"/>
-      <c r="E41" s="107">
+      <c r="B41" s="154"/>
+      <c r="C41" s="154"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="104">
         <f>SUM(D36:D40)</f>
-        <v>786578.29</v>
+        <v>520153.29000000004</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="175" t="s">
+      <c r="A42" s="154" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="175"/>
-      <c r="C42" s="175"/>
-      <c r="D42" s="100"/>
-      <c r="E42" s="158"/>
+      <c r="B42" s="154"/>
+      <c r="C42" s="154"/>
+      <c r="D42" s="217"/>
+      <c r="E42" s="142"/>
     </row>
     <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="200" t="s">
+      <c r="A43" s="174" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" s="175"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="218">
+        <v>190000</v>
+      </c>
+      <c r="E43" s="143" t="s">
         <v>137</v>
       </c>
-      <c r="B43" s="201"/>
-      <c r="C43" s="172"/>
-      <c r="D43" s="186">
-        <v>170000</v>
-      </c>
-      <c r="E43" s="159" t="s">
-        <v>132</v>
-      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="174" t="s">
+      <c r="A44" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="174"/>
-      <c r="C44" s="174"/>
-      <c r="D44" s="101"/>
-      <c r="E44" s="153">
+      <c r="B44" s="153"/>
+      <c r="C44" s="153"/>
+      <c r="D44" s="210"/>
+      <c r="E44" s="137">
         <f>SUM(D43:D43)</f>
-        <v>170000</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="175" t="s">
+      <c r="A45" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="187"/>
-      <c r="C45" s="174"/>
-      <c r="D45" s="99"/>
-      <c r="E45" s="107"/>
+      <c r="B45" s="162"/>
+      <c r="C45" s="153"/>
+      <c r="D45" s="219"/>
+      <c r="E45" s="104"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="65" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="B46" s="65"/>
       <c r="C46" s="65"/>
-      <c r="D46" s="96">
-        <v>69000</v>
-      </c>
-      <c r="E46" s="160"/>
-    </row>
-    <row r="47" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="202" t="s">
-        <v>133</v>
-      </c>
-      <c r="B47" s="203"/>
+      <c r="D46" s="214">
+        <v>0</v>
+      </c>
+      <c r="E46" s="144"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="65" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" s="65"/>
       <c r="C47" s="65"/>
-      <c r="D47" s="96">
-        <v>14770</v>
-      </c>
-      <c r="E47" s="160"/>
+      <c r="D47" s="214">
+        <v>44926.11</v>
+      </c>
+      <c r="E47" s="145"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="65" t="s">
-        <v>116</v>
-      </c>
-      <c r="B48" s="65"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="96">
-        <v>56522.84</v>
-      </c>
-      <c r="E48" s="161"/>
+      <c r="A48" s="163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="163"/>
+      <c r="C48" s="163"/>
+      <c r="D48" s="220"/>
+      <c r="E48" s="104">
+        <f>SUM(D46:D47)</f>
+        <v>44926.11</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="188" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="188"/>
-      <c r="C49" s="188"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="107">
-        <f>SUM(D46:D48)</f>
-        <v>140292.84</v>
-      </c>
+      <c r="A49" s="65"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="221"/>
+      <c r="E49" s="70"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="65"/>
-      <c r="B50" s="65"/>
-      <c r="C50" s="65"/>
-      <c r="D50" s="65"/>
-      <c r="E50" s="71"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="189" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="189"/>
-      <c r="C51" s="189"/>
+      <c r="A50" s="164" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="164"/>
+      <c r="C50" s="164"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="105"/>
+    </row>
+    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="165"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="72"/>
       <c r="D51" s="72"/>
-      <c r="E51" s="108"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="27"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="190"/>
-      <c r="B52" s="73"/>
-      <c r="C52" s="73"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="27"/>
-    </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="191" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="192"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="75"/>
-      <c r="E53" s="76">
-        <f>(SUM(E21:E51))</f>
-        <v>2999076.44</v>
-      </c>
-      <c r="F53" s="93"/>
-      <c r="G53" s="27"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="73"/>
-      <c r="B54" s="73"/>
-      <c r="C54" s="73"/>
-      <c r="D54" s="73"/>
-      <c r="E54" s="73"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="73"/>
-      <c r="B55" s="73"/>
-      <c r="C55" s="73"/>
-      <c r="D55" s="73"/>
-      <c r="E55" s="73"/>
-      <c r="H55" s="102"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="193" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="194"/>
-      <c r="C56" s="195"/>
-      <c r="D56" s="77"/>
-      <c r="E56" s="78"/>
+      <c r="A52" s="166" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" s="167"/>
+      <c r="C52" s="74"/>
+      <c r="D52" s="74"/>
+      <c r="E52" s="75">
+        <f>(SUM(E21:E50))</f>
+        <v>2657284.71</v>
+      </c>
+      <c r="F52" s="92"/>
+      <c r="G52" s="27"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="72"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="72"/>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="72"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="72"/>
+      <c r="H54" s="99"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="168" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="169"/>
+      <c r="C55" s="170"/>
+      <c r="D55" s="76"/>
+      <c r="E55" s="77"/>
+    </row>
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="171"/>
+      <c r="B56" s="159"/>
+      <c r="C56" s="65"/>
+      <c r="D56" s="68"/>
+      <c r="E56" s="66"/>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="196"/>
+      <c r="A57" s="182"/>
       <c r="B57" s="182"/>
       <c r="C57" s="65"/>
-      <c r="D57" s="68"/>
+      <c r="D57" s="95"/>
       <c r="E57" s="66"/>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="199"/>
-      <c r="B58" s="199"/>
-      <c r="C58" s="65"/>
-      <c r="D58" s="96"/>
-      <c r="E58" s="66"/>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="67"/>
+      <c r="B59" s="69"/>
       <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
+      <c r="D59" s="68"/>
+      <c r="E59" s="66"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="67"/>
-      <c r="B60" s="69"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="68"/>
-      <c r="E60" s="66"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="32"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36">
-        <f>SUM(D57:D60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="150"/>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="43">
-        <f>E61+E64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36">
+        <f>SUM(D56:D59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="135"/>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B65" s="7"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="43">
+        <f>E60+E63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="B67" s="64">
+        <f>E52</f>
+        <v>2657284.71</v>
+      </c>
+    </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="63" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B68" s="64">
-        <f>E53</f>
-        <v>2999076.44</v>
+        <f>E52-E50</f>
+        <v>2657284.71</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="63" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B69" s="64">
-        <f>E53-E51</f>
-        <v>2999076.44</v>
+        <f>E65-E63</f>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="63" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B70" s="64">
-        <f>E66-E64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="63" t="s">
-        <v>108</v>
-      </c>
-      <c r="B71" s="64">
-        <f>E66</f>
-        <v>0</v>
-      </c>
+        <f>E65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="24"/>
     </row>
     <row r="73" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73" s="26"/>
+      <c r="A73" s="84" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="111">
+        <v>-149034.37999999756</v>
+      </c>
       <c r="C73" s="24"/>
-    </row>
-    <row r="74" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="85" t="s">
-        <v>109</v>
-      </c>
-      <c r="B74" s="118">
-        <v>291888.99000000162</v>
-      </c>
-      <c r="C74" s="24"/>
-      <c r="D74" s="30"/>
+      <c r="D73" s="30"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" s="89">
+        <f>-B68</f>
+        <v>-2657284.71</v>
+      </c>
+      <c r="E74" s="27"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="B75" s="90">
-        <f>-B69</f>
-        <v>-2999076.44</v>
-      </c>
-      <c r="E75" s="27"/>
+        <v>25</v>
+      </c>
+      <c r="B75" s="89">
+        <f>B96</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="B76" s="90">
-        <f>B98</f>
-        <v>0</v>
+        <f>PRORRATEO!G36-B83</f>
+        <v>3037545.4400000009</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="B77" s="91">
-        <f>PRORRATEO!G36-B84</f>
-        <v>2788870.3600000008</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="92" t="s">
+      <c r="A77" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B78" s="103"/>
-    </row>
-    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="88" t="s">
-        <v>113</v>
-      </c>
-      <c r="B79" s="89">
-        <f>SUM(B74:C78)</f>
-        <v>81682.910000002477</v>
-      </c>
+      <c r="B77" s="100"/>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" s="88">
+        <f>SUM(B73:C77)</f>
+        <v>231226.35000000335</v>
+      </c>
+      <c r="D78" s="27"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="85"/>
+      <c r="B79" s="85"/>
       <c r="D79" s="27"/>
+      <c r="E79" s="26"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="86"/>
-      <c r="B80" s="86"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="26"/>
+      <c r="A80" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="111">
+        <v>1000000</v>
+      </c>
+      <c r="D80" s="26"/>
+      <c r="E80" s="27"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="85" t="s">
-        <v>110</v>
-      </c>
-      <c r="B81" s="118">
-        <v>1000000</v>
-      </c>
-      <c r="D81" s="26"/>
+      <c r="A81" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B81" s="89">
+        <f>-B69</f>
+        <v>0</v>
+      </c>
+      <c r="D81" s="27"/>
       <c r="E81" s="27"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="B82" s="90">
-        <f>-B70</f>
+        <v>25</v>
+      </c>
+      <c r="B82" s="89">
+        <f>B104</f>
         <v>0</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="35" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="B83" s="90">
-        <f>B106</f>
-        <v>0</v>
-      </c>
-      <c r="D83" s="27"/>
+        <v>0</v>
+      </c>
+      <c r="D83" s="136"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="B84" s="91">
-        <v>0</v>
-      </c>
-      <c r="D84" s="151"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="92" t="s">
+      <c r="A84" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B85" s="103"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="26"/>
-    </row>
-    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="88" t="s">
-        <v>114</v>
-      </c>
-      <c r="B86" s="89">
-        <f>SUM(B81:C85)</f>
+      <c r="B84" s="100"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="26"/>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="B85" s="88">
+        <f>SUM(B80:C84)</f>
         <v>1000000</v>
       </c>
-      <c r="F86" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="F85" s="27"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="85"/>
+      <c r="B86" s="85"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="86"/>
-      <c r="B87" s="86"/>
+      <c r="A87" s="85"/>
+      <c r="B87" s="85"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="86"/>
-      <c r="B88" s="86"/>
+      <c r="A88" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" s="111">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="85" t="s">
-        <v>129</v>
-      </c>
-      <c r="B89" s="118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="B90" s="90">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="92"/>
-      <c r="B91" s="103"/>
-    </row>
-    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="88" t="s">
-        <v>134</v>
-      </c>
-      <c r="B92" s="89">
+      <c r="A89" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="B89" s="89">
         <v>1025063.51</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="198" t="s">
+    <row r="90" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="87" t="s">
+        <v>125</v>
+      </c>
+      <c r="B90" s="88">
+        <v>1040813.49</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="181" t="s">
         <v>18</v>
       </c>
-      <c r="B94" s="198"/>
-      <c r="C94" s="198"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="198"/>
-      <c r="B95" s="198"/>
-      <c r="C95" s="198"/>
-    </row>
-    <row r="96" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="80"/>
-      <c r="B96" s="23"/>
-      <c r="C96" s="23">
+      <c r="B92" s="181"/>
+      <c r="C92" s="181"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="181"/>
+      <c r="B93" s="181"/>
+      <c r="C93" s="181"/>
+    </row>
+    <row r="94" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="79"/>
+      <c r="B94" s="23"/>
+      <c r="C94" s="23">
         <v>40000</v>
       </c>
-      <c r="E96" s="93"/>
-    </row>
-    <row r="97" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="80"/>
-      <c r="B97" s="82"/>
-      <c r="C97" s="79"/>
-      <c r="D97" s="93"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="28" t="s">
+      <c r="E94" s="92"/>
+    </row>
+    <row r="95" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="79"/>
+      <c r="B95" s="81"/>
+      <c r="C95" s="78"/>
+      <c r="D95" s="92"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B98" s="81">
-        <f>SUM(B96:B97)</f>
-        <v>0</v>
-      </c>
-      <c r="C98" s="29"/>
+      <c r="B96" s="80">
+        <f>SUM(B94:B95)</f>
+        <v>0</v>
+      </c>
+      <c r="C96" s="29"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M97" s="5"/>
+    </row>
+    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="180"/>
+      <c r="B98" s="180"/>
+      <c r="C98" s="180"/>
+      <c r="D98" s="180"/>
+      <c r="E98" s="180"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M99" s="5"/>
-    </row>
-    <row r="100" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="197"/>
-      <c r="B100" s="197"/>
-      <c r="C100" s="197"/>
-      <c r="D100" s="197"/>
-      <c r="E100" s="197"/>
+      <c r="A99" s="180"/>
+      <c r="B99" s="180"/>
+      <c r="C99" s="180"/>
+      <c r="D99" s="180"/>
+      <c r="E99" s="180"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="180"/>
+      <c r="B100" s="180"/>
+      <c r="C100" s="180"/>
+      <c r="D100" s="180"/>
+      <c r="E100" s="180"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="197"/>
-      <c r="B101" s="197"/>
-      <c r="C101" s="197"/>
-      <c r="D101" s="197"/>
-      <c r="E101" s="197"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A102" s="197"/>
-      <c r="B102" s="197"/>
-      <c r="C102" s="197"/>
-      <c r="D102" s="197"/>
-      <c r="E102" s="197"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="197"/>
-      <c r="B103" s="197"/>
-      <c r="C103" s="197"/>
-      <c r="D103" s="197"/>
-      <c r="E103" s="197"/>
+      <c r="A101" s="180"/>
+      <c r="B101" s="180"/>
+      <c r="C101" s="180"/>
+      <c r="D101" s="180"/>
+      <c r="E101" s="180"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
+    <mergeCell ref="A98:E101"/>
+    <mergeCell ref="A92:C93"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A43:B43"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2852,15 +2953,6 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A100:E103"/>
-    <mergeCell ref="A94:C95"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A47:B47"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2894,283 +2986,283 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="119"/>
-      <c r="B1" s="120"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="215"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
-      <c r="I1" s="215"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="215"/>
-      <c r="L1" s="215"/>
-      <c r="M1" s="215"/>
-      <c r="N1" s="215"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="122"/>
+      <c r="A1" s="112"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="115"/>
     </row>
     <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="123"/>
-      <c r="B2" s="124"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126" t="s">
-        <v>95</v>
-      </c>
-      <c r="F2" s="126"/>
-      <c r="G2" s="127">
-        <v>0</v>
-      </c>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="128">
+      <c r="A2" s="116"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="119"/>
+      <c r="G2" s="120">
+        <v>0</v>
+      </c>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="121">
         <v>2700000</v>
       </c>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="131"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="121"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="123"/>
+      <c r="P2" s="124"/>
       <c r="Q2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="123"/>
-      <c r="B3" s="124"/>
-      <c r="C3" s="125"/>
-      <c r="D3" s="125"/>
-      <c r="E3" s="125"/>
-      <c r="F3" s="125"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
-      <c r="K3" s="125"/>
-      <c r="L3" s="125"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="131"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="118"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="118"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="124"/>
       <c r="Q3" s="19"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="222" t="s">
+      <c r="A4" s="194" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="195"/>
+      <c r="C4" s="195"/>
+      <c r="D4" s="195"/>
+      <c r="E4" s="195"/>
+      <c r="F4" s="195"/>
+      <c r="G4" s="195"/>
+      <c r="H4" s="195"/>
+      <c r="I4" s="195"/>
+      <c r="J4" s="195"/>
+      <c r="K4" s="195"/>
+      <c r="L4" s="195"/>
+      <c r="M4" s="195"/>
+      <c r="N4" s="195"/>
+      <c r="O4" s="195"/>
+      <c r="P4" s="196"/>
+      <c r="Q4" s="19"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="197"/>
+      <c r="B5" s="198"/>
+      <c r="C5" s="198"/>
+      <c r="D5" s="198"/>
+      <c r="E5" s="198"/>
+      <c r="F5" s="198"/>
+      <c r="G5" s="198"/>
+      <c r="H5" s="198"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="198"/>
+      <c r="K5" s="198"/>
+      <c r="L5" s="198"/>
+      <c r="M5" s="198"/>
+      <c r="N5" s="198"/>
+      <c r="O5" s="198"/>
+      <c r="P5" s="199"/>
+      <c r="Q5" s="19"/>
+    </row>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="197"/>
+      <c r="B6" s="198"/>
+      <c r="C6" s="198"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="198"/>
+      <c r="G6" s="198"/>
+      <c r="H6" s="198"/>
+      <c r="I6" s="198"/>
+      <c r="J6" s="198"/>
+      <c r="K6" s="198"/>
+      <c r="L6" s="198"/>
+      <c r="M6" s="198"/>
+      <c r="N6" s="198"/>
+      <c r="O6" s="198"/>
+      <c r="P6" s="199"/>
+      <c r="Q6" s="19"/>
+    </row>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="197"/>
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="198"/>
+      <c r="E7" s="198"/>
+      <c r="F7" s="198"/>
+      <c r="G7" s="198"/>
+      <c r="H7" s="198"/>
+      <c r="I7" s="198"/>
+      <c r="J7" s="198"/>
+      <c r="K7" s="198"/>
+      <c r="L7" s="198"/>
+      <c r="M7" s="198"/>
+      <c r="N7" s="198"/>
+      <c r="O7" s="198"/>
+      <c r="P7" s="199"/>
+      <c r="Q7" s="19"/>
+    </row>
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="200"/>
+      <c r="B8" s="201"/>
+      <c r="C8" s="201"/>
+      <c r="D8" s="201"/>
+      <c r="E8" s="201"/>
+      <c r="F8" s="201"/>
+      <c r="G8" s="201"/>
+      <c r="H8" s="201"/>
+      <c r="I8" s="201"/>
+      <c r="J8" s="201"/>
+      <c r="K8" s="201"/>
+      <c r="L8" s="201"/>
+      <c r="M8" s="201"/>
+      <c r="N8" s="201"/>
+      <c r="O8" s="201"/>
+      <c r="P8" s="202"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="205" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="206"/>
+      <c r="C9" s="206"/>
+      <c r="D9" s="206"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="206"/>
+      <c r="G9" s="206"/>
+      <c r="H9" s="206"/>
+      <c r="I9" s="206"/>
+      <c r="J9" s="206"/>
+      <c r="K9" s="206"/>
+      <c r="L9" s="206"/>
+      <c r="M9" s="206"/>
+      <c r="N9" s="206"/>
+      <c r="O9" s="206"/>
+      <c r="P9" s="206"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="207" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="207"/>
+      <c r="C10" s="207"/>
+      <c r="D10" s="207"/>
+      <c r="E10" s="207"/>
+      <c r="F10" s="207"/>
+      <c r="G10" s="207"/>
+      <c r="H10" s="207"/>
+      <c r="I10" s="207"/>
+      <c r="J10" s="207"/>
+      <c r="K10" s="207"/>
+      <c r="L10" s="207"/>
+      <c r="M10" s="207"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
+      <c r="P10" s="207"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="188" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="101"/>
+      <c r="C11" s="188" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="188" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="188" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="184" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="188" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="190" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="184" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="184" t="s">
+        <v>91</v>
+      </c>
+      <c r="K11" s="192" t="s">
+        <v>92</v>
+      </c>
+      <c r="L11" s="184" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11" s="184" t="s">
         <v>123</v>
-      </c>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="224"/>
-      <c r="Q4" s="19"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="225"/>
-      <c r="B5" s="226"/>
-      <c r="C5" s="226"/>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="M5" s="226"/>
-      <c r="N5" s="226"/>
-      <c r="O5" s="226"/>
-      <c r="P5" s="227"/>
-      <c r="Q5" s="19"/>
-    </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="225"/>
-      <c r="B6" s="226"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
-      <c r="H6" s="226"/>
-      <c r="I6" s="226"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="226"/>
-      <c r="L6" s="226"/>
-      <c r="M6" s="226"/>
-      <c r="N6" s="226"/>
-      <c r="O6" s="226"/>
-      <c r="P6" s="227"/>
-      <c r="Q6" s="19"/>
-    </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="225"/>
-      <c r="B7" s="226"/>
-      <c r="C7" s="226"/>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
-      <c r="G7" s="226"/>
-      <c r="H7" s="226"/>
-      <c r="I7" s="226"/>
-      <c r="J7" s="226"/>
-      <c r="K7" s="226"/>
-      <c r="L7" s="226"/>
-      <c r="M7" s="226"/>
-      <c r="N7" s="226"/>
-      <c r="O7" s="226"/>
-      <c r="P7" s="227"/>
-      <c r="Q7" s="19"/>
-    </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="228"/>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="230"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="233" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="234"/>
-      <c r="C9" s="234"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="234"/>
-      <c r="F9" s="234"/>
-      <c r="G9" s="234"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="234"/>
-      <c r="J9" s="234"/>
-      <c r="K9" s="234"/>
-      <c r="L9" s="234"/>
-      <c r="M9" s="234"/>
-      <c r="N9" s="234"/>
-      <c r="O9" s="234"/>
-      <c r="P9" s="234"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="235" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="235"/>
-      <c r="C10" s="235"/>
-      <c r="D10" s="235"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="235"/>
-      <c r="G10" s="235"/>
-      <c r="H10" s="235"/>
-      <c r="I10" s="235"/>
-      <c r="J10" s="235"/>
-      <c r="K10" s="235"/>
-      <c r="L10" s="235"/>
-      <c r="M10" s="235"/>
-      <c r="N10" s="235"/>
-      <c r="O10" s="235"/>
-      <c r="P10" s="235"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="210" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="104"/>
-      <c r="C11" s="210" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="210" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="210" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="213" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="210" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="218" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="213" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="213" t="s">
-        <v>94</v>
-      </c>
-      <c r="K11" s="220" t="s">
-        <v>95</v>
-      </c>
-      <c r="L11" s="213" t="s">
-        <v>79</v>
-      </c>
-      <c r="M11" s="213" t="s">
-        <v>128</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="216" t="s">
+      <c r="O11" s="186" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="231" t="s">
+      <c r="P11" s="203" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="212"/>
-      <c r="B12" s="105"/>
-      <c r="C12" s="212"/>
-      <c r="D12" s="211"/>
-      <c r="E12" s="212"/>
-      <c r="F12" s="214"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="219"/>
-      <c r="I12" s="214"/>
-      <c r="J12" s="214"/>
-      <c r="K12" s="221"/>
-      <c r="L12" s="214"/>
-      <c r="M12" s="214"/>
+      <c r="A12" s="189"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="189"/>
+      <c r="D12" s="208"/>
+      <c r="E12" s="189"/>
+      <c r="F12" s="185"/>
+      <c r="G12" s="189"/>
+      <c r="H12" s="191"/>
+      <c r="I12" s="185"/>
+      <c r="J12" s="185"/>
+      <c r="K12" s="193"/>
+      <c r="L12" s="185"/>
+      <c r="M12" s="185"/>
       <c r="N12" s="37" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="O12" s="217"/>
-      <c r="P12" s="232"/>
+      <c r="O12" s="187"/>
+      <c r="P12" s="204"/>
     </row>
     <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>1</v>
       </c>
       <c r="B13" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="40" t="s">
         <v>27</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>28</v>
       </c>
       <c r="D13" s="40"/>
       <c r="E13" s="48">
@@ -3179,7 +3271,7 @@
       <c r="F13" s="49">
         <v>324000.01</v>
       </c>
-      <c r="G13" s="241">
+      <c r="G13" s="222">
         <f>356868.01-G29-G30</f>
         <v>324009.66000000003</v>
       </c>
@@ -3191,87 +3283,87 @@
         <f>IF(H13&gt;0,H13*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J13" s="98">
+      <c r="J13" s="97">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
         <v>324000</v>
       </c>
-      <c r="K13" s="98">
+      <c r="K13" s="97">
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="149">
-        <f>EDESUR!I5</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="164"/>
-      <c r="N13" s="148">
+      <c r="L13" s="134">
+        <f>EDESUR!K3</f>
+        <v>29460.826927751194</v>
+      </c>
+      <c r="M13" s="148"/>
+      <c r="N13" s="133">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
-        <v>323990.01</v>
+        <v>353451.01</v>
       </c>
       <c r="O13" s="52">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
-        <v>343429.01</v>
+        <v>374658.01</v>
       </c>
       <c r="P13" s="53">
         <f>ROUND(N13*3%,0) + N13</f>
-        <v>333710.01</v>
+        <v>364055.01</v>
       </c>
       <c r="Q13" s="27">
         <v>0.01</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="141">
+      <c r="A14" s="126">
         <v>2</v>
       </c>
-      <c r="B14" s="141" t="s">
+      <c r="B14" s="126" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="141" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="142"/>
-      <c r="E14" s="143">
+      <c r="D14" s="127"/>
+      <c r="E14" s="128">
         <v>6.6</v>
       </c>
       <c r="F14" s="50">
         <v>280517.02</v>
       </c>
-      <c r="G14" s="241">
+      <c r="G14" s="222">
         <v>281000</v>
       </c>
-      <c r="H14" s="144">
+      <c r="H14" s="129">
         <f t="shared" si="0"/>
         <v>-482.97999999998137</v>
       </c>
-      <c r="I14" s="144">
+      <c r="I14" s="129">
         <f t="shared" ref="I14:I35" si="3">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="145">
+      <c r="J14" s="130">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K14" s="145">
+      <c r="K14" s="130">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="152">
-        <f>EDESUR!I6</f>
-        <v>102901.79</v>
-      </c>
-      <c r="M14" s="165"/>
-      <c r="N14" s="148">
+      <c r="L14" s="134">
+        <f>EDESUR!K4</f>
+        <v>149105.45982222489</v>
+      </c>
+      <c r="M14" s="149"/>
+      <c r="N14" s="133">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>280619.02</v>
-      </c>
-      <c r="O14" s="146">
+        <v>326822.02</v>
+      </c>
+      <c r="O14" s="131">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>297456.02</v>
-      </c>
-      <c r="P14" s="147">
+        <v>346431.02</v>
+      </c>
+      <c r="P14" s="132">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>289038.02</v>
+        <v>336627.02</v>
       </c>
       <c r="Q14" s="27">
         <f>Q13+0.01</f>
@@ -3283,13 +3375,13 @@
         <v>3</v>
       </c>
       <c r="B15" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="40" t="s">
-        <v>32</v>
-      </c>
       <c r="D15" s="41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" s="48">
         <v>5.4</v>
@@ -3297,7 +3389,7 @@
       <c r="F15" s="49">
         <v>149456.03</v>
       </c>
-      <c r="G15" s="241">
+      <c r="G15" s="222">
         <f>F15</f>
         <v>149456.03</v>
       </c>
@@ -3309,30 +3401,30 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="98">
+      <c r="J15" s="97">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K15" s="98">
+      <c r="K15" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="149">
-        <f>EDESUR!I7</f>
-        <v>3655.79</v>
-      </c>
-      <c r="M15" s="163"/>
-      <c r="N15" s="148">
+      <c r="L15" s="134">
+        <f>EDESUR!K5</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="M15" s="147"/>
+      <c r="N15" s="133">
         <f t="shared" si="4"/>
-        <v>149456.03</v>
+        <v>159057.03</v>
       </c>
       <c r="O15" s="52">
         <f t="shared" si="5"/>
-        <v>158423.03</v>
+        <v>168600.03</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="6"/>
-        <v>153940.03</v>
+        <v>163829.03</v>
       </c>
       <c r="Q15" s="27">
         <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
@@ -3344,13 +3436,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="40" t="s">
-        <v>34</v>
-      </c>
       <c r="D16" s="41" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E16" s="48">
         <v>6.6</v>
@@ -3358,7 +3450,7 @@
       <c r="F16" s="49">
         <v>172600.04</v>
       </c>
-      <c r="G16" s="241">
+      <c r="G16" s="222">
         <f>189033-G32</f>
         <v>172603.8</v>
       </c>
@@ -3370,30 +3462,30 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J16" s="98">
+      <c r="J16" s="97">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K16" s="98">
+      <c r="K16" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="149">
-        <f>EDESUR!I9</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="164"/>
-      <c r="N16" s="148">
+      <c r="L16" s="134">
+        <f>EDESUR!K7</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="M16" s="148"/>
+      <c r="N16" s="133">
         <f t="shared" si="4"/>
-        <v>178196.04</v>
+        <v>194400.04</v>
       </c>
       <c r="O16" s="52">
         <f t="shared" si="5"/>
-        <v>188888.04</v>
+        <v>206064.04</v>
       </c>
       <c r="P16" s="53">
         <f t="shared" si="6"/>
-        <v>183542.04</v>
+        <v>200232.04</v>
       </c>
       <c r="Q16" s="27">
         <f t="shared" si="7"/>
@@ -3401,69 +3493,69 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="141">
+      <c r="A17" s="126">
         <v>5</v>
       </c>
-      <c r="B17" s="141" t="s">
+      <c r="B17" s="126" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="141" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="141" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="143">
+      <c r="D17" s="126" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="128">
         <v>6.6</v>
       </c>
       <c r="F17" s="50">
         <v>178200.05</v>
       </c>
-      <c r="G17" s="241">
+      <c r="G17" s="222">
         <f>F17</f>
         <v>178200.05</v>
       </c>
-      <c r="H17" s="144">
+      <c r="H17" s="129">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="144">
+      <c r="I17" s="129">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="145">
+      <c r="J17" s="130">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K17" s="145">
+      <c r="K17" s="130">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="152">
-        <f>EDESUR!I10</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="165">
-        <v>0</v>
-      </c>
-      <c r="N17" s="148">
+      <c r="L17" s="134">
+        <f>EDESUR!K8</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="M17" s="149">
+        <v>0</v>
+      </c>
+      <c r="N17" s="133">
         <f t="shared" si="4"/>
-        <v>178200.05</v>
-      </c>
-      <c r="O17" s="146">
+        <v>194403.05</v>
+      </c>
+      <c r="O17" s="131">
         <f t="shared" si="5"/>
-        <v>188892.05</v>
-      </c>
-      <c r="P17" s="147">
+        <v>206067.05</v>
+      </c>
+      <c r="P17" s="132">
         <f t="shared" si="6"/>
-        <v>183546.05</v>
+        <v>200235.05</v>
       </c>
       <c r="Q17" s="27">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
       <c r="R17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3471,13 +3563,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="40" t="s">
-        <v>38</v>
-      </c>
       <c r="D18" s="40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E18" s="48">
         <v>5.4</v>
@@ -3485,7 +3577,7 @@
       <c r="F18" s="49">
         <v>156924.06</v>
       </c>
-      <c r="G18" s="241">
+      <c r="G18" s="222">
         <v>129600.06</v>
       </c>
       <c r="H18" s="51">
@@ -3496,30 +3588,30 @@
         <f t="shared" si="3"/>
         <v>819.71999999999991</v>
       </c>
-      <c r="J18" s="98">
+      <c r="J18" s="97">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K18" s="98">
+      <c r="K18" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="149">
-        <f>EDESUR!I11</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="164"/>
-      <c r="N18" s="148">
+      <c r="L18" s="134">
+        <f>EDESUR!K9</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="M18" s="148"/>
+      <c r="N18" s="133">
         <f t="shared" si="4"/>
-        <v>173944.06</v>
+        <v>187201.06</v>
       </c>
       <c r="O18" s="52">
         <f t="shared" si="5"/>
-        <v>184381.06</v>
+        <v>198433.06</v>
       </c>
       <c r="P18" s="53">
         <f t="shared" si="6"/>
-        <v>179162.06</v>
+        <v>192817.06</v>
       </c>
       <c r="Q18" s="27">
         <f t="shared" si="7"/>
@@ -3527,60 +3619,60 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="141">
+      <c r="A19" s="126">
         <v>7</v>
       </c>
-      <c r="B19" s="141" t="s">
+      <c r="B19" s="126" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="141" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="141" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="143">
+      <c r="D19" s="126" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="128">
         <v>5.4</v>
       </c>
       <c r="F19" s="50">
         <v>279288.07</v>
       </c>
-      <c r="G19" s="241">
+      <c r="G19" s="222">
         <f>F19</f>
         <v>279288.07</v>
       </c>
-      <c r="H19" s="144">
+      <c r="H19" s="129">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="144">
+      <c r="I19" s="129">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="145">
+      <c r="J19" s="130">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K19" s="145">
+      <c r="K19" s="130">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="149">
-        <f>EDESUR!I12</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="164"/>
-      <c r="N19" s="148">
+      <c r="L19" s="134">
+        <f>EDESUR!K6</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="M19" s="148"/>
+      <c r="N19" s="133">
         <f t="shared" si="4"/>
-        <v>145800.07</v>
-      </c>
-      <c r="O19" s="146">
+        <v>159057.07</v>
+      </c>
+      <c r="O19" s="131">
         <f t="shared" si="5"/>
-        <v>154548.07</v>
-      </c>
-      <c r="P19" s="147">
+        <v>168600.07</v>
+      </c>
+      <c r="P19" s="132">
         <f t="shared" si="6"/>
-        <v>150174.07</v>
+        <v>163829.07</v>
       </c>
       <c r="Q19" s="27">
         <f t="shared" si="7"/>
@@ -3588,59 +3680,60 @@
       </c>
     </row>
     <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="141">
+      <c r="A20" s="126">
         <v>8</v>
       </c>
-      <c r="B20" s="141" t="s">
+      <c r="B20" s="126" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="141" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="142" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="143">
+      <c r="D20" s="127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="128">
         <v>6.6</v>
       </c>
       <c r="F20" s="50">
-        <v>241432.08</v>
-      </c>
-      <c r="G20" s="50">
-        <v>0</v>
-      </c>
-      <c r="H20" s="144">
+        <v>248675.08</v>
+      </c>
+      <c r="G20" s="222">
+        <f>F20</f>
+        <v>248675.08</v>
+      </c>
+      <c r="H20" s="129">
         <f t="shared" si="0"/>
-        <v>241432.08</v>
-      </c>
-      <c r="I20" s="144">
+        <v>0</v>
+      </c>
+      <c r="I20" s="129">
         <f t="shared" si="3"/>
-        <v>7242.9623999999994</v>
-      </c>
-      <c r="J20" s="145">
+        <v>0</v>
+      </c>
+      <c r="J20" s="130">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K20" s="145">
+      <c r="K20" s="130">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="149">
-        <f>EDESUR!I13</f>
-        <v>63231.57</v>
-      </c>
-      <c r="M20" s="164"/>
-      <c r="N20" s="148">
+      <c r="L20" s="134">
+        <f>EDESUR!K11</f>
+        <v>80448.24873370814</v>
+      </c>
+      <c r="M20" s="148"/>
+      <c r="N20" s="133">
         <f t="shared" si="4"/>
-        <v>490107.08</v>
-      </c>
-      <c r="O20" s="146">
+        <v>258648.08</v>
+      </c>
+      <c r="O20" s="131">
         <f t="shared" si="5"/>
-        <v>519514.08</v>
-      </c>
-      <c r="P20" s="147">
+        <v>274167.08</v>
+      </c>
+      <c r="P20" s="132">
         <f t="shared" si="6"/>
-        <v>504810.08</v>
+        <v>266407.07999999996</v>
       </c>
       <c r="Q20" s="27">
         <f t="shared" si="7"/>
@@ -3652,13 +3745,13 @@
         <v>9</v>
       </c>
       <c r="B21" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="40" t="s">
-        <v>44</v>
-      </c>
       <c r="D21" s="41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" s="48">
         <v>6.6</v>
@@ -3666,44 +3759,44 @@
       <c r="F21" s="49">
         <v>199813.09</v>
       </c>
-      <c r="G21" s="241">
-        <f>F21</f>
-        <v>199813.09</v>
+      <c r="G21" s="222">
+        <f>F21+12187.9</f>
+        <v>212000.99</v>
       </c>
       <c r="H21" s="51">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-12187.899999999994</v>
       </c>
       <c r="I21" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="98">
+      <c r="J21" s="97">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K21" s="98">
+      <c r="K21" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="149">
-        <f>EDESUR!I14</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="164">
+      <c r="L21" s="134">
+        <f>EDESUR!K12</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="M21" s="148">
         <v>50000</v>
       </c>
-      <c r="N21" s="148">
+      <c r="N21" s="133">
         <f t="shared" si="4"/>
-        <v>228200.09</v>
+        <v>232216.09</v>
       </c>
       <c r="O21" s="52">
         <f t="shared" si="5"/>
-        <v>241892.09</v>
+        <v>246149.09</v>
       </c>
       <c r="P21" s="53">
         <f t="shared" si="6"/>
-        <v>235046.09</v>
+        <v>239182.09</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="7"/>
@@ -3715,13 +3808,13 @@
         <v>10</v>
       </c>
       <c r="B22" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="40" t="s">
-        <v>46</v>
-      </c>
       <c r="D22" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" s="48">
         <v>5.4</v>
@@ -3729,42 +3822,42 @@
       <c r="F22" s="49">
         <v>16198.1</v>
       </c>
-      <c r="G22" s="243">
-        <f>RESUMEN!D39+16198.1</f>
-        <v>174186.39</v>
+      <c r="G22" s="222">
+        <f>RESUMEN!D39+16198.1-12187.9</f>
+        <v>161998.49000000002</v>
       </c>
       <c r="H22" s="51">
         <f>F22-G22</f>
-        <v>-157988.29</v>
+        <v>-145800.39000000001</v>
       </c>
       <c r="I22" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J22" s="98">
+      <c r="J22" s="97">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K22" s="98">
+      <c r="K22" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="149">
-        <f>EDESUR!I15</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="164"/>
-      <c r="N22" s="148">
+      <c r="L22" s="134">
+        <f>EDESUR!K13</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="M22" s="148"/>
+      <c r="N22" s="133">
         <f t="shared" si="4"/>
-        <v>-12187.9</v>
+        <v>13257.1</v>
       </c>
       <c r="O22" s="52">
         <f t="shared" si="5"/>
-        <v>-12918.9</v>
+        <v>14053.1</v>
       </c>
       <c r="P22" s="53">
         <f t="shared" si="6"/>
-        <v>-12553.9</v>
+        <v>13655.1</v>
       </c>
       <c r="Q22" s="27">
         <f t="shared" si="7"/>
@@ -3776,10 +3869,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="40" t="s">
         <v>47</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>48</v>
       </c>
       <c r="D23" s="41"/>
       <c r="E23" s="48">
@@ -3788,7 +3881,7 @@
       <c r="F23" s="49">
         <v>145800.10999999999</v>
       </c>
-      <c r="G23" s="241">
+      <c r="G23" s="222">
         <f>154014.33-G34</f>
         <v>145800.10999999999</v>
       </c>
@@ -3800,37 +3893,37 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="98">
+      <c r="J23" s="97">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K23" s="98">
+      <c r="K23" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="149">
-        <f>EDESUR!I12</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="164"/>
-      <c r="N23" s="148">
+      <c r="L23" s="134">
+        <f>EDESUR!K10</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="M23" s="148"/>
+      <c r="N23" s="133">
         <f t="shared" si="4"/>
-        <v>145800.10999999999</v>
+        <v>159057.10999999999</v>
       </c>
       <c r="O23" s="52">
         <f t="shared" si="5"/>
-        <v>154548.10999999999</v>
+        <v>168601.11</v>
       </c>
       <c r="P23" s="53">
         <f t="shared" si="6"/>
-        <v>150174.10999999999</v>
+        <v>163829.10999999999</v>
       </c>
       <c r="Q23" s="27">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="R23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3838,13 +3931,13 @@
         <v>12</v>
       </c>
       <c r="B24" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="40" t="s">
-        <v>50</v>
-      </c>
       <c r="D24" s="41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" s="48">
         <v>6.6</v>
@@ -3852,7 +3945,7 @@
       <c r="F24" s="49">
         <v>178200.12</v>
       </c>
-      <c r="G24" s="241">
+      <c r="G24" s="222">
         <f>F24</f>
         <v>178200.12</v>
       </c>
@@ -3864,30 +3957,30 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="98">
+      <c r="J24" s="97">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K24" s="98">
+      <c r="K24" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="149">
-        <f>EDESUR!I17</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="164"/>
-      <c r="N24" s="148">
+      <c r="L24" s="134">
+        <f>EDESUR!K15</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="M24" s="148"/>
+      <c r="N24" s="133">
         <f t="shared" si="4"/>
-        <v>178200.12</v>
+        <v>194403.12</v>
       </c>
       <c r="O24" s="52">
         <f t="shared" si="5"/>
-        <v>188892.12</v>
+        <v>206067.12</v>
       </c>
       <c r="P24" s="53">
         <f t="shared" si="6"/>
-        <v>183546.12</v>
+        <v>200235.12</v>
       </c>
       <c r="Q24" s="27">
         <f t="shared" si="7"/>
@@ -3899,13 +3992,13 @@
         <v>13</v>
       </c>
       <c r="B25" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="40" t="s">
-        <v>52</v>
-      </c>
       <c r="D25" s="41" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E25" s="48">
         <v>6.6</v>
@@ -3913,7 +4006,7 @@
       <c r="F25" s="49">
         <v>173579.13</v>
       </c>
-      <c r="G25" s="241">
+      <c r="G25" s="222">
         <f>F25</f>
         <v>173579.13</v>
       </c>
@@ -3925,30 +4018,30 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="98">
+      <c r="J25" s="97">
         <f t="shared" si="1"/>
         <v>178200</v>
       </c>
-      <c r="K25" s="98">
+      <c r="K25" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="149">
-        <f>EDESUR!I18</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="164"/>
-      <c r="N25" s="148">
+      <c r="L25" s="134">
+        <f>EDESUR!K16</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="M25" s="148"/>
+      <c r="N25" s="133">
         <f t="shared" si="4"/>
-        <v>178200.13</v>
+        <v>194403.13</v>
       </c>
       <c r="O25" s="52">
         <f t="shared" si="5"/>
-        <v>188892.13</v>
+        <v>206067.13</v>
       </c>
       <c r="P25" s="53">
         <f t="shared" si="6"/>
-        <v>183546.13</v>
+        <v>200235.13</v>
       </c>
       <c r="Q25" s="27">
         <f t="shared" si="7"/>
@@ -3956,57 +4049,57 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="141">
+      <c r="A26" s="126">
         <v>14</v>
       </c>
-      <c r="B26" s="141" t="s">
+      <c r="B26" s="126" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="141" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="142"/>
-      <c r="E26" s="143">
+      <c r="D26" s="127"/>
+      <c r="E26" s="128">
         <v>5.4</v>
       </c>
       <c r="F26" s="50">
         <v>150174.14000000001</v>
       </c>
-      <c r="G26" s="241">
+      <c r="G26" s="222">
         <v>150174.14000000001</v>
       </c>
-      <c r="H26" s="144">
+      <c r="H26" s="129">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="144">
+      <c r="I26" s="129">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="145">
+      <c r="J26" s="130">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K26" s="145">
+      <c r="K26" s="130">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="152">
-        <f>EDESUR!I19</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="165"/>
-      <c r="N26" s="148">
+      <c r="L26" s="134">
+        <f>EDESUR!K17</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="M26" s="149"/>
+      <c r="N26" s="133">
         <f t="shared" si="4"/>
-        <v>145800.14000000001</v>
-      </c>
-      <c r="O26" s="146">
+        <v>159057.14000000001</v>
+      </c>
+      <c r="O26" s="131">
         <f t="shared" si="5"/>
-        <v>154548.14000000001</v>
-      </c>
-      <c r="P26" s="147">
+        <v>168601.14</v>
+      </c>
+      <c r="P26" s="132">
         <f t="shared" si="6"/>
-        <v>150174.14000000001</v>
+        <v>163829.14000000001</v>
       </c>
       <c r="Q26" s="27">
         <f t="shared" si="7"/>
@@ -4018,10 +4111,10 @@
         <v>15</v>
       </c>
       <c r="B27" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="40" t="s">
         <v>55</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>56</v>
       </c>
       <c r="D27" s="41"/>
       <c r="E27" s="48">
@@ -4030,7 +4123,7 @@
       <c r="F27" s="49">
         <v>145800.15</v>
       </c>
-      <c r="G27" s="241">
+      <c r="G27" s="222">
         <f>F27</f>
         <v>145800.15</v>
       </c>
@@ -4042,30 +4135,30 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="98">
+      <c r="J27" s="97">
         <f t="shared" si="1"/>
         <v>145800.00000000003</v>
       </c>
-      <c r="K27" s="98">
+      <c r="K27" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="149">
-        <f>EDESUR!I16</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="164"/>
-      <c r="N27" s="148">
+      <c r="L27" s="134">
+        <f>EDESUR!K14</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="M27" s="148"/>
+      <c r="N27" s="133">
         <f t="shared" si="4"/>
-        <v>145800.15</v>
+        <v>159057.15</v>
       </c>
       <c r="O27" s="52">
         <f t="shared" si="5"/>
-        <v>154548.15</v>
+        <v>168601.15</v>
       </c>
       <c r="P27" s="53">
         <f t="shared" si="6"/>
-        <v>150174.15</v>
+        <v>163829.15</v>
       </c>
       <c r="Q27" s="27">
         <f t="shared" si="7"/>
@@ -4073,17 +4166,17 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="141">
+      <c r="A28" s="126">
         <v>16</v>
       </c>
-      <c r="B28" s="141" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="141" t="s">
-        <v>38</v>
+      <c r="B28" s="126" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="126" t="s">
+        <v>37</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E28" s="48">
         <v>0.7</v>
@@ -4091,7 +4184,7 @@
       <c r="F28" s="49">
         <v>20609.16</v>
       </c>
-      <c r="G28" s="241">
+      <c r="G28" s="222">
         <v>16800.16</v>
       </c>
       <c r="H28" s="51">
@@ -4102,30 +4195,30 @@
         <f t="shared" si="3"/>
         <v>114.27</v>
       </c>
-      <c r="J28" s="98">
+      <c r="J28" s="97">
         <f t="shared" si="1"/>
         <v>18899.999999999996</v>
       </c>
-      <c r="K28" s="98">
+      <c r="K28" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="149">
-        <f>EDESUR!I22</f>
-        <v>266.88</v>
-      </c>
-      <c r="M28" s="164"/>
-      <c r="N28" s="148">
+      <c r="L28" s="134">
+        <f>EDESUR!K20</f>
+        <v>1718.548237452153</v>
+      </c>
+      <c r="M28" s="148"/>
+      <c r="N28" s="133">
         <f t="shared" si="4"/>
-        <v>23090.16</v>
+        <v>24542.16</v>
       </c>
       <c r="O28" s="52">
         <f t="shared" si="5"/>
-        <v>24476.16</v>
+        <v>26015.16</v>
       </c>
       <c r="P28" s="53">
         <f t="shared" si="6"/>
-        <v>23783.16</v>
+        <v>25278.16</v>
       </c>
       <c r="Q28" s="27">
         <f t="shared" si="7"/>
@@ -4133,14 +4226,14 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="141">
+      <c r="A29" s="126">
         <v>17</v>
       </c>
-      <c r="B29" s="141" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="141" t="s">
-        <v>28</v>
+      <c r="B29" s="126" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="126" t="s">
+        <v>27</v>
       </c>
       <c r="D29" s="41"/>
       <c r="E29" s="48">
@@ -4149,7 +4242,7 @@
       <c r="F29" s="50">
         <v>16429.169999999998</v>
       </c>
-      <c r="G29" s="241">
+      <c r="G29" s="222">
         <f>F29</f>
         <v>16429.169999999998</v>
       </c>
@@ -4161,30 +4254,30 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="98">
+      <c r="J29" s="97">
         <f t="shared" si="1"/>
         <v>16200</v>
       </c>
-      <c r="K29" s="98">
+      <c r="K29" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="149">
-        <f>EDESUR!I23</f>
-        <v>228.75</v>
-      </c>
-      <c r="M29" s="164"/>
-      <c r="N29" s="148">
+      <c r="L29" s="134">
+        <f>EDESUR!K21</f>
+        <v>1473.0413463875598</v>
+      </c>
+      <c r="M29" s="148"/>
+      <c r="N29" s="133">
         <f t="shared" si="4"/>
-        <v>16429.169999999998</v>
+        <v>17673.169999999998</v>
       </c>
       <c r="O29" s="52">
         <f t="shared" si="5"/>
-        <v>17415.169999999998</v>
+        <v>18734.169999999998</v>
       </c>
       <c r="P29" s="53">
         <f t="shared" si="6"/>
-        <v>16922.169999999998</v>
+        <v>18203.169999999998</v>
       </c>
       <c r="Q29" s="27">
         <f t="shared" si="7"/>
@@ -4196,19 +4289,19 @@
         <v>18</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="84"/>
+        <v>27</v>
+      </c>
+      <c r="D30" s="83"/>
       <c r="E30" s="48">
         <v>0.6</v>
       </c>
       <c r="F30" s="49">
         <v>16429.18</v>
       </c>
-      <c r="G30" s="241">
+      <c r="G30" s="222">
         <f>F30</f>
         <v>16429.18</v>
       </c>
@@ -4220,30 +4313,30 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="98">
+      <c r="J30" s="97">
         <f t="shared" si="1"/>
         <v>16200</v>
       </c>
-      <c r="K30" s="98">
+      <c r="K30" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="149">
-        <f>EDESUR!I24</f>
-        <v>228.75</v>
-      </c>
-      <c r="M30" s="164"/>
-      <c r="N30" s="148">
+      <c r="L30" s="134">
+        <f>EDESUR!K22</f>
+        <v>1473.0413463875598</v>
+      </c>
+      <c r="M30" s="148"/>
+      <c r="N30" s="133">
         <f t="shared" si="4"/>
-        <v>16429.18</v>
+        <v>17673.18</v>
       </c>
       <c r="O30" s="52">
         <f t="shared" si="5"/>
-        <v>17415.18</v>
+        <v>18734.18</v>
       </c>
       <c r="P30" s="53">
         <f t="shared" si="6"/>
-        <v>16922.18</v>
+        <v>18203.18</v>
       </c>
       <c r="Q30" s="27">
         <f t="shared" si="7"/>
@@ -4251,55 +4344,55 @@
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="141">
+      <c r="A31" s="126">
         <v>19</v>
       </c>
-      <c r="B31" s="141" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="141" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="142"/>
-      <c r="E31" s="143">
+      <c r="B31" s="126" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="126" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="127"/>
+      <c r="E31" s="128">
         <v>0.6</v>
       </c>
       <c r="F31" s="50">
         <v>16429.189999999999</v>
       </c>
-      <c r="G31" s="241">
+      <c r="G31" s="222">
         <f>F31</f>
         <v>16429.189999999999</v>
       </c>
-      <c r="H31" s="144">
+      <c r="H31" s="129">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="144">
+      <c r="I31" s="129">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="145">
+      <c r="J31" s="130">
         <f t="shared" si="1"/>
         <v>16200</v>
       </c>
-      <c r="K31" s="145">
+      <c r="K31" s="130">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="152">
-        <f>EDESUR!I25</f>
-        <v>228.75</v>
-      </c>
-      <c r="M31" s="165"/>
-      <c r="N31" s="148">
+      <c r="L31" s="134">
+        <f>EDESUR!K23</f>
+        <v>1473.0413463875598</v>
+      </c>
+      <c r="M31" s="149"/>
+      <c r="N31" s="133">
         <f t="shared" si="4"/>
-        <v>16429.189999999999</v>
-      </c>
-      <c r="O31" s="146"/>
-      <c r="P31" s="147">
+        <v>17673.189999999999</v>
+      </c>
+      <c r="O31" s="131"/>
+      <c r="P31" s="132">
         <f t="shared" si="6"/>
-        <v>16922.189999999999</v>
+        <v>18203.189999999999</v>
       </c>
       <c r="Q31" s="27">
         <f>Q30+0.01</f>
@@ -4311,13 +4404,13 @@
         <v>20</v>
       </c>
       <c r="B32" s="54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E32" s="48">
         <v>0.6</v>
@@ -4325,7 +4418,7 @@
       <c r="F32" s="56">
         <v>16429.2</v>
       </c>
-      <c r="G32" s="241">
+      <c r="G32" s="222">
         <f>F32</f>
         <v>16429.2</v>
       </c>
@@ -4337,27 +4430,27 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J32" s="98">
+      <c r="J32" s="97">
         <f t="shared" si="1"/>
         <v>16200</v>
       </c>
-      <c r="K32" s="98">
+      <c r="K32" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="149">
-        <f>EDESUR!I26</f>
-        <v>228.75</v>
-      </c>
-      <c r="M32" s="164"/>
-      <c r="N32" s="148">
+      <c r="L32" s="134">
+        <f>EDESUR!K24</f>
+        <v>1473.0413463875598</v>
+      </c>
+      <c r="M32" s="148"/>
+      <c r="N32" s="133">
         <f t="shared" si="4"/>
-        <v>16429.2</v>
+        <v>17673.2</v>
       </c>
       <c r="O32" s="52"/>
       <c r="P32" s="53">
         <f t="shared" si="6"/>
-        <v>16922.2</v>
+        <v>18203.2</v>
       </c>
       <c r="Q32" s="27">
         <f t="shared" ref="Q32:Q35" si="8">Q31+0.01</f>
@@ -4369,13 +4462,13 @@
         <v>21</v>
       </c>
       <c r="B33" s="54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E33" s="48">
         <v>0.3</v>
@@ -4383,7 +4476,7 @@
       <c r="F33" s="56">
         <v>8214.2099999999991</v>
       </c>
-      <c r="G33" s="241">
+      <c r="G33" s="222">
         <f>F33</f>
         <v>8214.2099999999991</v>
       </c>
@@ -4395,27 +4488,27 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J33" s="98">
+      <c r="J33" s="97">
         <f t="shared" si="1"/>
         <v>8100</v>
       </c>
-      <c r="K33" s="98">
+      <c r="K33" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="149">
-        <f>EDESUR!I27</f>
-        <v>114.38</v>
-      </c>
-      <c r="M33" s="164"/>
-      <c r="N33" s="148">
+      <c r="L33" s="134">
+        <f>EDESUR!K25</f>
+        <v>736.52067319377988</v>
+      </c>
+      <c r="M33" s="148"/>
+      <c r="N33" s="133">
         <f t="shared" si="4"/>
-        <v>8214.2099999999991</v>
+        <v>8837.2099999999991</v>
       </c>
       <c r="O33" s="52"/>
       <c r="P33" s="53">
         <f t="shared" si="6"/>
-        <v>8460.2099999999991</v>
+        <v>9102.2099999999991</v>
       </c>
       <c r="Q33" s="27">
         <f t="shared" si="8"/>
@@ -4427,10 +4520,10 @@
         <v>22</v>
       </c>
       <c r="B34" s="55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D34" s="41"/>
       <c r="E34" s="48">
@@ -4439,7 +4532,7 @@
       <c r="F34" s="56">
         <v>8214.2199999999993</v>
       </c>
-      <c r="G34" s="242">
+      <c r="G34" s="223">
         <f t="shared" ref="G34" si="9">F34</f>
         <v>8214.2199999999993</v>
       </c>
@@ -4451,27 +4544,27 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J34" s="98">
+      <c r="J34" s="97">
         <f t="shared" si="1"/>
         <v>8100</v>
       </c>
-      <c r="K34" s="98">
+      <c r="K34" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="149">
-        <f>EDESUR!I28</f>
-        <v>114.38</v>
-      </c>
-      <c r="M34" s="164"/>
-      <c r="N34" s="148">
+      <c r="L34" s="134">
+        <f>EDESUR!K26</f>
+        <v>736.52067319377988</v>
+      </c>
+      <c r="M34" s="148"/>
+      <c r="N34" s="133">
         <f t="shared" si="4"/>
-        <v>8214.2199999999993</v>
+        <v>8837.2199999999993</v>
       </c>
       <c r="O34" s="52"/>
       <c r="P34" s="53">
         <f t="shared" si="6"/>
-        <v>8460.2199999999993</v>
+        <v>9102.2199999999993</v>
       </c>
       <c r="Q34" s="27">
         <f t="shared" si="8"/>
@@ -4483,13 +4576,13 @@
         <v>23</v>
       </c>
       <c r="B35" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="57" t="s">
-        <v>65</v>
-      </c>
       <c r="D35" s="41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E35" s="48">
         <v>0.3</v>
@@ -4497,7 +4590,7 @@
       <c r="F35" s="56">
         <v>8214.23</v>
       </c>
-      <c r="G35" s="241">
+      <c r="G35" s="222">
         <f>F35</f>
         <v>8214.23</v>
       </c>
@@ -4509,27 +4602,27 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="98">
+      <c r="J35" s="97">
         <f t="shared" si="1"/>
         <v>8100</v>
       </c>
-      <c r="K35" s="98">
+      <c r="K35" s="97">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="149">
-        <f>EDESUR!I29</f>
-        <v>114.38</v>
-      </c>
-      <c r="M35" s="164"/>
-      <c r="N35" s="148">
+      <c r="L35" s="134">
+        <f>EDESUR!K27</f>
+        <v>736.52067319377988</v>
+      </c>
+      <c r="M35" s="148"/>
+      <c r="N35" s="133">
         <f t="shared" si="4"/>
-        <v>8214.23</v>
+        <v>8837.23</v>
       </c>
       <c r="O35" s="58"/>
       <c r="P35" s="53">
         <f t="shared" si="6"/>
-        <v>8460.23</v>
+        <v>9102.23</v>
       </c>
       <c r="Q35" s="27">
         <f t="shared" si="8"/>
@@ -4541,27 +4634,27 @@
       <c r="B36" s="59"/>
       <c r="C36" s="60"/>
       <c r="D36" s="60"/>
-      <c r="E36" s="106">
+      <c r="E36" s="103">
         <f>SUM(E13:E35)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="F36" s="34">
         <f>SUM(F13:F35)</f>
-        <v>2902950.7600000012</v>
+        <v>2910193.7600000012</v>
       </c>
       <c r="G36" s="38">
         <f>SUM(G13:G35)</f>
-        <v>2788870.3600000008</v>
+        <v>3037545.4400000009</v>
       </c>
       <c r="H36" s="38">
         <f>SUM(H13:H35)</f>
-        <v>114080.4</v>
+        <v>-127351.67999999999</v>
       </c>
       <c r="I36" s="38">
         <f t="shared" ref="I36:O36" si="10">SUM(I13:I35)</f>
-        <v>8176.9524000000001</v>
-      </c>
-      <c r="J36" s="87">
+        <v>933.9899999999999</v>
+      </c>
+      <c r="J36" s="86">
         <f t="shared" si="10"/>
         <v>2700000</v>
       </c>
@@ -4571,20 +4664,20 @@
       </c>
       <c r="L36" s="61">
         <f>SUM(L13:L35)</f>
-        <v>171314.17</v>
+        <v>442653.69000000029</v>
       </c>
       <c r="M36" s="61"/>
       <c r="N36" s="61">
         <f>SUM(N13:N35)</f>
-        <v>3043574.7600000007</v>
+        <v>3066236.7600000012</v>
       </c>
       <c r="O36" s="61">
         <f t="shared" si="10"/>
-        <v>3165239.7100000004</v>
+        <v>3184643.7100000004</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P13:P35)</f>
-        <v>3134881.7600000007</v>
+        <v>3158223.7600000007</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4593,94 +4686,100 @@
     </row>
     <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="197" t="str">
+      <c r="C39" s="180" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="197"/>
-      <c r="E39" s="197"/>
-      <c r="F39" s="197"/>
-      <c r="G39" s="197"/>
-      <c r="H39" s="197"/>
-      <c r="I39" s="197"/>
-      <c r="J39" s="197"/>
-      <c r="K39" s="197"/>
-      <c r="L39" s="197"/>
-      <c r="M39" s="197"/>
-      <c r="N39" s="197"/>
+      <c r="D39" s="180"/>
+      <c r="E39" s="180"/>
+      <c r="F39" s="180"/>
+      <c r="G39" s="180"/>
+      <c r="H39" s="180"/>
+      <c r="I39" s="180"/>
+      <c r="J39" s="180"/>
+      <c r="K39" s="180"/>
+      <c r="L39" s="180"/>
+      <c r="M39" s="180"/>
+      <c r="N39" s="180"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="197"/>
-      <c r="D40" s="197"/>
-      <c r="E40" s="197"/>
-      <c r="F40" s="197"/>
-      <c r="G40" s="197"/>
-      <c r="H40" s="197"/>
-      <c r="I40" s="197"/>
-      <c r="J40" s="197"/>
-      <c r="K40" s="197"/>
-      <c r="L40" s="197"/>
-      <c r="M40" s="197"/>
-      <c r="N40" s="197"/>
+      <c r="C40" s="180"/>
+      <c r="D40" s="180"/>
+      <c r="E40" s="180"/>
+      <c r="F40" s="180"/>
+      <c r="G40" s="180"/>
+      <c r="H40" s="180"/>
+      <c r="I40" s="180"/>
+      <c r="J40" s="180"/>
+      <c r="K40" s="180"/>
+      <c r="L40" s="180"/>
+      <c r="M40" s="180"/>
+      <c r="N40" s="180"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="197"/>
-      <c r="D41" s="197"/>
-      <c r="E41" s="197"/>
-      <c r="F41" s="197"/>
-      <c r="G41" s="197"/>
-      <c r="H41" s="197"/>
-      <c r="I41" s="197"/>
-      <c r="J41" s="197"/>
-      <c r="K41" s="197"/>
-      <c r="L41" s="197"/>
-      <c r="M41" s="197"/>
-      <c r="N41" s="197"/>
+      <c r="C41" s="180"/>
+      <c r="D41" s="180"/>
+      <c r="E41" s="180"/>
+      <c r="F41" s="180"/>
+      <c r="G41" s="180"/>
+      <c r="H41" s="180"/>
+      <c r="I41" s="180"/>
+      <c r="J41" s="180"/>
+      <c r="K41" s="180"/>
+      <c r="L41" s="180"/>
+      <c r="M41" s="180"/>
+      <c r="N41" s="180"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="197"/>
-      <c r="D42" s="197"/>
-      <c r="E42" s="197"/>
-      <c r="F42" s="197"/>
-      <c r="G42" s="197"/>
-      <c r="H42" s="197"/>
-      <c r="I42" s="197"/>
-      <c r="J42" s="197"/>
-      <c r="K42" s="197"/>
-      <c r="L42" s="197"/>
-      <c r="M42" s="197"/>
-      <c r="N42" s="197"/>
+      <c r="C42" s="180"/>
+      <c r="D42" s="180"/>
+      <c r="E42" s="180"/>
+      <c r="F42" s="180"/>
+      <c r="G42" s="180"/>
+      <c r="H42" s="180"/>
+      <c r="I42" s="180"/>
+      <c r="J42" s="180"/>
+      <c r="K42" s="180"/>
+      <c r="L42" s="180"/>
+      <c r="M42" s="180"/>
+      <c r="N42" s="180"/>
     </row>
     <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="197"/>
-      <c r="D43" s="197"/>
-      <c r="E43" s="197"/>
-      <c r="F43" s="197"/>
-      <c r="G43" s="197"/>
-      <c r="H43" s="197"/>
-      <c r="I43" s="197"/>
-      <c r="J43" s="197"/>
-      <c r="K43" s="197"/>
-      <c r="L43" s="197"/>
-      <c r="M43" s="197"/>
-      <c r="N43" s="197"/>
+      <c r="C43" s="180"/>
+      <c r="D43" s="180"/>
+      <c r="E43" s="180"/>
+      <c r="F43" s="180"/>
+      <c r="G43" s="180"/>
+      <c r="H43" s="180"/>
+      <c r="I43" s="180"/>
+      <c r="J43" s="180"/>
+      <c r="K43" s="180"/>
+      <c r="L43" s="180"/>
+      <c r="M43" s="180"/>
+      <c r="N43" s="180"/>
     </row>
     <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="197"/>
-      <c r="D44" s="197"/>
-      <c r="E44" s="197"/>
-      <c r="F44" s="197"/>
-      <c r="G44" s="197"/>
-      <c r="H44" s="197"/>
-      <c r="I44" s="197"/>
-      <c r="J44" s="197"/>
-      <c r="K44" s="197"/>
-      <c r="L44" s="197"/>
-      <c r="M44" s="197"/>
-      <c r="N44" s="197"/>
+      <c r="C44" s="180"/>
+      <c r="D44" s="180"/>
+      <c r="E44" s="180"/>
+      <c r="F44" s="180"/>
+      <c r="G44" s="180"/>
+      <c r="H44" s="180"/>
+      <c r="I44" s="180"/>
+      <c r="J44" s="180"/>
+      <c r="K44" s="180"/>
+      <c r="L44" s="180"/>
+      <c r="M44" s="180"/>
+      <c r="N44" s="180"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4694,12 +4793,6 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4707,643 +4800,994 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
-    <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="109" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="109" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="111" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="140" t="s">
-        <v>127</v>
-      </c>
-      <c r="I3" s="238" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" s="239"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="109"/>
-      <c r="C4" s="109"/>
-      <c r="E4" s="109"/>
-      <c r="G4" s="112"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="239"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="109">
-        <v>1</v>
-      </c>
-      <c r="C5" s="109" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="166">
-        <v>8123.99</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="167">
-        <f>E5</f>
-        <v>8123.99</v>
-      </c>
-      <c r="I5" s="236">
-        <f>E5-G5</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="237"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="109">
-        <v>1</v>
-      </c>
-      <c r="C6" s="109" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="166">
-        <v>102901.79</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="167">
-        <v>0</v>
-      </c>
-      <c r="I6" s="236">
-        <f t="shared" ref="I6:I19" si="0">E6-G6</f>
-        <v>102901.79</v>
-      </c>
-      <c r="J6" s="237"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="109">
-        <v>1</v>
-      </c>
-      <c r="C7" s="109" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="166">
-        <v>3655.79</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="167">
-        <v>0</v>
-      </c>
-      <c r="I7" s="236">
-        <f t="shared" si="0"/>
-        <v>3655.79</v>
-      </c>
-      <c r="J7" s="237"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="109">
-        <v>2</v>
-      </c>
-      <c r="C8" s="109" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="166">
-        <v>3655.79</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="167">
-        <f>E8</f>
-        <v>3655.79</v>
-      </c>
-      <c r="I8" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="237"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="110">
-        <v>2</v>
-      </c>
-      <c r="C9" s="110" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="166">
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="167">
-        <f>E9</f>
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="I9" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="237"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="110">
-        <v>2</v>
-      </c>
-      <c r="C10" s="110" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="166">
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="167">
-        <f>E10</f>
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="I10" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="237"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="110">
-        <v>2</v>
-      </c>
-      <c r="C11" s="110" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="166">
-        <v>3655.79</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="167">
-        <f>E11</f>
-        <v>3655.79</v>
-      </c>
-      <c r="I11" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="237"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="110">
-        <v>3</v>
-      </c>
-      <c r="C12" s="110" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="166">
-        <v>3655.79</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="167">
-        <f>E12</f>
-        <v>3655.79</v>
-      </c>
-      <c r="I12" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="237"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="109">
-        <v>3</v>
-      </c>
-      <c r="C13" s="109" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="166">
-        <v>63231.57</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="167">
-        <v>0</v>
-      </c>
-      <c r="I13" s="236">
-        <f t="shared" si="0"/>
-        <v>63231.57</v>
-      </c>
-      <c r="J13" s="237"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="110">
-        <v>3</v>
-      </c>
-      <c r="C14" s="110" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="166">
-        <f>E10</f>
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="167">
-        <f t="shared" ref="G14:G19" si="1">E14</f>
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="I14" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="237"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="110">
-        <v>3</v>
-      </c>
-      <c r="C15" s="110" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="166">
-        <f>E12</f>
-        <v>3655.79</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="167">
-        <f t="shared" si="1"/>
-        <v>3655.79</v>
-      </c>
-      <c r="I15" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="237"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="109">
-        <v>4</v>
-      </c>
-      <c r="C16" s="109" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="166">
-        <f>E15</f>
-        <v>3655.79</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="167">
-        <f t="shared" si="1"/>
-        <v>3655.79</v>
-      </c>
-      <c r="I16" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="237"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="110">
-        <v>4</v>
-      </c>
-      <c r="C17" s="110" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="166">
-        <f>E14</f>
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="167">
-        <f t="shared" si="1"/>
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="I17" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="237"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="109">
-        <v>4</v>
-      </c>
-      <c r="C18" s="109" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="166">
-        <f>E17</f>
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="167">
-        <f t="shared" si="1"/>
-        <v>4468.1899999999996</v>
-      </c>
-      <c r="I18" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="237"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="110">
-        <v>4</v>
-      </c>
-      <c r="C19" s="110" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="166">
-        <f>E16</f>
-        <v>3655.79</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="167">
-        <f t="shared" si="1"/>
-        <v>3655.79</v>
-      </c>
-      <c r="I19" s="236">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="237"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="109"/>
-      <c r="C20" s="109"/>
-      <c r="E20" s="109"/>
-      <c r="G20" s="112"/>
-      <c r="I20" s="236"/>
-      <c r="J20" s="237"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="133" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="133"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="135">
-        <f>SUM(E5:E20)</f>
-        <v>222188.83000000002</v>
-      </c>
-      <c r="F21" s="136"/>
-      <c r="G21" s="135">
-        <f>SUM(G5:G20)</f>
-        <v>52399.68</v>
-      </c>
-      <c r="I21" s="236">
-        <f>E21-G21</f>
-        <v>169789.15000000002</v>
-      </c>
-      <c r="J21" s="237"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="109">
-        <v>1</v>
-      </c>
-      <c r="E22" s="168">
-        <v>473.9</v>
-      </c>
-      <c r="G22" s="117">
-        <v>207.02</v>
-      </c>
-      <c r="I22" s="236">
-        <f t="shared" ref="I22" si="2">E22-G22</f>
-        <v>266.88</v>
-      </c>
-      <c r="J22" s="237"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="109">
-        <v>2</v>
-      </c>
-      <c r="E23" s="168">
-        <v>406.2</v>
-      </c>
-      <c r="G23" s="117">
-        <v>177.45</v>
-      </c>
-      <c r="I23" s="236">
-        <f t="shared" ref="I23:I31" si="3">E23-G23</f>
-        <v>228.75</v>
-      </c>
-      <c r="J23" s="237"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="109">
-        <v>3</v>
-      </c>
-      <c r="E24" s="168">
-        <f>E23</f>
-        <v>406.2</v>
-      </c>
-      <c r="G24" s="117">
-        <v>177.45</v>
-      </c>
-      <c r="I24" s="236">
-        <f t="shared" si="3"/>
-        <v>228.75</v>
-      </c>
-      <c r="J24" s="237"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="109">
-        <v>4</v>
-      </c>
-      <c r="E25" s="168">
-        <f>E24</f>
-        <v>406.2</v>
-      </c>
-      <c r="G25" s="117">
-        <v>177.45</v>
-      </c>
-      <c r="I25" s="236">
-        <f t="shared" si="3"/>
-        <v>228.75</v>
-      </c>
-      <c r="J25" s="237"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="109">
-        <v>5</v>
-      </c>
-      <c r="E26" s="168">
-        <f>E25</f>
-        <v>406.2</v>
-      </c>
-      <c r="G26" s="117">
-        <v>177.45</v>
-      </c>
-      <c r="I26" s="236">
-        <f t="shared" si="3"/>
-        <v>228.75</v>
-      </c>
-      <c r="J26" s="237"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="109">
-        <v>6</v>
-      </c>
-      <c r="E27" s="168">
-        <v>203.1</v>
-      </c>
-      <c r="G27" s="117">
-        <v>88.72</v>
-      </c>
-      <c r="I27" s="236">
-        <f t="shared" si="3"/>
-        <v>114.38</v>
-      </c>
-      <c r="J27" s="237"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="109">
-        <v>7</v>
-      </c>
-      <c r="E28" s="168">
-        <f>E27</f>
-        <v>203.1</v>
-      </c>
-      <c r="G28" s="117">
-        <v>88.72</v>
-      </c>
-      <c r="I28" s="236">
-        <f t="shared" si="3"/>
-        <v>114.38</v>
-      </c>
-      <c r="J28" s="237"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="109">
-        <v>8</v>
-      </c>
-      <c r="E29" s="168">
-        <f>E28</f>
-        <v>203.1</v>
-      </c>
-      <c r="G29" s="117">
-        <v>88.72</v>
-      </c>
-      <c r="I29" s="236">
-        <f t="shared" si="3"/>
-        <v>114.38</v>
-      </c>
-      <c r="J29" s="237"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="138" t="s">
-        <v>120</v>
-      </c>
-      <c r="C30" s="139"/>
-      <c r="D30" s="137"/>
-      <c r="E30" s="135">
-        <f>SUM(E22:E29)</f>
-        <v>2707.9999999999995</v>
-      </c>
-      <c r="F30" s="137"/>
-      <c r="G30" s="135">
-        <f>SUM(G22:G29)</f>
-        <v>1182.9800000000002</v>
-      </c>
-      <c r="I30" s="236">
-        <f t="shared" si="3"/>
-        <v>1525.0199999999993</v>
-      </c>
-      <c r="J30" s="237"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E31" s="116"/>
-      <c r="G31" s="113"/>
-      <c r="I31" s="236">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="237"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E32" s="114"/>
-      <c r="G32" s="115"/>
-      <c r="I32" s="236"/>
-      <c r="J32" s="237"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E33" s="116">
-        <f>E30+E21</f>
-        <v>224896.83000000002</v>
-      </c>
-      <c r="G33" s="113">
-        <f>G21+G30</f>
-        <v>53582.66</v>
-      </c>
-      <c r="I33" s="236">
-        <f>E33-G33</f>
-        <v>171314.17</v>
-      </c>
-      <c r="J33" s="237"/>
-    </row>
-  </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A2E191-9409-46F3-B653-02D2C9674BEA}">
+  <dimension ref="B2:K39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="242" customWidth="1"/>
+    <col min="6" max="6" width="13" style="242" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="242" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="242" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="242" customWidth="1"/>
+    <col min="12" max="12" width="2.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="106" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="224" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="224" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="106" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="106" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="I2" s="106"/>
+      <c r="J2" s="225" t="s">
+        <v>148</v>
+      </c>
+      <c r="K2" s="107" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="226">
+        <v>1</v>
+      </c>
+      <c r="C3" s="226" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="227">
+        <v>8687.5</v>
+      </c>
+      <c r="E3" s="227">
+        <v>8687.5</v>
+      </c>
+      <c r="F3" s="228">
+        <f>(E3-D3)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="229">
+        <f>F3/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="230">
+        <f>(F3/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="231">
+        <v>0.12</v>
+      </c>
+      <c r="J3" s="151">
+        <f>H34*I3</f>
+        <v>29460.826927751194</v>
+      </c>
+      <c r="K3" s="150">
+        <f>H3+J3</f>
+        <v>29460.826927751194</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="232">
+        <v>1</v>
+      </c>
+      <c r="C4" s="232" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="233">
+        <v>4488.6000000000004</v>
+      </c>
+      <c r="E4" s="233">
+        <v>4865.1000000000004</v>
+      </c>
+      <c r="F4" s="234">
+        <f>(E4-D4)</f>
+        <v>376.5</v>
+      </c>
+      <c r="G4" s="235">
+        <f>F4/F32</f>
+        <v>0.67412712623097581</v>
+      </c>
+      <c r="H4" s="230">
+        <f>(F4/F32)*H32</f>
+        <v>132902.00501196174</v>
+      </c>
+      <c r="I4" s="236">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J4" s="151">
+        <f>H34*I4</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="K4" s="150">
+        <f t="shared" ref="K4:K28" si="0">H4+J4</f>
+        <v>149105.45982222489</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="232">
+        <v>1</v>
+      </c>
+      <c r="C5" s="232" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="227">
+        <v>2366.38</v>
+      </c>
+      <c r="E5" s="227">
+        <v>2366.38</v>
+      </c>
+      <c r="F5" s="228">
+        <f t="shared" ref="F5:F17" si="1">(E5-D5)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="229">
+        <f>F5/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="230">
+        <f>(F5/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="236">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J5" s="151">
+        <f>H34*I5</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="K5" s="150">
+        <f t="shared" si="0"/>
+        <v>13257.372117488037</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="226">
+        <v>2</v>
+      </c>
+      <c r="C6" s="226" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="227">
+        <v>3731.1</v>
+      </c>
+      <c r="E6" s="227">
+        <v>3731.1</v>
+      </c>
+      <c r="F6" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="229">
+        <f>F6/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="230">
+        <f>(F6/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="236">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J6" s="151">
+        <f>H34*I6</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="K6" s="150">
+        <f t="shared" si="0"/>
+        <v>13257.372117488037</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="226">
+        <v>2</v>
+      </c>
+      <c r="C7" s="226" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="227">
+        <v>3897.7</v>
+      </c>
+      <c r="E7" s="227">
+        <v>3897.7</v>
+      </c>
+      <c r="F7" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="229">
+        <f>F7/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="230">
+        <f>(F7/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="236">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J7" s="151">
+        <f>H34*I7</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="K7" s="150">
+        <f t="shared" si="0"/>
+        <v>16203.454810263158</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="226">
+        <v>2</v>
+      </c>
+      <c r="C8" s="226" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="227">
+        <v>2956.2</v>
+      </c>
+      <c r="E8" s="227">
+        <v>2956.2</v>
+      </c>
+      <c r="F8" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="229">
+        <f>F8/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="230">
+        <f>(F8/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="236">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J8" s="151">
+        <f>H34*I8</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="K8" s="150">
+        <f t="shared" si="0"/>
+        <v>16203.454810263158</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="226">
+        <v>2</v>
+      </c>
+      <c r="C9" s="226" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="227">
+        <v>3923.7</v>
+      </c>
+      <c r="E9" s="227">
+        <v>3923.7</v>
+      </c>
+      <c r="F9" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="229">
+        <f>F9/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="237">
+        <f>(F9/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="236">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J9" s="151">
+        <f>H34*I9</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="K9" s="150">
+        <f t="shared" si="0"/>
+        <v>13257.372117488037</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="226">
+        <v>3</v>
+      </c>
+      <c r="C10" s="226" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="227">
+        <v>2881.8</v>
+      </c>
+      <c r="E10" s="227">
+        <v>2881.8</v>
+      </c>
+      <c r="F10" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="229">
+        <f>F10/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="230">
+        <f>(F10/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="236">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J10" s="151">
+        <f>H34*I10</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="K10" s="150">
+        <f t="shared" si="0"/>
+        <v>13257.372117488037</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="232">
+        <v>3</v>
+      </c>
+      <c r="C11" s="232" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="233">
+        <v>4646</v>
+      </c>
+      <c r="E11" s="233">
+        <v>4828</v>
+      </c>
+      <c r="F11" s="234">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="G11" s="235">
+        <f>F11/F32</f>
+        <v>0.32587287376902419</v>
+      </c>
+      <c r="H11" s="230">
+        <f>(F11/F32)*H32</f>
+        <v>64244.793923444988</v>
+      </c>
+      <c r="I11" s="236">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J11" s="151">
+        <f>H34*I11</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="K11" s="150">
+        <f t="shared" si="0"/>
+        <v>80448.24873370814</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="226">
+        <v>3</v>
+      </c>
+      <c r="C12" s="226" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="227">
+        <v>4554.6000000000004</v>
+      </c>
+      <c r="E12" s="227">
+        <v>4554.6000000000004</v>
+      </c>
+      <c r="F12" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="229">
+        <f>F12/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="230">
+        <f>(F12/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="236">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J12" s="151">
+        <f>H34*I12</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="K12" s="150">
+        <f t="shared" si="0"/>
+        <v>16203.454810263158</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="226">
+        <v>3</v>
+      </c>
+      <c r="C13" s="226" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="227">
+        <v>4138.6000000000004</v>
+      </c>
+      <c r="E13" s="227">
+        <v>4138.6000000000004</v>
+      </c>
+      <c r="F13" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="229">
+        <f>F13/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="230">
+        <f>(F13/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="236">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J13" s="151">
+        <f>H34*I13</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="K13" s="150">
+        <f t="shared" si="0"/>
+        <v>13257.372117488037</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="226">
+        <v>4</v>
+      </c>
+      <c r="C14" s="226" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="227">
+        <v>8190.4</v>
+      </c>
+      <c r="E14" s="227">
+        <v>8190.4</v>
+      </c>
+      <c r="F14" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="229">
+        <f>F14/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="230">
+        <f>(F14/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="236">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J14" s="151">
+        <f>H34*I14</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="K14" s="150">
+        <f t="shared" si="0"/>
+        <v>13257.372117488037</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="226">
+        <v>4</v>
+      </c>
+      <c r="C15" s="226" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="227">
+        <v>3475.3</v>
+      </c>
+      <c r="E15" s="227">
+        <v>3475.3</v>
+      </c>
+      <c r="F15" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="229">
+        <f>F15/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="230">
+        <f>(F15/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="236">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J15" s="151">
+        <f>H34*I15</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="K15" s="150">
+        <f t="shared" si="0"/>
+        <v>16203.454810263158</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="226">
+        <v>4</v>
+      </c>
+      <c r="C16" s="226" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="227">
+        <v>4363.3</v>
+      </c>
+      <c r="E16" s="227">
+        <v>4363.3</v>
+      </c>
+      <c r="F16" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="229">
+        <f>F16/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="230">
+        <f>(F16/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="236">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J16" s="151">
+        <f>H34*I16</f>
+        <v>16203.454810263158</v>
+      </c>
+      <c r="K16" s="150">
+        <f t="shared" si="0"/>
+        <v>16203.454810263158</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="226">
+        <v>4</v>
+      </c>
+      <c r="C17" s="226" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="227">
+        <v>6036.6</v>
+      </c>
+      <c r="E17" s="227">
+        <v>6036.6</v>
+      </c>
+      <c r="F17" s="228">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="229">
+        <f>F17/F32</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="230">
+        <f>(F17/F32)*H32</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="236">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J17" s="151">
+        <f>H34*I17</f>
+        <v>13257.372117488037</v>
+      </c>
+      <c r="K17" s="150">
+        <f t="shared" si="0"/>
+        <v>13257.372117488037</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="106"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="238"/>
+      <c r="E18" s="238"/>
+      <c r="F18" s="239">
+        <f>SUM(F3:F17)</f>
+        <v>558.5</v>
+      </c>
+      <c r="G18" s="107" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="230">
+        <f>SUM(H3:H17)</f>
+        <v>197146.79893540672</v>
+      </c>
+      <c r="I18" s="106"/>
+      <c r="J18" s="240">
+        <f>SUM(J3:J17)</f>
+        <v>235686.61542200952</v>
+      </c>
+      <c r="K18" s="150">
+        <f t="shared" si="0"/>
+        <v>432833.41435741622</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="106"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="106"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="106"/>
+      <c r="H19" s="241"/>
+      <c r="K19" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="106">
+        <v>1</v>
+      </c>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="236">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="J20" s="151">
+        <f>H34*I20</f>
+        <v>1718.548237452153</v>
+      </c>
+      <c r="K20" s="150">
+        <f t="shared" si="0"/>
+        <v>1718.548237452153</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="106">
+        <v>2</v>
+      </c>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="236">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J21" s="151">
+        <f>H34*I21</f>
+        <v>1473.0413463875598</v>
+      </c>
+      <c r="K21" s="150">
+        <f t="shared" si="0"/>
+        <v>1473.0413463875598</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="106">
+        <v>3</v>
+      </c>
+      <c r="D22" s="106"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="106"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="236">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J22" s="151">
+        <f>H34*I22</f>
+        <v>1473.0413463875598</v>
+      </c>
+      <c r="K22" s="150">
+        <f t="shared" si="0"/>
+        <v>1473.0413463875598</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="106">
+        <v>4</v>
+      </c>
+      <c r="D23" s="106"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="236">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J23" s="151">
+        <f>H34*I23</f>
+        <v>1473.0413463875598</v>
+      </c>
+      <c r="K23" s="150">
+        <f t="shared" si="0"/>
+        <v>1473.0413463875598</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="106">
+        <v>5</v>
+      </c>
+      <c r="D24" s="106"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="236">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J24" s="151">
+        <f>H34*I24</f>
+        <v>1473.0413463875598</v>
+      </c>
+      <c r="K24" s="150">
+        <f t="shared" si="0"/>
+        <v>1473.0413463875598</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="106">
+        <v>6</v>
+      </c>
+      <c r="D25" s="106"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="236">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J25" s="151">
+        <f>H34*I25</f>
+        <v>736.52067319377988</v>
+      </c>
+      <c r="K25" s="150">
+        <f t="shared" si="0"/>
+        <v>736.52067319377988</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="106">
+        <v>7</v>
+      </c>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="236">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J26" s="151">
+        <f>H34*I26</f>
+        <v>736.52067319377988</v>
+      </c>
+      <c r="K26" s="150">
+        <f t="shared" si="0"/>
+        <v>736.52067319377988</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="106" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="106">
+        <v>8</v>
+      </c>
+      <c r="D27" s="106"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="236">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J27" s="151">
+        <f>H34*I27</f>
+        <v>736.52067319377988</v>
+      </c>
+      <c r="K27" s="150">
+        <f t="shared" si="0"/>
+        <v>736.52067319377988</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="109"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="109"/>
+      <c r="I28" s="107" t="s">
+        <v>151</v>
+      </c>
+      <c r="J28" s="151">
+        <f>SUM(J20:J27)</f>
+        <v>9820.2756425837306</v>
+      </c>
+      <c r="K28" s="150">
+        <f t="shared" si="0"/>
+        <v>9820.2756425837306</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F29" s="109"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="243" t="s">
+        <v>152</v>
+      </c>
+      <c r="E30" s="244"/>
+      <c r="F30" s="108">
+        <v>1254</v>
+      </c>
+      <c r="G30" s="107" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="245">
+        <v>442653.69</v>
+      </c>
+      <c r="K30" s="150">
+        <f>K18+K28</f>
+        <v>442653.68999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="110"/>
+      <c r="H31" s="246"/>
+      <c r="K31" s="247"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="243" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="244"/>
+      <c r="F32" s="239">
+        <f>SUM(F3:F17)</f>
+        <v>558.5</v>
+      </c>
+      <c r="G32" s="107" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="248">
+        <f>H30-H34</f>
+        <v>197146.79893540672</v>
+      </c>
+      <c r="K32" s="247"/>
+    </row>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="243"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="107"/>
+      <c r="H33" s="249"/>
+      <c r="K33" s="247"/>
+    </row>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="243" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" s="244"/>
+      <c r="F34" s="239">
+        <f>F30-F32</f>
+        <v>695.5</v>
+      </c>
+      <c r="G34" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="H34" s="248">
+        <f>(H30*F34)/F30</f>
+        <v>245506.89106459328</v>
+      </c>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="36" spans="4:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F36" s="250" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="251"/>
+      <c r="H36" s="252">
+        <f>H32+H33+H34</f>
+        <v>442653.69</v>
+      </c>
+    </row>
+    <row r="38" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D38" s="253" t="s">
+        <v>158</v>
+      </c>
+      <c r="E38" s="254"/>
+      <c r="F38" s="255">
+        <v>46164</v>
+      </c>
+      <c r="G38" s="255">
+        <v>46197</v>
+      </c>
+      <c r="H38" s="256" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D39" s="253" t="s">
+        <v>160</v>
+      </c>
+      <c r="E39" s="254"/>
+      <c r="F39" s="256">
+        <v>274268</v>
+      </c>
+      <c r="G39" s="256">
+        <v>275522</v>
+      </c>
+      <c r="H39" s="256">
+        <f>G39-F39</f>
+        <v>1254</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="D38:E38"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2026/SALTA 1167/Julio/SALTA1167-Julio.xlsx
+++ b/2026/SALTA 1167/Julio/SALTA1167-Julio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2247283-1D06-4607-9DAB-4B27BB113B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B0361B-C46B-4190-B490-320F17D366AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="162">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>Lect Med Edesur 01</t>
+  </si>
+  <si>
+    <t>A gaston le doble cobramos un sum erroneamente el mes pasado, corregir en agosto</t>
   </si>
 </sst>
 </file>
@@ -759,7 +762,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -832,6 +835,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -1189,7 +1198,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1462,117 +1471,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="8" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1649,48 +1547,164 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2125,12 +2139,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
-      <c r="B3" s="176" t="s">
+      <c r="B3" s="221" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="177"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="222"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -2168,49 +2182,49 @@
       <c r="E6" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="179" t="s">
+      <c r="B8" s="224" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="179"/>
+      <c r="C8" s="224"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="179"/>
-      <c r="C9" s="179"/>
+      <c r="B9" s="224"/>
+      <c r="C9" s="224"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="179"/>
-      <c r="C10" s="179"/>
+      <c r="B10" s="224"/>
+      <c r="C10" s="224"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="178" t="s">
+      <c r="A13" s="223" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="178"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="178"/>
-      <c r="E13" s="178"/>
+      <c r="B13" s="223"/>
+      <c r="C13" s="223"/>
+      <c r="D13" s="223"/>
+      <c r="E13" s="223"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="178"/>
-      <c r="B14" s="178"/>
-      <c r="C14" s="178"/>
-      <c r="D14" s="178"/>
-      <c r="E14" s="178"/>
+      <c r="A14" s="223"/>
+      <c r="B14" s="223"/>
+      <c r="C14" s="223"/>
+      <c r="D14" s="223"/>
+      <c r="E14" s="223"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="178"/>
-      <c r="B15" s="178"/>
-      <c r="C15" s="178"/>
-      <c r="D15" s="178"/>
-      <c r="E15" s="178"/>
+      <c r="A15" s="223"/>
+      <c r="B15" s="223"/>
+      <c r="C15" s="223"/>
+      <c r="D15" s="223"/>
+      <c r="E15" s="223"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="178"/>
-      <c r="B16" s="178"/>
-      <c r="C16" s="178"/>
-      <c r="D16" s="178"/>
-      <c r="E16" s="178"/>
+      <c r="A16" s="223"/>
+      <c r="B16" s="223"/>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2236,12 +2250,12 @@
       <c r="E21" s="93"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="174" t="s">
+      <c r="A22" s="217" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="175"/>
+      <c r="B22" s="218"/>
       <c r="C22" s="152"/>
-      <c r="D22" s="209">
+      <c r="D22" s="172">
         <v>510846.85</v>
       </c>
       <c r="E22" s="146" t="s">
@@ -2250,10 +2264,10 @@
       <c r="H22" s="82"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="174"/>
-      <c r="B23" s="175"/>
+      <c r="A23" s="217"/>
+      <c r="B23" s="218"/>
       <c r="C23" s="152"/>
-      <c r="D23" s="209"/>
+      <c r="D23" s="172"/>
       <c r="E23" s="94"/>
       <c r="H23" s="82"/>
     </row>
@@ -2263,7 +2277,7 @@
       </c>
       <c r="B24" s="153"/>
       <c r="C24" s="153"/>
-      <c r="D24" s="210"/>
+      <c r="D24" s="173"/>
       <c r="E24" s="137">
         <f>SUM(D22:D23)</f>
         <v>510846.85</v>
@@ -2275,16 +2289,16 @@
       </c>
       <c r="B25" s="153"/>
       <c r="C25" s="153"/>
-      <c r="D25" s="211"/>
+      <c r="D25" s="174"/>
       <c r="E25" s="138"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="174" t="s">
+      <c r="A26" s="217" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="175"/>
+      <c r="B26" s="218"/>
       <c r="C26" s="155"/>
-      <c r="D26" s="212">
+      <c r="D26" s="175">
         <v>79864</v>
       </c>
       <c r="E26" s="96" t="s">
@@ -2297,7 +2311,7 @@
       </c>
       <c r="B27" s="153"/>
       <c r="C27" s="153"/>
-      <c r="D27" s="210"/>
+      <c r="D27" s="173"/>
       <c r="E27" s="104">
         <f>SUM(D26:D26)</f>
         <v>79864</v>
@@ -2309,7 +2323,7 @@
       </c>
       <c r="B28" s="156"/>
       <c r="C28" s="156"/>
-      <c r="D28" s="213"/>
+      <c r="D28" s="176"/>
       <c r="E28" s="139"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2318,7 +2332,7 @@
       </c>
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
-      <c r="D29" s="214">
+      <c r="D29" s="177">
         <v>162387.66</v>
       </c>
       <c r="E29" s="96" t="s">
@@ -2331,7 +2345,7 @@
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
-      <c r="D30" s="214">
+      <c r="D30" s="177">
         <v>7090.36</v>
       </c>
       <c r="E30" s="146" t="str">
@@ -2345,7 +2359,7 @@
       </c>
       <c r="B31" s="157"/>
       <c r="C31" s="65"/>
-      <c r="D31" s="214">
+      <c r="D31" s="177">
         <v>482288.43</v>
       </c>
       <c r="E31" s="96" t="s">
@@ -2353,12 +2367,12 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="172" t="s">
+      <c r="A32" s="219" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="173"/>
+      <c r="B32" s="220"/>
       <c r="C32" s="65"/>
-      <c r="D32" s="214">
+      <c r="D32" s="177">
         <v>632390</v>
       </c>
       <c r="E32" s="96" t="s">
@@ -2371,7 +2385,7 @@
       </c>
       <c r="B33" s="159"/>
       <c r="C33" s="65"/>
-      <c r="D33" s="214">
+      <c r="D33" s="177">
         <v>27338.01</v>
       </c>
       <c r="E33" s="96" t="s">
@@ -2384,7 +2398,7 @@
       </c>
       <c r="B34" s="153"/>
       <c r="C34" s="153"/>
-      <c r="D34" s="215"/>
+      <c r="D34" s="178"/>
       <c r="E34" s="140">
         <f>SUM(D29:D33)</f>
         <v>1311494.46</v>
@@ -2394,16 +2408,16 @@
       <c r="A35" s="154"/>
       <c r="B35" s="153"/>
       <c r="C35" s="153"/>
-      <c r="D35" s="210"/>
+      <c r="D35" s="173"/>
       <c r="E35" s="141"/>
     </row>
     <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="174" t="s">
+      <c r="A36" s="217" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="175"/>
+      <c r="B36" s="218"/>
       <c r="C36" s="65"/>
-      <c r="D36" s="214">
+      <c r="D36" s="177">
         <v>82000</v>
       </c>
       <c r="E36" s="96" t="s">
@@ -2416,7 +2430,7 @@
       </c>
       <c r="B37" s="161"/>
       <c r="C37" s="65"/>
-      <c r="D37" s="214">
+      <c r="D37" s="177">
         <f>199530</f>
         <v>199530</v>
       </c>
@@ -2425,12 +2439,12 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="174" t="s">
+      <c r="A38" s="217" t="s">
         <v>141</v>
       </c>
-      <c r="B38" s="175"/>
+      <c r="B38" s="218"/>
       <c r="C38" s="65"/>
-      <c r="D38" s="216">
+      <c r="D38" s="179">
         <v>72635</v>
       </c>
       <c r="E38" s="96" t="s">
@@ -2438,23 +2452,23 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="174" t="s">
+      <c r="A39" s="217" t="s">
         <v>134</v>
       </c>
-      <c r="B39" s="175"/>
+      <c r="B39" s="218"/>
       <c r="C39" s="65"/>
-      <c r="D39" s="216">
+      <c r="D39" s="179">
         <v>157988.29</v>
       </c>
       <c r="E39" s="96"/>
     </row>
     <row r="40" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="174" t="s">
+      <c r="A40" s="217" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="175"/>
+      <c r="B40" s="218"/>
       <c r="C40" s="65"/>
-      <c r="D40" s="216">
+      <c r="D40" s="179">
         <v>8000</v>
       </c>
       <c r="E40" s="96" t="s">
@@ -2479,16 +2493,16 @@
       </c>
       <c r="B42" s="154"/>
       <c r="C42" s="154"/>
-      <c r="D42" s="217"/>
+      <c r="D42" s="180"/>
       <c r="E42" s="142"/>
     </row>
     <row r="43" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="174" t="s">
+      <c r="A43" s="217" t="s">
         <v>128</v>
       </c>
-      <c r="B43" s="175"/>
+      <c r="B43" s="218"/>
       <c r="C43" s="152"/>
-      <c r="D43" s="218">
+      <c r="D43" s="181">
         <v>190000</v>
       </c>
       <c r="E43" s="143" t="s">
@@ -2501,7 +2515,7 @@
       </c>
       <c r="B44" s="153"/>
       <c r="C44" s="153"/>
-      <c r="D44" s="210"/>
+      <c r="D44" s="173"/>
       <c r="E44" s="137">
         <f>SUM(D43:D43)</f>
         <v>190000</v>
@@ -2513,7 +2527,7 @@
       </c>
       <c r="B45" s="162"/>
       <c r="C45" s="153"/>
-      <c r="D45" s="219"/>
+      <c r="D45" s="182"/>
       <c r="E45" s="104"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2522,7 +2536,7 @@
       </c>
       <c r="B46" s="65"/>
       <c r="C46" s="65"/>
-      <c r="D46" s="214">
+      <c r="D46" s="177">
         <v>0</v>
       </c>
       <c r="E46" s="144"/>
@@ -2533,7 +2547,7 @@
       </c>
       <c r="B47" s="65"/>
       <c r="C47" s="65"/>
-      <c r="D47" s="214">
+      <c r="D47" s="177">
         <v>44926.11</v>
       </c>
       <c r="E47" s="145"/>
@@ -2544,7 +2558,7 @@
       </c>
       <c r="B48" s="163"/>
       <c r="C48" s="163"/>
-      <c r="D48" s="220"/>
+      <c r="D48" s="183"/>
       <c r="E48" s="104">
         <f>SUM(D46:D47)</f>
         <v>44926.11</v>
@@ -2554,7 +2568,7 @@
       <c r="A49" s="65"/>
       <c r="B49" s="65"/>
       <c r="C49" s="65"/>
-      <c r="D49" s="221"/>
+      <c r="D49" s="184"/>
       <c r="E49" s="70"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -2620,8 +2634,8 @@
       <c r="E56" s="66"/>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="182"/>
-      <c r="B57" s="182"/>
+      <c r="A57" s="216"/>
+      <c r="B57" s="216"/>
       <c r="C57" s="65"/>
       <c r="D57" s="95"/>
       <c r="E57" s="66"/>
@@ -2870,16 +2884,16 @@
     </row>
     <row r="91" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="181" t="s">
+      <c r="A92" s="215" t="s">
         <v>18</v>
       </c>
-      <c r="B92" s="181"/>
-      <c r="C92" s="181"/>
+      <c r="B92" s="215"/>
+      <c r="C92" s="215"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="181"/>
-      <c r="B93" s="181"/>
-      <c r="C93" s="181"/>
+      <c r="A93" s="215"/>
+      <c r="B93" s="215"/>
+      <c r="C93" s="215"/>
     </row>
     <row r="94" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="79"/>
@@ -2909,35 +2923,42 @@
       <c r="M97" s="5"/>
     </row>
     <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="180"/>
-      <c r="B98" s="180"/>
-      <c r="C98" s="180"/>
-      <c r="D98" s="180"/>
-      <c r="E98" s="180"/>
+      <c r="A98" s="214"/>
+      <c r="B98" s="214"/>
+      <c r="C98" s="214"/>
+      <c r="D98" s="214"/>
+      <c r="E98" s="214"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="180"/>
-      <c r="B99" s="180"/>
-      <c r="C99" s="180"/>
-      <c r="D99" s="180"/>
-      <c r="E99" s="180"/>
+      <c r="A99" s="214"/>
+      <c r="B99" s="214"/>
+      <c r="C99" s="214"/>
+      <c r="D99" s="214"/>
+      <c r="E99" s="214"/>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="180"/>
-      <c r="B100" s="180"/>
-      <c r="C100" s="180"/>
-      <c r="D100" s="180"/>
-      <c r="E100" s="180"/>
+      <c r="A100" s="214"/>
+      <c r="B100" s="214"/>
+      <c r="C100" s="214"/>
+      <c r="D100" s="214"/>
+      <c r="E100" s="214"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="180"/>
-      <c r="B101" s="180"/>
-      <c r="C101" s="180"/>
-      <c r="D101" s="180"/>
-      <c r="E101" s="180"/>
+      <c r="A101" s="214"/>
+      <c r="B101" s="214"/>
+      <c r="C101" s="214"/>
+      <c r="D101" s="214"/>
+      <c r="E101" s="214"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A98:E101"/>
     <mergeCell ref="A92:C93"/>
     <mergeCell ref="A57:B57"/>
@@ -2946,13 +2967,6 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2990,16 +3004,16 @@
       <c r="B1" s="113"/>
       <c r="C1" s="114"/>
       <c r="D1" s="114"/>
-      <c r="E1" s="183"/>
-      <c r="F1" s="183"/>
-      <c r="G1" s="183"/>
-      <c r="H1" s="183"/>
-      <c r="I1" s="183"/>
-      <c r="J1" s="183"/>
-      <c r="K1" s="183"/>
-      <c r="L1" s="183"/>
-      <c r="M1" s="183"/>
-      <c r="N1" s="183"/>
+      <c r="E1" s="230"/>
+      <c r="F1" s="230"/>
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="230"/>
+      <c r="M1" s="230"/>
+      <c r="N1" s="230"/>
       <c r="O1" s="113"/>
       <c r="P1" s="115"/>
     </row>
@@ -3050,209 +3064,209 @@
       <c r="Q3" s="19"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="194" t="s">
+      <c r="A4" s="237" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="195"/>
-      <c r="K4" s="195"/>
-      <c r="L4" s="195"/>
-      <c r="M4" s="195"/>
-      <c r="N4" s="195"/>
-      <c r="O4" s="195"/>
-      <c r="P4" s="196"/>
+      <c r="B4" s="238"/>
+      <c r="C4" s="238"/>
+      <c r="D4" s="238"/>
+      <c r="E4" s="238"/>
+      <c r="F4" s="238"/>
+      <c r="G4" s="238"/>
+      <c r="H4" s="238"/>
+      <c r="I4" s="238"/>
+      <c r="J4" s="238"/>
+      <c r="K4" s="238"/>
+      <c r="L4" s="238"/>
+      <c r="M4" s="238"/>
+      <c r="N4" s="238"/>
+      <c r="O4" s="238"/>
+      <c r="P4" s="239"/>
       <c r="Q4" s="19"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="197"/>
-      <c r="B5" s="198"/>
-      <c r="C5" s="198"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="198"/>
-      <c r="G5" s="198"/>
-      <c r="H5" s="198"/>
-      <c r="I5" s="198"/>
-      <c r="J5" s="198"/>
-      <c r="K5" s="198"/>
-      <c r="L5" s="198"/>
-      <c r="M5" s="198"/>
-      <c r="N5" s="198"/>
-      <c r="O5" s="198"/>
-      <c r="P5" s="199"/>
+      <c r="A5" s="240"/>
+      <c r="B5" s="241"/>
+      <c r="C5" s="241"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="M5" s="241"/>
+      <c r="N5" s="241"/>
+      <c r="O5" s="241"/>
+      <c r="P5" s="242"/>
       <c r="Q5" s="19"/>
     </row>
     <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="197"/>
-      <c r="B6" s="198"/>
-      <c r="C6" s="198"/>
-      <c r="D6" s="198"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="198"/>
-      <c r="G6" s="198"/>
-      <c r="H6" s="198"/>
-      <c r="I6" s="198"/>
-      <c r="J6" s="198"/>
-      <c r="K6" s="198"/>
-      <c r="L6" s="198"/>
-      <c r="M6" s="198"/>
-      <c r="N6" s="198"/>
-      <c r="O6" s="198"/>
-      <c r="P6" s="199"/>
+      <c r="A6" s="240"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="241"/>
+      <c r="D6" s="241"/>
+      <c r="E6" s="241"/>
+      <c r="F6" s="241"/>
+      <c r="G6" s="241"/>
+      <c r="H6" s="241"/>
+      <c r="I6" s="241"/>
+      <c r="J6" s="241"/>
+      <c r="K6" s="241"/>
+      <c r="L6" s="241"/>
+      <c r="M6" s="241"/>
+      <c r="N6" s="241"/>
+      <c r="O6" s="241"/>
+      <c r="P6" s="242"/>
       <c r="Q6" s="19"/>
     </row>
     <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197"/>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="198"/>
-      <c r="H7" s="198"/>
-      <c r="I7" s="198"/>
-      <c r="J7" s="198"/>
-      <c r="K7" s="198"/>
-      <c r="L7" s="198"/>
-      <c r="M7" s="198"/>
-      <c r="N7" s="198"/>
-      <c r="O7" s="198"/>
-      <c r="P7" s="199"/>
+      <c r="A7" s="240"/>
+      <c r="B7" s="241"/>
+      <c r="C7" s="241"/>
+      <c r="D7" s="241"/>
+      <c r="E7" s="241"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="241"/>
+      <c r="I7" s="241"/>
+      <c r="J7" s="241"/>
+      <c r="K7" s="241"/>
+      <c r="L7" s="241"/>
+      <c r="M7" s="241"/>
+      <c r="N7" s="241"/>
+      <c r="O7" s="241"/>
+      <c r="P7" s="242"/>
       <c r="Q7" s="19"/>
     </row>
     <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="200"/>
-      <c r="B8" s="201"/>
-      <c r="C8" s="201"/>
-      <c r="D8" s="201"/>
-      <c r="E8" s="201"/>
-      <c r="F8" s="201"/>
-      <c r="G8" s="201"/>
-      <c r="H8" s="201"/>
-      <c r="I8" s="201"/>
-      <c r="J8" s="201"/>
-      <c r="K8" s="201"/>
-      <c r="L8" s="201"/>
-      <c r="M8" s="201"/>
-      <c r="N8" s="201"/>
-      <c r="O8" s="201"/>
-      <c r="P8" s="202"/>
+      <c r="A8" s="243"/>
+      <c r="B8" s="244"/>
+      <c r="C8" s="244"/>
+      <c r="D8" s="244"/>
+      <c r="E8" s="244"/>
+      <c r="F8" s="244"/>
+      <c r="G8" s="244"/>
+      <c r="H8" s="244"/>
+      <c r="I8" s="244"/>
+      <c r="J8" s="244"/>
+      <c r="K8" s="244"/>
+      <c r="L8" s="244"/>
+      <c r="M8" s="244"/>
+      <c r="N8" s="244"/>
+      <c r="O8" s="244"/>
+      <c r="P8" s="245"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="205" t="s">
+      <c r="A9" s="248" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="206"/>
-      <c r="C9" s="206"/>
-      <c r="D9" s="206"/>
-      <c r="E9" s="206"/>
-      <c r="F9" s="206"/>
-      <c r="G9" s="206"/>
-      <c r="H9" s="206"/>
-      <c r="I9" s="206"/>
-      <c r="J9" s="206"/>
-      <c r="K9" s="206"/>
-      <c r="L9" s="206"/>
-      <c r="M9" s="206"/>
-      <c r="N9" s="206"/>
-      <c r="O9" s="206"/>
-      <c r="P9" s="206"/>
+      <c r="B9" s="249"/>
+      <c r="C9" s="249"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
+      <c r="M9" s="249"/>
+      <c r="N9" s="249"/>
+      <c r="O9" s="249"/>
+      <c r="P9" s="249"/>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="207" t="s">
+      <c r="A10" s="250" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="207"/>
-      <c r="C10" s="207"/>
-      <c r="D10" s="207"/>
-      <c r="E10" s="207"/>
-      <c r="F10" s="207"/>
-      <c r="G10" s="207"/>
-      <c r="H10" s="207"/>
-      <c r="I10" s="207"/>
-      <c r="J10" s="207"/>
-      <c r="K10" s="207"/>
-      <c r="L10" s="207"/>
-      <c r="M10" s="207"/>
-      <c r="N10" s="207"/>
-      <c r="O10" s="207"/>
-      <c r="P10" s="207"/>
+      <c r="B10" s="250"/>
+      <c r="C10" s="250"/>
+      <c r="D10" s="250"/>
+      <c r="E10" s="250"/>
+      <c r="F10" s="250"/>
+      <c r="G10" s="250"/>
+      <c r="H10" s="250"/>
+      <c r="I10" s="250"/>
+      <c r="J10" s="250"/>
+      <c r="K10" s="250"/>
+      <c r="L10" s="250"/>
+      <c r="M10" s="250"/>
+      <c r="N10" s="250"/>
+      <c r="O10" s="250"/>
+      <c r="P10" s="250"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="188" t="s">
+      <c r="A11" s="225" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="101"/>
-      <c r="C11" s="188" t="s">
+      <c r="C11" s="225" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="188" t="s">
+      <c r="D11" s="225" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="188" t="s">
+      <c r="E11" s="225" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="184" t="s">
+      <c r="F11" s="228" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="188" t="s">
+      <c r="G11" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="190" t="s">
+      <c r="H11" s="233" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="184" t="s">
+      <c r="I11" s="228" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="184" t="s">
+      <c r="J11" s="228" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="192" t="s">
+      <c r="K11" s="235" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="184" t="s">
+      <c r="L11" s="228" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="184" t="s">
+      <c r="M11" s="228" t="s">
         <v>123</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="186" t="s">
+      <c r="O11" s="231" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="203" t="s">
+      <c r="P11" s="246" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="189"/>
+      <c r="A12" s="227"/>
       <c r="B12" s="102"/>
-      <c r="C12" s="189"/>
-      <c r="D12" s="208"/>
-      <c r="E12" s="189"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="189"/>
-      <c r="H12" s="191"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="193"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
+      <c r="C12" s="227"/>
+      <c r="D12" s="226"/>
+      <c r="E12" s="227"/>
+      <c r="F12" s="229"/>
+      <c r="G12" s="227"/>
+      <c r="H12" s="234"/>
+      <c r="I12" s="229"/>
+      <c r="J12" s="229"/>
+      <c r="K12" s="236"/>
+      <c r="L12" s="229"/>
+      <c r="M12" s="229"/>
       <c r="N12" s="37" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/08</v>
       </c>
-      <c r="O12" s="187"/>
-      <c r="P12" s="204"/>
+      <c r="O12" s="232"/>
+      <c r="P12" s="247"/>
     </row>
     <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
@@ -3271,7 +3285,7 @@
       <c r="F13" s="49">
         <v>324000.01</v>
       </c>
-      <c r="G13" s="222">
+      <c r="G13" s="185">
         <f>356868.01-G29-G30</f>
         <v>324009.66000000003</v>
       </c>
@@ -3329,7 +3343,7 @@
       <c r="F14" s="50">
         <v>280517.02</v>
       </c>
-      <c r="G14" s="222">
+      <c r="G14" s="185">
         <v>281000</v>
       </c>
       <c r="H14" s="129">
@@ -3389,7 +3403,7 @@
       <c r="F15" s="49">
         <v>149456.03</v>
       </c>
-      <c r="G15" s="222">
+      <c r="G15" s="185">
         <f>F15</f>
         <v>149456.03</v>
       </c>
@@ -3450,7 +3464,7 @@
       <c r="F16" s="49">
         <v>172600.04</v>
       </c>
-      <c r="G16" s="222">
+      <c r="G16" s="185">
         <f>189033-G32</f>
         <v>172603.8</v>
       </c>
@@ -3511,7 +3525,7 @@
       <c r="F17" s="50">
         <v>178200.05</v>
       </c>
-      <c r="G17" s="222">
+      <c r="G17" s="185">
         <f>F17</f>
         <v>178200.05</v>
       </c>
@@ -3577,7 +3591,7 @@
       <c r="F18" s="49">
         <v>156924.06</v>
       </c>
-      <c r="G18" s="222">
+      <c r="G18" s="185">
         <v>129600.06</v>
       </c>
       <c r="H18" s="51">
@@ -3637,7 +3651,7 @@
       <c r="F19" s="50">
         <v>279288.07</v>
       </c>
-      <c r="G19" s="222">
+      <c r="G19" s="185">
         <f>F19</f>
         <v>279288.07</v>
       </c>
@@ -3698,7 +3712,7 @@
       <c r="F20" s="50">
         <v>248675.08</v>
       </c>
-      <c r="G20" s="222">
+      <c r="G20" s="185">
         <f>F20</f>
         <v>248675.08</v>
       </c>
@@ -3741,16 +3755,16 @@
       </c>
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="40">
+      <c r="A21" s="257">
         <v>9</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="257" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="257" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D21" s="258" t="s">
         <v>72</v>
       </c>
       <c r="E21" s="48">
@@ -3759,7 +3773,7 @@
       <c r="F21" s="49">
         <v>199813.09</v>
       </c>
-      <c r="G21" s="222">
+      <c r="G21" s="185">
         <f>F21+12187.9</f>
         <v>212000.99</v>
       </c>
@@ -3784,19 +3798,19 @@
         <v>16203.454810263158</v>
       </c>
       <c r="M21" s="148">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="N21" s="133">
         <f t="shared" si="4"/>
-        <v>232216.09</v>
+        <v>182216.09</v>
       </c>
       <c r="O21" s="52">
         <f t="shared" si="5"/>
-        <v>246149.09</v>
+        <v>193149.09</v>
       </c>
       <c r="P21" s="53">
         <f t="shared" si="6"/>
-        <v>239182.09</v>
+        <v>187682.09</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="7"/>
@@ -3822,7 +3836,7 @@
       <c r="F22" s="49">
         <v>16198.1</v>
       </c>
-      <c r="G22" s="222">
+      <c r="G22" s="185">
         <f>RESUMEN!D39+16198.1-12187.9</f>
         <v>161998.49000000002</v>
       </c>
@@ -3881,7 +3895,7 @@
       <c r="F23" s="49">
         <v>145800.10999999999</v>
       </c>
-      <c r="G23" s="222">
+      <c r="G23" s="185">
         <f>154014.33-G34</f>
         <v>145800.10999999999</v>
       </c>
@@ -3945,7 +3959,7 @@
       <c r="F24" s="49">
         <v>178200.12</v>
       </c>
-      <c r="G24" s="222">
+      <c r="G24" s="185">
         <f>F24</f>
         <v>178200.12</v>
       </c>
@@ -4006,7 +4020,7 @@
       <c r="F25" s="49">
         <v>173579.13</v>
       </c>
-      <c r="G25" s="222">
+      <c r="G25" s="185">
         <f>F25</f>
         <v>173579.13</v>
       </c>
@@ -4065,7 +4079,7 @@
       <c r="F26" s="50">
         <v>150174.14000000001</v>
       </c>
-      <c r="G26" s="222">
+      <c r="G26" s="185">
         <v>150174.14000000001</v>
       </c>
       <c r="H26" s="129">
@@ -4123,7 +4137,7 @@
       <c r="F27" s="49">
         <v>145800.15</v>
       </c>
-      <c r="G27" s="222">
+      <c r="G27" s="185">
         <f>F27</f>
         <v>145800.15</v>
       </c>
@@ -4184,7 +4198,7 @@
       <c r="F28" s="49">
         <v>20609.16</v>
       </c>
-      <c r="G28" s="222">
+      <c r="G28" s="185">
         <v>16800.16</v>
       </c>
       <c r="H28" s="51">
@@ -4242,7 +4256,7 @@
       <c r="F29" s="50">
         <v>16429.169999999998</v>
       </c>
-      <c r="G29" s="222">
+      <c r="G29" s="185">
         <f>F29</f>
         <v>16429.169999999998</v>
       </c>
@@ -4301,7 +4315,7 @@
       <c r="F30" s="49">
         <v>16429.18</v>
       </c>
-      <c r="G30" s="222">
+      <c r="G30" s="185">
         <f>F30</f>
         <v>16429.18</v>
       </c>
@@ -4360,7 +4374,7 @@
       <c r="F31" s="50">
         <v>16429.189999999999</v>
       </c>
-      <c r="G31" s="222">
+      <c r="G31" s="185">
         <f>F31</f>
         <v>16429.189999999999</v>
       </c>
@@ -4418,7 +4432,7 @@
       <c r="F32" s="56">
         <v>16429.2</v>
       </c>
-      <c r="G32" s="222">
+      <c r="G32" s="185">
         <f>F32</f>
         <v>16429.2</v>
       </c>
@@ -4476,7 +4490,7 @@
       <c r="F33" s="56">
         <v>8214.2099999999991</v>
       </c>
-      <c r="G33" s="222">
+      <c r="G33" s="185">
         <f>F33</f>
         <v>8214.2099999999991</v>
       </c>
@@ -4532,7 +4546,7 @@
       <c r="F34" s="56">
         <v>8214.2199999999993</v>
       </c>
-      <c r="G34" s="223">
+      <c r="G34" s="186">
         <f t="shared" ref="G34" si="9">F34</f>
         <v>8214.2199999999993</v>
       </c>
@@ -4590,7 +4604,7 @@
       <c r="F35" s="56">
         <v>8214.23</v>
       </c>
-      <c r="G35" s="222">
+      <c r="G35" s="185">
         <f>F35</f>
         <v>8214.23</v>
       </c>
@@ -4669,15 +4683,15 @@
       <c r="M36" s="61"/>
       <c r="N36" s="61">
         <f>SUM(N13:N35)</f>
-        <v>3066236.7600000012</v>
+        <v>3016236.7600000012</v>
       </c>
       <c r="O36" s="61">
         <f t="shared" si="10"/>
-        <v>3184643.7100000004</v>
+        <v>3131643.7100000004</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P13:P35)</f>
-        <v>3158223.7600000007</v>
+        <v>3106723.7600000012</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4686,100 +4700,94 @@
     </row>
     <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="180" t="str">
+      <c r="C39" s="214" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="180"/>
-      <c r="E39" s="180"/>
-      <c r="F39" s="180"/>
-      <c r="G39" s="180"/>
-      <c r="H39" s="180"/>
-      <c r="I39" s="180"/>
-      <c r="J39" s="180"/>
-      <c r="K39" s="180"/>
-      <c r="L39" s="180"/>
-      <c r="M39" s="180"/>
-      <c r="N39" s="180"/>
+      <c r="D39" s="214"/>
+      <c r="E39" s="214"/>
+      <c r="F39" s="214"/>
+      <c r="G39" s="214"/>
+      <c r="H39" s="214"/>
+      <c r="I39" s="214"/>
+      <c r="J39" s="214"/>
+      <c r="K39" s="214"/>
+      <c r="L39" s="214"/>
+      <c r="M39" s="214"/>
+      <c r="N39" s="214"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="180"/>
-      <c r="D40" s="180"/>
-      <c r="E40" s="180"/>
-      <c r="F40" s="180"/>
-      <c r="G40" s="180"/>
-      <c r="H40" s="180"/>
-      <c r="I40" s="180"/>
-      <c r="J40" s="180"/>
-      <c r="K40" s="180"/>
-      <c r="L40" s="180"/>
-      <c r="M40" s="180"/>
-      <c r="N40" s="180"/>
+      <c r="C40" s="214"/>
+      <c r="D40" s="214"/>
+      <c r="E40" s="214"/>
+      <c r="F40" s="214"/>
+      <c r="G40" s="214"/>
+      <c r="H40" s="214"/>
+      <c r="I40" s="214"/>
+      <c r="J40" s="214"/>
+      <c r="K40" s="214"/>
+      <c r="L40" s="214"/>
+      <c r="M40" s="214"/>
+      <c r="N40" s="214"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="180"/>
-      <c r="D41" s="180"/>
-      <c r="E41" s="180"/>
-      <c r="F41" s="180"/>
-      <c r="G41" s="180"/>
-      <c r="H41" s="180"/>
-      <c r="I41" s="180"/>
-      <c r="J41" s="180"/>
-      <c r="K41" s="180"/>
-      <c r="L41" s="180"/>
-      <c r="M41" s="180"/>
-      <c r="N41" s="180"/>
+      <c r="C41" s="214"/>
+      <c r="D41" s="214"/>
+      <c r="E41" s="214"/>
+      <c r="F41" s="214"/>
+      <c r="G41" s="214"/>
+      <c r="H41" s="214"/>
+      <c r="I41" s="214"/>
+      <c r="J41" s="214"/>
+      <c r="K41" s="214"/>
+      <c r="L41" s="214"/>
+      <c r="M41" s="214"/>
+      <c r="N41" s="214"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="180"/>
-      <c r="D42" s="180"/>
-      <c r="E42" s="180"/>
-      <c r="F42" s="180"/>
-      <c r="G42" s="180"/>
-      <c r="H42" s="180"/>
-      <c r="I42" s="180"/>
-      <c r="J42" s="180"/>
-      <c r="K42" s="180"/>
-      <c r="L42" s="180"/>
-      <c r="M42" s="180"/>
-      <c r="N42" s="180"/>
+      <c r="C42" s="214"/>
+      <c r="D42" s="214"/>
+      <c r="E42" s="214"/>
+      <c r="F42" s="214"/>
+      <c r="G42" s="214"/>
+      <c r="H42" s="214"/>
+      <c r="I42" s="214"/>
+      <c r="J42" s="214"/>
+      <c r="K42" s="214"/>
+      <c r="L42" s="214"/>
+      <c r="M42" s="214"/>
+      <c r="N42" s="214"/>
     </row>
     <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="180"/>
-      <c r="D43" s="180"/>
-      <c r="E43" s="180"/>
-      <c r="F43" s="180"/>
-      <c r="G43" s="180"/>
-      <c r="H43" s="180"/>
-      <c r="I43" s="180"/>
-      <c r="J43" s="180"/>
-      <c r="K43" s="180"/>
-      <c r="L43" s="180"/>
-      <c r="M43" s="180"/>
-      <c r="N43" s="180"/>
+      <c r="C43" s="214"/>
+      <c r="D43" s="214"/>
+      <c r="E43" s="214"/>
+      <c r="F43" s="214"/>
+      <c r="G43" s="214"/>
+      <c r="H43" s="214"/>
+      <c r="I43" s="214"/>
+      <c r="J43" s="214"/>
+      <c r="K43" s="214"/>
+      <c r="L43" s="214"/>
+      <c r="M43" s="214"/>
+      <c r="N43" s="214"/>
     </row>
     <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="180"/>
-      <c r="D44" s="180"/>
-      <c r="E44" s="180"/>
-      <c r="F44" s="180"/>
-      <c r="G44" s="180"/>
-      <c r="H44" s="180"/>
-      <c r="I44" s="180"/>
-      <c r="J44" s="180"/>
-      <c r="K44" s="180"/>
-      <c r="L44" s="180"/>
-      <c r="M44" s="180"/>
-      <c r="N44" s="180"/>
+      <c r="C44" s="214"/>
+      <c r="D44" s="214"/>
+      <c r="E44" s="214"/>
+      <c r="F44" s="214"/>
+      <c r="G44" s="214"/>
+      <c r="H44" s="214"/>
+      <c r="I44" s="214"/>
+      <c r="J44" s="214"/>
+      <c r="K44" s="214"/>
+      <c r="L44" s="214"/>
+      <c r="M44" s="214"/>
+      <c r="N44" s="214"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4793,6 +4801,12 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4801,9 +4815,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
-  <dimension ref="A1"/>
+  <dimension ref="C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="259" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4817,13 +4837,13 @@
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="242" customWidth="1"/>
-    <col min="6" max="6" width="13" style="242" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" style="242" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="242" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="205" customWidth="1"/>
+    <col min="6" max="6" width="13" style="205" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="205" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="205" customWidth="1"/>
     <col min="9" max="9" width="11.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="242" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="205" customWidth="1"/>
     <col min="12" max="12" width="2.7109375" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -4835,10 +4855,10 @@
       <c r="C2" s="106" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="224" t="s">
+      <c r="D2" s="187" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="224" t="s">
+      <c r="E2" s="187" t="s">
         <v>144</v>
       </c>
       <c r="F2" s="106" t="s">
@@ -4851,7 +4871,7 @@
         <v>147</v>
       </c>
       <c r="I2" s="106"/>
-      <c r="J2" s="225" t="s">
+      <c r="J2" s="188" t="s">
         <v>148</v>
       </c>
       <c r="K2" s="107" t="s">
@@ -4859,31 +4879,31 @@
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="226">
+      <c r="B3" s="189">
         <v>1</v>
       </c>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="189" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="227">
+      <c r="D3" s="190">
         <v>8687.5</v>
       </c>
-      <c r="E3" s="227">
+      <c r="E3" s="190">
         <v>8687.5</v>
       </c>
-      <c r="F3" s="228">
+      <c r="F3" s="191">
         <f>(E3-D3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="229">
+      <c r="G3" s="192">
         <f>F3/F32</f>
         <v>0</v>
       </c>
-      <c r="H3" s="230">
+      <c r="H3" s="193">
         <f>(F3/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I3" s="231">
+      <c r="I3" s="194">
         <v>0.12</v>
       </c>
       <c r="J3" s="151">
@@ -4896,31 +4916,31 @@
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="232">
+      <c r="B4" s="195">
         <v>1</v>
       </c>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="195" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="233">
+      <c r="D4" s="196">
         <v>4488.6000000000004</v>
       </c>
-      <c r="E4" s="233">
+      <c r="E4" s="196">
         <v>4865.1000000000004</v>
       </c>
-      <c r="F4" s="234">
+      <c r="F4" s="197">
         <f>(E4-D4)</f>
         <v>376.5</v>
       </c>
-      <c r="G4" s="235">
+      <c r="G4" s="198">
         <f>F4/F32</f>
         <v>0.67412712623097581</v>
       </c>
-      <c r="H4" s="230">
+      <c r="H4" s="193">
         <f>(F4/F32)*H32</f>
         <v>132902.00501196174</v>
       </c>
-      <c r="I4" s="236">
+      <c r="I4" s="199">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J4" s="151">
@@ -4933,31 +4953,31 @@
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="232">
+      <c r="B5" s="195">
         <v>1</v>
       </c>
-      <c r="C5" s="232" t="s">
+      <c r="C5" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="227">
+      <c r="D5" s="190">
         <v>2366.38</v>
       </c>
-      <c r="E5" s="227">
+      <c r="E5" s="190">
         <v>2366.38</v>
       </c>
-      <c r="F5" s="228">
+      <c r="F5" s="191">
         <f t="shared" ref="F5:F17" si="1">(E5-D5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="229">
+      <c r="G5" s="192">
         <f>F5/F32</f>
         <v>0</v>
       </c>
-      <c r="H5" s="230">
+      <c r="H5" s="193">
         <f>(F5/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I5" s="236">
+      <c r="I5" s="199">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J5" s="151">
@@ -4970,31 +4990,31 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="226">
+      <c r="B6" s="189">
         <v>2</v>
       </c>
-      <c r="C6" s="226" t="s">
+      <c r="C6" s="189" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="227">
+      <c r="D6" s="190">
         <v>3731.1</v>
       </c>
-      <c r="E6" s="227">
+      <c r="E6" s="190">
         <v>3731.1</v>
       </c>
-      <c r="F6" s="228">
+      <c r="F6" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G6" s="229">
+      <c r="G6" s="192">
         <f>F6/F32</f>
         <v>0</v>
       </c>
-      <c r="H6" s="230">
+      <c r="H6" s="193">
         <f>(F6/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I6" s="236">
+      <c r="I6" s="199">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J6" s="151">
@@ -5007,31 +5027,31 @@
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="226">
+      <c r="B7" s="189">
         <v>2</v>
       </c>
-      <c r="C7" s="226" t="s">
+      <c r="C7" s="189" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="227">
+      <c r="D7" s="190">
         <v>3897.7</v>
       </c>
-      <c r="E7" s="227">
+      <c r="E7" s="190">
         <v>3897.7</v>
       </c>
-      <c r="F7" s="228">
+      <c r="F7" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G7" s="229">
+      <c r="G7" s="192">
         <f>F7/F32</f>
         <v>0</v>
       </c>
-      <c r="H7" s="230">
+      <c r="H7" s="193">
         <f>(F7/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I7" s="236">
+      <c r="I7" s="199">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J7" s="151">
@@ -5044,31 +5064,31 @@
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="226">
+      <c r="B8" s="189">
         <v>2</v>
       </c>
-      <c r="C8" s="226" t="s">
+      <c r="C8" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="227">
+      <c r="D8" s="190">
         <v>2956.2</v>
       </c>
-      <c r="E8" s="227">
+      <c r="E8" s="190">
         <v>2956.2</v>
       </c>
-      <c r="F8" s="228">
+      <c r="F8" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="229">
+      <c r="G8" s="192">
         <f>F8/F32</f>
         <v>0</v>
       </c>
-      <c r="H8" s="230">
+      <c r="H8" s="193">
         <f>(F8/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I8" s="236">
+      <c r="I8" s="199">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J8" s="151">
@@ -5081,31 +5101,31 @@
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="226">
+      <c r="B9" s="189">
         <v>2</v>
       </c>
-      <c r="C9" s="226" t="s">
+      <c r="C9" s="189" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="227">
+      <c r="D9" s="190">
         <v>3923.7</v>
       </c>
-      <c r="E9" s="227">
+      <c r="E9" s="190">
         <v>3923.7</v>
       </c>
-      <c r="F9" s="228">
+      <c r="F9" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="229">
+      <c r="G9" s="192">
         <f>F9/F32</f>
         <v>0</v>
       </c>
-      <c r="H9" s="237">
+      <c r="H9" s="200">
         <f>(F9/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I9" s="236">
+      <c r="I9" s="199">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J9" s="151">
@@ -5118,31 +5138,31 @@
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="226">
+      <c r="B10" s="189">
         <v>3</v>
       </c>
-      <c r="C10" s="226" t="s">
+      <c r="C10" s="189" t="s">
         <v>81</v>
       </c>
-      <c r="D10" s="227">
+      <c r="D10" s="190">
         <v>2881.8</v>
       </c>
-      <c r="E10" s="227">
+      <c r="E10" s="190">
         <v>2881.8</v>
       </c>
-      <c r="F10" s="228">
+      <c r="F10" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="229">
+      <c r="G10" s="192">
         <f>F10/F32</f>
         <v>0</v>
       </c>
-      <c r="H10" s="230">
+      <c r="H10" s="193">
         <f>(F10/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I10" s="236">
+      <c r="I10" s="199">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J10" s="151">
@@ -5155,31 +5175,31 @@
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="232">
+      <c r="B11" s="195">
         <v>3</v>
       </c>
-      <c r="C11" s="232" t="s">
+      <c r="C11" s="195" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="233">
+      <c r="D11" s="196">
         <v>4646</v>
       </c>
-      <c r="E11" s="233">
+      <c r="E11" s="196">
         <v>4828</v>
       </c>
-      <c r="F11" s="234">
+      <c r="F11" s="197">
         <f t="shared" si="1"/>
         <v>182</v>
       </c>
-      <c r="G11" s="235">
+      <c r="G11" s="198">
         <f>F11/F32</f>
         <v>0.32587287376902419</v>
       </c>
-      <c r="H11" s="230">
+      <c r="H11" s="193">
         <f>(F11/F32)*H32</f>
         <v>64244.793923444988</v>
       </c>
-      <c r="I11" s="236">
+      <c r="I11" s="199">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J11" s="151">
@@ -5192,31 +5212,31 @@
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="226">
+      <c r="B12" s="189">
         <v>3</v>
       </c>
-      <c r="C12" s="226" t="s">
+      <c r="C12" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="227">
+      <c r="D12" s="190">
         <v>4554.6000000000004</v>
       </c>
-      <c r="E12" s="227">
+      <c r="E12" s="190">
         <v>4554.6000000000004</v>
       </c>
-      <c r="F12" s="228">
+      <c r="F12" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G12" s="229">
+      <c r="G12" s="192">
         <f>F12/F32</f>
         <v>0</v>
       </c>
-      <c r="H12" s="230">
+      <c r="H12" s="193">
         <f>(F12/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I12" s="236">
+      <c r="I12" s="199">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J12" s="151">
@@ -5229,31 +5249,31 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="226">
+      <c r="B13" s="189">
         <v>3</v>
       </c>
-      <c r="C13" s="226" t="s">
+      <c r="C13" s="189" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="227">
+      <c r="D13" s="190">
         <v>4138.6000000000004</v>
       </c>
-      <c r="E13" s="227">
+      <c r="E13" s="190">
         <v>4138.6000000000004</v>
       </c>
-      <c r="F13" s="228">
+      <c r="F13" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="229">
+      <c r="G13" s="192">
         <f>F13/F32</f>
         <v>0</v>
       </c>
-      <c r="H13" s="230">
+      <c r="H13" s="193">
         <f>(F13/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I13" s="236">
+      <c r="I13" s="199">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J13" s="151">
@@ -5266,31 +5286,31 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="226">
+      <c r="B14" s="189">
         <v>4</v>
       </c>
-      <c r="C14" s="226" t="s">
+      <c r="C14" s="189" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="227">
+      <c r="D14" s="190">
         <v>8190.4</v>
       </c>
-      <c r="E14" s="227">
+      <c r="E14" s="190">
         <v>8190.4</v>
       </c>
-      <c r="F14" s="228">
+      <c r="F14" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G14" s="229">
+      <c r="G14" s="192">
         <f>F14/F32</f>
         <v>0</v>
       </c>
-      <c r="H14" s="230">
+      <c r="H14" s="193">
         <f>(F14/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I14" s="236">
+      <c r="I14" s="199">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J14" s="151">
@@ -5303,31 +5323,31 @@
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="226">
+      <c r="B15" s="189">
         <v>4</v>
       </c>
-      <c r="C15" s="226" t="s">
+      <c r="C15" s="189" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="227">
+      <c r="D15" s="190">
         <v>3475.3</v>
       </c>
-      <c r="E15" s="227">
+      <c r="E15" s="190">
         <v>3475.3</v>
       </c>
-      <c r="F15" s="228">
+      <c r="F15" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G15" s="229">
+      <c r="G15" s="192">
         <f>F15/F32</f>
         <v>0</v>
       </c>
-      <c r="H15" s="230">
+      <c r="H15" s="193">
         <f>(F15/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I15" s="236">
+      <c r="I15" s="199">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J15" s="151">
@@ -5340,31 +5360,31 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="226">
+      <c r="B16" s="189">
         <v>4</v>
       </c>
-      <c r="C16" s="226" t="s">
+      <c r="C16" s="189" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="227">
+      <c r="D16" s="190">
         <v>4363.3</v>
       </c>
-      <c r="E16" s="227">
+      <c r="E16" s="190">
         <v>4363.3</v>
       </c>
-      <c r="F16" s="228">
+      <c r="F16" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G16" s="229">
+      <c r="G16" s="192">
         <f>F16/F32</f>
         <v>0</v>
       </c>
-      <c r="H16" s="230">
+      <c r="H16" s="193">
         <f>(F16/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I16" s="236">
+      <c r="I16" s="199">
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J16" s="151">
@@ -5377,31 +5397,31 @@
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="226">
+      <c r="B17" s="189">
         <v>4</v>
       </c>
-      <c r="C17" s="226" t="s">
+      <c r="C17" s="189" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="227">
+      <c r="D17" s="190">
         <v>6036.6</v>
       </c>
-      <c r="E17" s="227">
+      <c r="E17" s="190">
         <v>6036.6</v>
       </c>
-      <c r="F17" s="228">
+      <c r="F17" s="191">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G17" s="229">
+      <c r="G17" s="192">
         <f>F17/F32</f>
         <v>0</v>
       </c>
-      <c r="H17" s="230">
+      <c r="H17" s="193">
         <f>(F17/F32)*H32</f>
         <v>0</v>
       </c>
-      <c r="I17" s="236">
+      <c r="I17" s="199">
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J17" s="151">
@@ -5416,21 +5436,21 @@
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="106"/>
       <c r="C18" s="106"/>
-      <c r="D18" s="238"/>
-      <c r="E18" s="238"/>
-      <c r="F18" s="239">
+      <c r="D18" s="201"/>
+      <c r="E18" s="201"/>
+      <c r="F18" s="202">
         <f>SUM(F3:F17)</f>
         <v>558.5</v>
       </c>
       <c r="G18" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="H18" s="230">
+      <c r="H18" s="193">
         <f>SUM(H3:H17)</f>
         <v>197146.79893540672</v>
       </c>
       <c r="I18" s="106"/>
-      <c r="J18" s="240">
+      <c r="J18" s="203">
         <f>SUM(J3:J17)</f>
         <v>235686.61542200952</v>
       </c>
@@ -5446,7 +5466,7 @@
       <c r="E19" s="106"/>
       <c r="F19" s="106"/>
       <c r="G19" s="106"/>
-      <c r="H19" s="241"/>
+      <c r="H19" s="204"/>
       <c r="K19" s="150">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5464,7 +5484,7 @@
       <c r="F20" s="106"/>
       <c r="G20" s="106"/>
       <c r="H20" s="106"/>
-      <c r="I20" s="236">
+      <c r="I20" s="199">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="J20" s="151">
@@ -5488,7 +5508,7 @@
       <c r="F21" s="106"/>
       <c r="G21" s="106"/>
       <c r="H21" s="106"/>
-      <c r="I21" s="236">
+      <c r="I21" s="199">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J21" s="151">
@@ -5512,7 +5532,7 @@
       <c r="F22" s="106"/>
       <c r="G22" s="106"/>
       <c r="H22" s="106"/>
-      <c r="I22" s="236">
+      <c r="I22" s="199">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J22" s="151">
@@ -5536,7 +5556,7 @@
       <c r="F23" s="106"/>
       <c r="G23" s="106"/>
       <c r="H23" s="106"/>
-      <c r="I23" s="236">
+      <c r="I23" s="199">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J23" s="151">
@@ -5560,7 +5580,7 @@
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
       <c r="H24" s="106"/>
-      <c r="I24" s="236">
+      <c r="I24" s="199">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J24" s="151">
@@ -5584,7 +5604,7 @@
       <c r="F25" s="106"/>
       <c r="G25" s="106"/>
       <c r="H25" s="106"/>
-      <c r="I25" s="236">
+      <c r="I25" s="199">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J25" s="151">
@@ -5608,7 +5628,7 @@
       <c r="F26" s="106"/>
       <c r="G26" s="106"/>
       <c r="H26" s="106"/>
-      <c r="I26" s="236">
+      <c r="I26" s="199">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J26" s="151">
@@ -5632,7 +5652,7 @@
       <c r="F27" s="106"/>
       <c r="G27" s="106"/>
       <c r="H27" s="106"/>
-      <c r="I27" s="236">
+      <c r="I27" s="199">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="J27" s="151">
@@ -5668,17 +5688,17 @@
       <c r="F29" s="109"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D30" s="243" t="s">
+      <c r="D30" s="253" t="s">
         <v>152</v>
       </c>
-      <c r="E30" s="244"/>
+      <c r="E30" s="254"/>
       <c r="F30" s="108">
         <v>1254</v>
       </c>
       <c r="G30" s="107" t="s">
         <v>153</v>
       </c>
-      <c r="H30" s="245">
+      <c r="H30" s="206">
         <v>442653.69</v>
       </c>
       <c r="K30" s="150">
@@ -5690,103 +5710,103 @@
       <c r="D31" s="109"/>
       <c r="E31" s="109"/>
       <c r="F31" s="110"/>
-      <c r="H31" s="246"/>
-      <c r="K31" s="247"/>
+      <c r="H31" s="207"/>
+      <c r="K31" s="208"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D32" s="243" t="s">
+      <c r="D32" s="253" t="s">
         <v>154</v>
       </c>
-      <c r="E32" s="244"/>
-      <c r="F32" s="239">
+      <c r="E32" s="254"/>
+      <c r="F32" s="202">
         <f>SUM(F3:F17)</f>
         <v>558.5</v>
       </c>
       <c r="G32" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="H32" s="248">
+      <c r="H32" s="209">
         <f>H30-H34</f>
         <v>197146.79893540672</v>
       </c>
-      <c r="K32" s="247"/>
+      <c r="K32" s="208"/>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D33" s="243"/>
-      <c r="E33" s="244"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="254"/>
       <c r="F33" s="108"/>
       <c r="G33" s="107"/>
-      <c r="H33" s="249"/>
-      <c r="K33" s="247"/>
+      <c r="H33" s="210"/>
+      <c r="K33" s="208"/>
     </row>
     <row r="34" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D34" s="243" t="s">
+      <c r="D34" s="253" t="s">
         <v>155</v>
       </c>
-      <c r="E34" s="244"/>
-      <c r="F34" s="239">
+      <c r="E34" s="254"/>
+      <c r="F34" s="202">
         <f>F30-F32</f>
         <v>695.5</v>
       </c>
       <c r="G34" s="107" t="s">
         <v>156</v>
       </c>
-      <c r="H34" s="248">
+      <c r="H34" s="209">
         <f>(H30*F34)/F30</f>
         <v>245506.89106459328</v>
       </c>
       <c r="K34" s="1"/>
     </row>
     <row r="36" spans="4:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F36" s="250" t="s">
+      <c r="F36" s="255" t="s">
         <v>157</v>
       </c>
-      <c r="G36" s="251"/>
-      <c r="H36" s="252">
+      <c r="G36" s="256"/>
+      <c r="H36" s="211">
         <f>H32+H33+H34</f>
         <v>442653.69</v>
       </c>
     </row>
     <row r="38" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D38" s="253" t="s">
+      <c r="D38" s="251" t="s">
         <v>158</v>
       </c>
-      <c r="E38" s="254"/>
-      <c r="F38" s="255">
+      <c r="E38" s="252"/>
+      <c r="F38" s="212">
         <v>46164</v>
       </c>
-      <c r="G38" s="255">
+      <c r="G38" s="212">
         <v>46197</v>
       </c>
-      <c r="H38" s="256" t="s">
+      <c r="H38" s="213" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="39" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D39" s="253" t="s">
+      <c r="D39" s="251" t="s">
         <v>160</v>
       </c>
-      <c r="E39" s="254"/>
-      <c r="F39" s="256">
+      <c r="E39" s="252"/>
+      <c r="F39" s="213">
         <v>274268</v>
       </c>
-      <c r="G39" s="256">
+      <c r="G39" s="213">
         <v>275522</v>
       </c>
-      <c r="H39" s="256">
+      <c r="H39" s="213">
         <f>G39-F39</f>
         <v>1254</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="D38:E38"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="D38:E38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
